--- a/data/DB_Dashboard.xlsx
+++ b/data/DB_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmari\Desktop\Observatorio Calp\observatorio_calp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9713CB-9C66-440A-AB17-65AA5C52A496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E54697-B080-4C1B-B2B8-7CC63FE6A5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A3E3E45F-D34A-4772-8FFC-37BF922E3DDC}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="340">
   <si>
     <t>Año</t>
   </si>
@@ -196,9 +196,6 @@
   </si>
   <si>
     <t>Volumen de residuos producidos por los turistas al mes ÷ número total de pernoctaciones de turistas residentes = Residuos por pernoctación de turista residente al mes</t>
-  </si>
-  <si>
-    <t>Volumen total de materiales reciclados por año ÷ número total de turistas por año = volumen total de residuos reciclados por turista por año</t>
   </si>
   <si>
     <t>Volumen total de residuos reciclados por turista por año ÷ Volumen total de residuos reciclados por residente por año*100 = porcentaje de residuos reciclados por turista por año</t>
@@ -1452,14 +1449,29 @@
       <t>.2</t>
     </r>
   </si>
+  <si>
+    <t>Volumen total de materiales reciclados por año ÷ número total de turistas por año = Volumen total de residuos reciclados por turista por año</t>
+  </si>
+  <si>
+    <t>Cantidades de residuos reciclados por residentes al año</t>
+  </si>
+  <si>
+    <t>Cantidades de residuos reciclados por turista al año</t>
+  </si>
+  <si>
+    <t>ETIS - Residuos reciclados por turistas respecto al total</t>
+  </si>
+  <si>
+    <t>ETIS - Residuos reciclados por residentes respecto al total</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1680,7 +1692,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1768,20 +1780,16 @@
     <xf numFmtId="4" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1790,6 +1798,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1814,6 +1825,7 @@
         <name val="Montserrat"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
     </dxf>
     <dxf>
       <font>
@@ -1831,569 +1843,7 @@
         <name val="Montserrat"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="171" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="171" formatCode="0.0%"/>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
     </dxf>
     <dxf>
       <font>
@@ -2481,10 +1931,61 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.0"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.0"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
@@ -2496,6 +1997,471 @@
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color indexed="64"/>
@@ -2519,10 +2485,55 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -2545,24 +2556,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{72A2E2F1-7CAD-4C76-BEFF-2442C0A18302}" name="Dashboard" displayName="Dashboard" ref="A1:O52" totalsRowShown="0" headerRowDxfId="2" dataDxfId="1" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="A1:O52" xr:uid="{72A2E2F1-7CAD-4C76-BEFF-2442C0A18302}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{72A2E2F1-7CAD-4C76-BEFF-2442C0A18302}" name="Dashboard" displayName="Dashboard" ref="A1:O52" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31" totalsRowBorderDxfId="30">
+  <autoFilter ref="A1:O52" xr:uid="{72A2E2F1-7CAD-4C76-BEFF-2442C0A18302}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Gestión de residuos"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{1793D8B9-1834-4672-94E2-370894E55593}" name="Año" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{2FF65C8B-F0E1-459C-B72F-3A1A5329FDAB}" name="ETIS" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{F07E8271-E1B8-461E-B50E-2EB9D386F2B2}" name="AT" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{0D608246-D32D-48AD-800A-6F54D324BFD7}" name="id" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{D51E5057-D018-405C-B143-B371CD456218}" name="Ámbito" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{CFCF5ECA-0AA5-45F6-A186-ECCAC4B1EC6E}" name="Descripción" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{1488B99B-78C9-4468-8D60-263604C2D928}" name="Indicador" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{4AC59F78-D67E-44DA-81BA-1C07113D1CC5}" name="Organismo" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{F4FC4163-F838-4797-BEA4-9644F0B3C06D}" name="Fuente" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{7198AE02-1EA6-4D67-A26F-8B3748D568D6}" name="Tiempo" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{4C02F462-3174-4584-8410-1077CADC5591}" name="Unidad" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{8FB0E2B5-632E-4D1F-AAEB-0F2BD259FA74}" name="Método de cálculo" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{C3FBCC74-5AA3-417F-9D36-95040BB64175}" name="Datos requeridos" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{1CC99560-09A8-483F-9CD5-16A60F770D27}" name="Valor" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{AB90ABD6-A80B-4C26-AC5E-FC8654EC0E4D}" name="Comentarios" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{1793D8B9-1834-4672-94E2-370894E55593}" name="Año" dataDxfId="29"/>
+    <tableColumn id="12" xr3:uid="{2FF65C8B-F0E1-459C-B72F-3A1A5329FDAB}" name="ETIS" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{F07E8271-E1B8-461E-B50E-2EB9D386F2B2}" name="AT" dataDxfId="27"/>
+    <tableColumn id="14" xr3:uid="{0D608246-D32D-48AD-800A-6F54D324BFD7}" name="id" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{D51E5057-D018-405C-B143-B371CD456218}" name="Ámbito" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{CFCF5ECA-0AA5-45F6-A186-ECCAC4B1EC6E}" name="Descripción" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{1488B99B-78C9-4468-8D60-263604C2D928}" name="Indicador" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{4AC59F78-D67E-44DA-81BA-1C07113D1CC5}" name="Organismo" dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{F4FC4163-F838-4797-BEA4-9644F0B3C06D}" name="Fuente" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{7198AE02-1EA6-4D67-A26F-8B3748D568D6}" name="Tiempo" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{4C02F462-3174-4584-8410-1077CADC5591}" name="Unidad" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{8FB0E2B5-632E-4D1F-AAEB-0F2BD259FA74}" name="Método de cálculo" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{C3FBCC74-5AA3-417F-9D36-95040BB64175}" name="Datos requeridos" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{1CC99560-09A8-483F-9CD5-16A60F770D27}" name="Valor" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{AB90ABD6-A80B-4C26-AC5E-FC8654EC0E4D}" name="Comentarios" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2575,28 +2592,28 @@
     <tableColumn id="1" xr3:uid="{37A32B2F-03BA-4553-8470-CA20D3777409}" name="Mes"/>
     <tableColumn id="8" xr3:uid="{2CA49775-932E-45F6-944E-9F105552BC72}" name="Orden meses"/>
     <tableColumn id="7" xr3:uid="{5FB8A54B-30AF-4CF9-8720-8E59D72FAE07}" name="Año"/>
-    <tableColumn id="2" xr3:uid="{B343196D-F313-4338-A33E-C35CA22E1037}" name="1. Turistas extranjeros que visitaron Calp" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{7694471A-5A27-4BAB-9627-5B49B697400E}" name="1. Turistas nacionales que visitaron Calp" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{1BAEF350-378C-40C2-820B-759FCF4ED388}" name="1. Total turistas" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{A35DAE71-EE4A-4EC9-8460-F2F26963F5A2}" name="2.% Turistas extranjeros que visitaron Calp" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{77257F63-E741-45A0-A7C8-573D91BC35FA}" name="2. % Turistas nacionales que visitaron Calp" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{B343196D-F313-4338-A33E-C35CA22E1037}" name="1. Turistas extranjeros que visitaron Calp" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{7694471A-5A27-4BAB-9627-5B49B697400E}" name="1. Turistas nacionales que visitaron Calp" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{1BAEF350-378C-40C2-820B-759FCF4ED388}" name="1. Total turistas" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{A35DAE71-EE4A-4EC9-8460-F2F26963F5A2}" name="2.% Turistas extranjeros que visitaron Calp" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{77257F63-E741-45A0-A7C8-573D91BC35FA}" name="2. % Turistas nacionales que visitaron Calp" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{32B811EC-84D2-45FC-891C-7E090EB6CBCD}" name="Alojamientos" displayName="Alojamientos" ref="A1:H9" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{32B811EC-84D2-45FC-891C-7E090EB6CBCD}" name="Alojamientos" displayName="Alojamientos" ref="A1:H9" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:H9" xr:uid="{32B811EC-84D2-45FC-891C-7E090EB6CBCD}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{07BCC607-7EEB-4361-B136-CCDA8E5F70BE}" name="Tipo" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{0871BF09-A2EB-42F4-86E2-C14CDB481EC8}" name="Año" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{B1AB5E11-B4CF-48BB-A35C-C459F9489AB4}" name="Establecimientos" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{ACC63EB1-5B06-4BEE-9E7E-B340C9BD2498}" name="Plazas" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{03DB75FF-9B48-49D9-9D17-D4363A5A9025}" name="Habitaciones" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{B55E2CBA-9D33-447F-AFD9-B5ED8123A040}" name="Parcelas" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{18A9F2D6-F247-4306-843D-3BC9A08F8F16}" name="% alojamientos" dataDxfId="21" dataCellStyle="Porcentaje"/>
-    <tableColumn id="7" xr3:uid="{0CA9FABA-AC27-4D35-A37F-5ADFC3A1E28A}" name="% plazas" dataDxfId="20" dataCellStyle="Porcentaje">
+    <tableColumn id="1" xr3:uid="{07BCC607-7EEB-4361-B136-CCDA8E5F70BE}" name="Tipo" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{0871BF09-A2EB-42F4-86E2-C14CDB481EC8}" name="Año" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{B1AB5E11-B4CF-48BB-A35C-C459F9489AB4}" name="Establecimientos" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{ACC63EB1-5B06-4BEE-9E7E-B340C9BD2498}" name="Plazas" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{03DB75FF-9B48-49D9-9D17-D4363A5A9025}" name="Habitaciones" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{B55E2CBA-9D33-447F-AFD9-B5ED8123A040}" name="Parcelas" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{18A9F2D6-F247-4306-843D-3BC9A08F8F16}" name="% alojamientos" dataDxfId="1" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{0CA9FABA-AC27-4D35-A37F-5ADFC3A1E28A}" name="% plazas" dataDxfId="0" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>D2/D$9</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2932,20 +2949,20 @@
   <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="11.5546875" style="40"/>
-    <col min="3" max="4" width="16.6640625" style="40" customWidth="1"/>
-    <col min="5" max="5" width="52.5546875" style="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="113" style="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.6640625" style="40" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.6640625" style="40" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.6640625" style="40" customWidth="1"/>
-    <col min="10" max="10" width="14.21875" style="40" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" style="40"/>
-    <col min="12" max="12" width="22" style="40" customWidth="1"/>
-    <col min="13" max="13" width="21.5546875" style="40" customWidth="1"/>
-    <col min="14" max="14" width="15.21875" style="48" customWidth="1"/>
-    <col min="15" max="15" width="255.77734375" style="49" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="11.5546875" style="40"/>
+    <col min="1" max="2" width="11.5546875" style="37"/>
+    <col min="3" max="4" width="16.6640625" style="37" customWidth="1"/>
+    <col min="5" max="5" width="52.5546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="113" style="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.6640625" style="37" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.6640625" style="37" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.6640625" style="37" customWidth="1"/>
+    <col min="10" max="10" width="14.21875" style="37" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" style="37"/>
+    <col min="12" max="12" width="22" style="37" customWidth="1"/>
+    <col min="13" max="13" width="21.5546875" style="37" customWidth="1"/>
+    <col min="14" max="14" width="15.21875" style="44" customWidth="1"/>
+    <col min="15" max="15" width="255.77734375" style="45" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="11.5546875" style="37"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
@@ -2959,7 +2976,7 @@
         <v>19</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -2986,21 +3003,21 @@
         <v>6</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A2" s="24">
         <v>2024</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="26" t="s">
         <v>20</v>
@@ -3012,16 +3029,16 @@
         <v>8</v>
       </c>
       <c r="F2" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2" s="29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J2" s="29" t="s">
         <v>11</v>
@@ -3030,24 +3047,24 @@
         <v>12</v>
       </c>
       <c r="L2" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="M2" s="27" t="s">
         <v>60</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>61</v>
       </c>
       <c r="N2" s="28">
         <v>1.1399999999999999</v>
       </c>
       <c r="O2" s="29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <v>2024</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>20</v>
@@ -3062,13 +3079,13 @@
         <v>9</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>11</v>
@@ -3080,19 +3097,19 @@
         <v>14</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <v>2024</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>20</v>
@@ -3107,13 +3124,13 @@
         <v>15</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>11</v>
@@ -3125,19 +3142,19 @@
         <v>16</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O4" s="8"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
         <v>2024</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>20</v>
@@ -3149,16 +3166,16 @@
         <v>8</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>281</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>282</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>11</v>
@@ -3167,22 +3184,22 @@
         <v>12</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O5" s="6"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <v>2024</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>20</v>
@@ -3194,16 +3211,16 @@
         <v>8</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>11</v>
@@ -3212,22 +3229,22 @@
         <v>12</v>
       </c>
       <c r="L6" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="M6" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="M6" s="7" t="s">
-        <v>288</v>
-      </c>
       <c r="N6" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A7" s="24">
         <v>2024</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C7" s="26" t="s">
         <v>20</v>
@@ -3239,16 +3256,16 @@
         <v>21</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H7" s="26" t="s">
         <v>10</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J7" s="26" t="s">
         <v>11</v>
@@ -3257,24 +3274,24 @@
         <v>12</v>
       </c>
       <c r="L7" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M7" s="26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N7" s="28">
         <v>52.27</v>
       </c>
       <c r="O7" s="29" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" s="24">
         <v>2024</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>20</v>
@@ -3286,16 +3303,16 @@
         <v>21</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H8" s="26" t="s">
         <v>10</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J8" s="26" t="s">
         <v>11</v>
@@ -3304,24 +3321,24 @@
         <v>12</v>
       </c>
       <c r="L8" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M8" s="26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N8" s="28">
         <v>47.73</v>
       </c>
       <c r="O8" s="29" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A9" s="24">
         <v>2024</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="26" t="s">
         <v>20</v>
@@ -3333,40 +3350,40 @@
         <v>22</v>
       </c>
       <c r="F9" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="H9" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>65</v>
-      </c>
       <c r="I9" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J9" s="26" t="s">
         <v>11</v>
       </c>
       <c r="K9" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="L9" s="26" t="s">
-        <v>67</v>
-      </c>
       <c r="M9" s="26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N9" s="32">
         <v>401126</v>
       </c>
       <c r="O9" s="29"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A10" s="24">
         <v>2024</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" s="26" t="s">
         <v>20</v>
@@ -3378,40 +3395,40 @@
         <v>22</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H10" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="I10" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="J10" s="26" t="s">
+      <c r="L10" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="K10" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="L10" s="26" t="s">
-        <v>72</v>
-      </c>
       <c r="M10" s="26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N10" s="32">
         <v>4813511</v>
       </c>
       <c r="O10" s="29"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A11" s="24">
         <v>2024</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" s="26" t="s">
         <v>20</v>
@@ -3423,42 +3440,42 @@
         <v>22</v>
       </c>
       <c r="F11" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="26" t="s">
         <v>174</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="H11" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" s="26" t="s">
-        <v>175</v>
       </c>
       <c r="J11" s="26" t="s">
         <v>11</v>
       </c>
       <c r="K11" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="L11" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="L11" s="26" t="s">
-        <v>177</v>
-      </c>
       <c r="M11" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N11" s="34">
         <v>120.8</v>
       </c>
       <c r="O11" s="29" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A12" s="24">
         <v>2024</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" s="26" t="s">
         <v>20</v>
@@ -3470,42 +3487,42 @@
         <v>22</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J12" s="26" t="s">
         <v>11</v>
       </c>
       <c r="K12" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="L12" s="26" t="s">
-        <v>76</v>
-      </c>
       <c r="M12" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N12" s="34">
         <v>9.75</v>
       </c>
       <c r="O12" s="29" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A13" s="24">
         <v>2024</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>20</v>
@@ -3517,16 +3534,16 @@
         <v>22</v>
       </c>
       <c r="F13" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="H13" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="H13" s="26" t="s">
-        <v>83</v>
-      </c>
       <c r="I13" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J13" s="26" t="s">
         <v>11</v>
@@ -3535,24 +3552,24 @@
         <v>12</v>
       </c>
       <c r="L13" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M13" s="26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N13" s="34">
         <v>34.97</v>
       </c>
-      <c r="O13" s="47" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="O13" s="43" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A14" s="24">
         <v>2024</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C14" s="26" t="s">
         <v>20</v>
@@ -3564,16 +3581,16 @@
         <v>22</v>
       </c>
       <c r="F14" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="H14" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="G14" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="H14" s="26" t="s">
+      <c r="I14" s="26" t="s">
         <v>182</v>
-      </c>
-      <c r="I14" s="26" t="s">
-        <v>183</v>
       </c>
       <c r="J14" s="26" t="s">
         <v>11</v>
@@ -3582,24 +3599,24 @@
         <v>12</v>
       </c>
       <c r="L14" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="M14" s="26" t="s">
         <v>184</v>
-      </c>
-      <c r="M14" s="26" t="s">
-        <v>185</v>
       </c>
       <c r="N14" s="34">
         <v>11.7</v>
       </c>
       <c r="O14" s="31" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A15" s="24">
         <v>2024</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C15" s="26" t="s">
         <v>28</v>
@@ -3611,16 +3628,16 @@
         <v>22</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I15" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J15" s="26" t="s">
         <v>11</v>
@@ -3629,22 +3646,22 @@
         <v>17</v>
       </c>
       <c r="L15" s="26" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M15" s="26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N15" s="34">
         <v>859</v>
       </c>
-      <c r="O15" s="45"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="O15" s="42"/>
+    </row>
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A16" s="24">
         <v>2024</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C16" s="26" t="s">
         <v>28</v>
@@ -3656,16 +3673,16 @@
         <v>22</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J16" s="26" t="s">
         <v>11</v>
@@ -3674,22 +3691,22 @@
         <v>17</v>
       </c>
       <c r="L16" s="26" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M16" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N16" s="34">
         <v>7</v>
       </c>
-      <c r="O16" s="45"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="O16" s="42"/>
+    </row>
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24">
         <v>2024</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17" s="26" t="s">
         <v>28</v>
@@ -3701,16 +3718,16 @@
         <v>22</v>
       </c>
       <c r="F17" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="G17" s="26" t="s">
         <v>320</v>
       </c>
-      <c r="G17" s="26" t="s">
-        <v>321</v>
-      </c>
       <c r="H17" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I17" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J17" s="26" t="s">
         <v>11</v>
@@ -3719,22 +3736,22 @@
         <v>17</v>
       </c>
       <c r="L17" s="26" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M17" s="26" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N17" s="34">
         <v>4</v>
       </c>
-      <c r="O17" s="45"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="O17" s="42"/>
+    </row>
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A18" s="18">
         <v>2024</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>20</v>
@@ -3746,42 +3763,42 @@
         <v>23</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I18" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L18" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M18" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N18" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O18" s="23" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A19" s="5">
         <v>2024</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>20</v>
@@ -3793,42 +3810,42 @@
         <v>24</v>
       </c>
       <c r="F19" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>239</v>
-      </c>
       <c r="H19" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>233</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>234</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A20" s="24">
         <v>2024</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C20" s="26" t="s">
         <v>20</v>
@@ -3840,42 +3857,42 @@
         <v>25</v>
       </c>
       <c r="F20" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="H20" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="G20" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="H20" s="26" t="s">
-        <v>142</v>
-      </c>
       <c r="I20" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J20" s="26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K20" s="27" t="s">
         <v>12</v>
       </c>
       <c r="L20" s="26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M20" s="26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N20" s="28">
         <v>68.89</v>
       </c>
       <c r="O20" s="29" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="18" hidden="1" x14ac:dyDescent="0.4">
       <c r="A21" s="24">
         <v>2024</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C21" s="26" t="s">
         <v>20</v>
@@ -3887,42 +3904,42 @@
         <v>25</v>
       </c>
       <c r="F21" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="H21" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="I21" s="26" t="s">
         <v>150</v>
-      </c>
-      <c r="G21" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="H21" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="I21" s="26" t="s">
-        <v>151</v>
       </c>
       <c r="J21" s="26" t="s">
         <v>11</v>
       </c>
       <c r="K21" s="27" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L21" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M21" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N21" s="28">
         <v>6.59</v>
       </c>
       <c r="O21" s="29" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="18" hidden="1" x14ac:dyDescent="0.4">
       <c r="A22" s="24">
         <v>2024</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C22" s="26" t="s">
         <v>20</v>
@@ -3934,42 +3951,42 @@
         <v>25</v>
       </c>
       <c r="F22" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="H22" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22" s="26" t="s">
         <v>150</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="H22" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="I22" s="26" t="s">
-        <v>151</v>
       </c>
       <c r="J22" s="26" t="s">
         <v>11</v>
       </c>
       <c r="K22" s="27" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L22" s="26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M22" s="26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N22" s="28">
         <v>12.02</v>
       </c>
       <c r="O22" s="29" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="18" hidden="1" x14ac:dyDescent="0.4">
       <c r="A23" s="24">
         <v>2024</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C23" s="26" t="s">
         <v>20</v>
@@ -3981,34 +3998,34 @@
         <v>25</v>
       </c>
       <c r="F23" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="H23" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="I23" s="26" t="s">
         <v>150</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="H23" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="I23" s="26" t="s">
-        <v>151</v>
       </c>
       <c r="J23" s="26" t="s">
         <v>11</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L23" s="26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M23" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N23" s="28">
         <v>9.56</v>
       </c>
       <c r="O23" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.4">
@@ -4016,7 +4033,7 @@
         <v>2024</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" s="26" t="s">
         <v>20</v>
@@ -4031,7 +4048,7 @@
         <v>37</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H24" s="26" t="s">
         <v>38</v>
@@ -4049,13 +4066,13 @@
         <v>45</v>
       </c>
       <c r="M24" s="26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N24" s="28">
         <v>36.78</v>
       </c>
       <c r="O24" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.4">
@@ -4063,7 +4080,7 @@
         <v>2024</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="26" t="s">
         <v>20</v>
@@ -4078,7 +4095,7 @@
         <v>37</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H25" s="26" t="s">
         <v>38</v>
@@ -4096,13 +4113,13 @@
         <v>44</v>
       </c>
       <c r="M25" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N25" s="28">
         <v>34.18</v>
       </c>
       <c r="O25" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.4">
@@ -4110,7 +4127,7 @@
         <v>2024</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C26" s="26" t="s">
         <v>20</v>
@@ -4125,7 +4142,7 @@
         <v>42</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H26" s="26" t="s">
         <v>38</v>
@@ -4137,19 +4154,19 @@
         <v>11</v>
       </c>
       <c r="K26" s="27" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="L26" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M26" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N26" s="28">
         <v>50.85</v>
       </c>
       <c r="O26" s="29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.4">
@@ -4157,7 +4174,7 @@
         <v>2024</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C27" s="26" t="s">
         <v>20</v>
@@ -4168,11 +4185,11 @@
       <c r="E27" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="26" t="s">
-        <v>42</v>
+      <c r="F27" s="46" t="s">
+        <v>336</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>200</v>
+        <v>339</v>
       </c>
       <c r="H27" s="26" t="s">
         <v>38</v>
@@ -4187,16 +4204,16 @@
         <v>43</v>
       </c>
       <c r="L27" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="M27" s="26" t="s">
         <v>50</v>
-      </c>
-      <c r="M27" s="26" t="s">
-        <v>51</v>
       </c>
       <c r="N27" s="28">
         <v>2.1</v>
       </c>
       <c r="O27" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.4">
@@ -4204,7 +4221,7 @@
         <v>2024</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C28" s="26" t="s">
         <v>20</v>
@@ -4216,10 +4233,10 @@
         <v>18</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>42</v>
+        <v>337</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>200</v>
+        <v>338</v>
       </c>
       <c r="H28" s="26" t="s">
         <v>38</v>
@@ -4234,24 +4251,24 @@
         <v>43</v>
       </c>
       <c r="L28" s="26" t="s">
-        <v>46</v>
+        <v>335</v>
       </c>
       <c r="M28" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N28" s="28">
         <v>4.8899999999999997</v>
       </c>
       <c r="O28" s="29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="18" hidden="1" x14ac:dyDescent="0.4">
       <c r="A29" s="5">
         <v>2024</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>20</v>
@@ -4263,42 +4280,42 @@
         <v>26</v>
       </c>
       <c r="F29" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>262</v>
-      </c>
       <c r="H29" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K29" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="L29" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="L29" s="7" t="s">
+      <c r="M29" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="M29" s="7" t="s">
-        <v>265</v>
-      </c>
       <c r="N29" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O29" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>20</v>
@@ -4310,16 +4327,16 @@
         <v>26</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J30" s="7" t="s">
         <v>11</v>
@@ -4328,24 +4345,24 @@
         <v>17</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A31" s="5">
         <v>2024</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>20</v>
@@ -4357,42 +4374,42 @@
         <v>26</v>
       </c>
       <c r="F31" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I31" s="7" t="s">
         <v>271</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>272</v>
       </c>
       <c r="J31" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K31" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="L31" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="L31" s="7" t="s">
+      <c r="M31" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="M31" s="7" t="s">
+      <c r="N31" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="O31" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="N31" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="O31" s="6" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A32" s="5">
         <v>2024</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>20</v>
@@ -4404,42 +4421,42 @@
         <v>26</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J32" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L32" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="O32" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="M32" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="O32" s="6" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A33" s="24">
         <v>2024</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C33" s="26" t="s">
         <v>20</v>
@@ -4451,16 +4468,16 @@
         <v>27</v>
       </c>
       <c r="F33" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="G33" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="G33" s="26" t="s">
+      <c r="H33" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H33" s="26" t="s">
-        <v>253</v>
-      </c>
       <c r="I33" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J33" s="26" t="s">
         <v>11</v>
@@ -4469,24 +4486,24 @@
         <v>12</v>
       </c>
       <c r="L33" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="M33" s="26" t="s">
         <v>254</v>
-      </c>
-      <c r="M33" s="26" t="s">
-        <v>255</v>
       </c>
       <c r="N33" s="30">
         <v>45</v>
       </c>
       <c r="O33" s="29" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.4">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A34" s="24">
         <v>2024</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C34" s="26" t="s">
         <v>28</v>
@@ -4498,16 +4515,16 @@
         <v>29</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I34" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J34" s="26" t="s">
         <v>11</v>
@@ -4516,24 +4533,24 @@
         <v>12</v>
       </c>
       <c r="L34" s="26" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M34" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N34" s="28">
         <v>82.11</v>
       </c>
       <c r="O34" s="29" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.4">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A35" s="24">
         <v>2024</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C35" s="26" t="s">
         <v>28</v>
@@ -4545,16 +4562,16 @@
         <v>29</v>
       </c>
       <c r="F35" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G35" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="H35" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="I35" s="26" t="s">
         <v>166</v>
-      </c>
-      <c r="G35" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="H35" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="I35" s="26" t="s">
-        <v>167</v>
       </c>
       <c r="J35" s="26" t="s">
         <v>11</v>
@@ -4563,24 +4580,24 @@
         <v>12</v>
       </c>
       <c r="L35" s="26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M35" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N35" s="28">
         <v>17.89</v>
       </c>
       <c r="O35" s="29" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.4">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A36" s="18">
         <v>2024</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C36" s="20" t="s">
         <v>28</v>
@@ -4589,45 +4606,45 @@
         <v>11</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I36" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J36" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K36" s="21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L36" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M36" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N36" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O36" s="23" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A37" s="18">
         <v>2024</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C37" s="20" t="s">
         <v>28</v>
@@ -4636,45 +4653,45 @@
         <v>12</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I37" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K37" s="21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L37" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M37" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N37" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O37" s="23" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A38" s="24">
         <v>2024</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C38" s="26" t="s">
         <v>28</v>
@@ -4686,42 +4703,42 @@
         <v>30</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G38" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I38" s="26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J38" s="26" t="s">
         <v>11</v>
       </c>
       <c r="K38" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L38" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="L38" s="26" t="s">
-        <v>90</v>
-      </c>
       <c r="M38" s="26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N38" s="28">
         <v>49.16</v>
       </c>
       <c r="O38" s="29" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A39" s="24">
         <v>2024</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C39" s="26" t="s">
         <v>28</v>
@@ -4733,16 +4750,16 @@
         <v>30</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G39" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I39" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J39" s="26" t="s">
         <v>11</v>
@@ -4751,24 +4768,24 @@
         <v>12</v>
       </c>
       <c r="L39" s="26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M39" s="26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N39" s="28">
         <v>37.65</v>
       </c>
-      <c r="O39" s="47" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="O39" s="43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A40" s="24">
         <v>2024</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C40" s="26" t="s">
         <v>28</v>
@@ -4780,16 +4797,16 @@
         <v>30</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G40" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I40" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J40" s="26" t="s">
         <v>11</v>
@@ -4798,24 +4815,24 @@
         <v>12</v>
       </c>
       <c r="L40" s="26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M40" s="26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N40" s="28">
         <v>32.590000000000003</v>
       </c>
-      <c r="O40" s="47" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="O40" s="43" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A41" s="24">
         <v>2024</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C41" s="26" t="s">
         <v>28</v>
@@ -4827,16 +4844,16 @@
         <v>30</v>
       </c>
       <c r="F41" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G41" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="H41" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="G41" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="H41" s="26" t="s">
+      <c r="I41" s="26" t="s">
         <v>105</v>
-      </c>
-      <c r="I41" s="26" t="s">
-        <v>106</v>
       </c>
       <c r="J41" s="26" t="s">
         <v>11</v>
@@ -4845,24 +4862,24 @@
         <v>12</v>
       </c>
       <c r="L41" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="M41" s="26" t="s">
         <v>108</v>
-      </c>
-      <c r="M41" s="26" t="s">
-        <v>109</v>
       </c>
       <c r="N41" s="30">
         <v>70</v>
       </c>
       <c r="O41" s="31" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.4">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A42" s="24">
         <v>2024</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C42" s="26" t="s">
         <v>28</v>
@@ -4874,16 +4891,16 @@
         <v>31</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G42" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H42" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="I42" s="26" t="s">
         <v>182</v>
-      </c>
-      <c r="I42" s="26" t="s">
-        <v>183</v>
       </c>
       <c r="J42" s="26" t="s">
         <v>11</v>
@@ -4892,24 +4909,24 @@
         <v>12</v>
       </c>
       <c r="L42" s="26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M42" s="26" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N42" s="30">
         <v>18</v>
       </c>
       <c r="O42" s="29" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.4">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A43" s="24">
         <v>2024</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C43" s="26" t="s">
         <v>28</v>
@@ -4921,16 +4938,16 @@
         <v>32</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G43" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I43" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J43" s="26" t="s">
         <v>11</v>
@@ -4939,24 +4956,24 @@
         <v>12</v>
       </c>
       <c r="L43" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M43" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N43" s="30">
         <v>94</v>
       </c>
       <c r="O43" s="29" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.4">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A44" s="24">
         <v>2024</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C44" s="26" t="s">
         <v>28</v>
@@ -4968,16 +4985,16 @@
         <v>32</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G44" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H44" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I44" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J44" s="26" t="s">
         <v>11</v>
@@ -4986,24 +5003,24 @@
         <v>12</v>
       </c>
       <c r="L44" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M44" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N44" s="30">
         <v>6</v>
       </c>
       <c r="O44" s="29" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.4">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A45" s="24">
         <v>2024</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C45" s="26" t="s">
         <v>28</v>
@@ -5015,40 +5032,40 @@
         <v>32</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G45" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H45" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I45" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J45" s="26" t="s">
         <v>11</v>
       </c>
       <c r="K45" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L45" s="26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M45" s="26"/>
       <c r="N45" s="32">
         <v>737000000</v>
       </c>
       <c r="O45" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.4">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A46" s="24">
         <v>2024</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C46" s="26" t="s">
         <v>28</v>
@@ -5060,42 +5077,42 @@
         <v>32</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G46" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I46" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J46" s="26" t="s">
         <v>11</v>
       </c>
       <c r="K46" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L46" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M46" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N46" s="32">
         <v>575000000</v>
       </c>
       <c r="O46" s="29" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.4">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A47" s="24">
         <v>2024</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C47" s="26" t="s">
         <v>28</v>
@@ -5107,42 +5124,42 @@
         <v>32</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G47" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I47" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J47" s="26" t="s">
         <v>11</v>
       </c>
       <c r="K47" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L47" s="26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M47" s="26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N47" s="32">
         <v>162000000</v>
       </c>
       <c r="O47" s="29" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="16.8" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="5">
         <v>2024</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>28</v>
@@ -5154,42 +5171,42 @@
         <v>33</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G48" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="H48" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="H48" s="7" t="s">
-        <v>243</v>
-      </c>
       <c r="I48" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J48" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L48" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N48" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O48" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="16.8" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="5">
         <v>2024</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>28</v>
@@ -5201,16 +5218,16 @@
         <v>33</v>
       </c>
       <c r="F49" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="I49" s="7" t="s">
         <v>246</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>247</v>
       </c>
       <c r="J49" s="7" t="s">
         <v>11</v>
@@ -5219,22 +5236,22 @@
         <v>17</v>
       </c>
       <c r="L49" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="M49" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N49" s="9"/>
       <c r="O49" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.4">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A50" s="24">
         <v>2024</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C50" s="26" t="s">
         <v>28</v>
@@ -5246,16 +5263,16 @@
         <v>34</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G50" s="26" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H50" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="I50" s="26" t="s">
         <v>182</v>
-      </c>
-      <c r="I50" s="26" t="s">
-        <v>183</v>
       </c>
       <c r="J50" s="26" t="s">
         <v>11</v>
@@ -5264,24 +5281,24 @@
         <v>12</v>
       </c>
       <c r="L50" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M50" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N50" s="30">
         <v>9</v>
       </c>
       <c r="O50" s="29" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.4">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A51" s="5">
         <v>2024</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>28</v>
@@ -5293,16 +5310,16 @@
         <v>35</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J51" s="7" t="s">
         <v>11</v>
@@ -5311,24 +5328,24 @@
         <v>12</v>
       </c>
       <c r="L51" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="M51" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="M51" s="7" t="s">
+      <c r="N51" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="O51" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="N51" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="O51" s="8" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A52" s="13">
         <v>2024</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>28</v>
@@ -5340,16 +5357,16 @@
         <v>35</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J52" s="7" t="s">
         <v>11</v>
@@ -5358,16 +5375,16 @@
         <v>12</v>
       </c>
       <c r="L52" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="M52" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="M52" s="15" t="s">
-        <v>270</v>
-      </c>
       <c r="N52" s="16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O52" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -5389,8 +5406,7 @@
   <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.5546875" style="39"/>
-    <col min="3" max="3" width="11.5546875" style="39" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" customWidth="1"/>
     <col min="4" max="4" width="46.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -5400,369 +5416,369 @@
   <sheetData>
     <row r="1" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E1" t="s">
+        <v>331</v>
+      </c>
+      <c r="F1" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="G1" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1" t="s">
         <v>329</v>
       </c>
-      <c r="C1" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="46" t="s">
-        <v>333</v>
-      </c>
-      <c r="E1" s="46" t="s">
-        <v>332</v>
-      </c>
-      <c r="F1" s="46" t="s">
-        <v>303</v>
-      </c>
-      <c r="G1" s="46" t="s">
-        <v>331</v>
-      </c>
-      <c r="H1" s="46" t="s">
-        <v>330</v>
-      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2024</v>
+      </c>
+      <c r="D2" s="35">
+        <v>13510</v>
+      </c>
+      <c r="E2" s="35">
+        <v>12491</v>
+      </c>
+      <c r="F2" s="35">
+        <v>26001</v>
+      </c>
+      <c r="G2" s="36">
+        <v>5.4483715378038751</v>
+      </c>
+      <c r="H2" s="36">
+        <v>4.0201603429575581</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>290</v>
       </c>
-      <c r="B2" s="39">
-        <v>1</v>
-      </c>
-      <c r="C2" s="39">
-        <v>2024</v>
-      </c>
-      <c r="D2" s="36">
-        <v>13510</v>
-      </c>
-      <c r="E2" s="36">
-        <v>12491</v>
-      </c>
-      <c r="F2" s="36">
-        <v>26001</v>
-      </c>
-      <c r="G2" s="37">
-        <v>5.4483715378038751</v>
-      </c>
-      <c r="H2" s="38">
-        <v>4.0201603429575581</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2024</v>
+      </c>
+      <c r="D3" s="35">
+        <v>12883</v>
+      </c>
+      <c r="E3" s="35">
+        <v>10390</v>
+      </c>
+      <c r="F3" s="35">
+        <v>23273</v>
+      </c>
+      <c r="G3" s="36">
+        <v>5.1955122517784842</v>
+      </c>
+      <c r="H3" s="36">
+        <v>3.3439649318172311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>291</v>
       </c>
-      <c r="B3" s="39">
-        <v>2</v>
-      </c>
-      <c r="C3" s="39">
-        <v>2024</v>
-      </c>
-      <c r="D3" s="36">
-        <v>12883</v>
-      </c>
-      <c r="E3" s="36">
-        <v>10390</v>
-      </c>
-      <c r="F3" s="36">
-        <v>23273</v>
-      </c>
-      <c r="G3" s="37">
-        <v>5.1955122517784842</v>
-      </c>
-      <c r="H3" s="38">
-        <v>3.3439649318172311</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="35">
+        <v>16076</v>
+      </c>
+      <c r="E4" s="35">
+        <v>17411</v>
+      </c>
+      <c r="F4" s="35">
+        <v>33487</v>
+      </c>
+      <c r="G4" s="36">
+        <v>6.4831991740736559</v>
+      </c>
+      <c r="H4" s="36">
+        <v>5.6036355560991149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>292</v>
       </c>
-      <c r="B4" s="39">
-        <v>3</v>
-      </c>
-      <c r="C4" s="39">
-        <v>2024</v>
-      </c>
-      <c r="D4" s="36">
-        <v>16076</v>
-      </c>
-      <c r="E4" s="36">
-        <v>17411</v>
-      </c>
-      <c r="F4" s="36">
-        <v>33487</v>
-      </c>
-      <c r="G4" s="37">
-        <v>6.4831991740736559</v>
-      </c>
-      <c r="H4" s="38">
-        <v>5.6036355560991149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="35">
+        <v>19391</v>
+      </c>
+      <c r="E5" s="35">
+        <v>19604</v>
+      </c>
+      <c r="F5" s="35">
+        <v>38995</v>
+      </c>
+      <c r="G5" s="36">
+        <v>7.8200867867916308</v>
+      </c>
+      <c r="H5" s="36">
+        <v>6.3094406663469673</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>293</v>
       </c>
-      <c r="B5" s="39">
-        <v>4</v>
-      </c>
-      <c r="C5" s="39">
-        <v>2024</v>
-      </c>
-      <c r="D5" s="36">
-        <v>19391</v>
-      </c>
-      <c r="E5" s="36">
-        <v>19604</v>
-      </c>
-      <c r="F5" s="36">
-        <v>38995</v>
-      </c>
-      <c r="G5" s="37">
-        <v>7.8200867867916308</v>
-      </c>
-      <c r="H5" s="38">
-        <v>6.3094406663469673</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>2024</v>
+      </c>
+      <c r="D6" s="35">
+        <v>21886</v>
+      </c>
+      <c r="E6" s="35">
+        <v>22453</v>
+      </c>
+      <c r="F6" s="35">
+        <v>44339</v>
+      </c>
+      <c r="G6" s="36">
+        <v>8.8262812343727308</v>
+      </c>
+      <c r="H6" s="36">
+        <v>7.2263758050136948</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>294</v>
       </c>
-      <c r="B6" s="39">
-        <v>5</v>
-      </c>
-      <c r="C6" s="39">
-        <v>2024</v>
-      </c>
-      <c r="D6" s="36">
-        <v>21886</v>
-      </c>
-      <c r="E6" s="36">
-        <v>22453</v>
-      </c>
-      <c r="F6" s="36">
-        <v>44339</v>
-      </c>
-      <c r="G6" s="37">
-        <v>8.8262812343727308</v>
-      </c>
-      <c r="H6" s="38">
-        <v>7.2263758050136948</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>2024</v>
+      </c>
+      <c r="D7" s="35">
+        <v>23792</v>
+      </c>
+      <c r="E7" s="35">
+        <v>30465</v>
+      </c>
+      <c r="F7" s="35">
+        <v>54257</v>
+      </c>
+      <c r="G7" s="36">
+        <v>9.5949412011421007</v>
+      </c>
+      <c r="H7" s="36">
+        <v>9.804994383812506</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>295</v>
       </c>
-      <c r="B7" s="39">
-        <v>6</v>
-      </c>
-      <c r="C7" s="39">
-        <v>2024</v>
-      </c>
-      <c r="D7" s="36">
-        <v>23792</v>
-      </c>
-      <c r="E7" s="36">
-        <v>30465</v>
-      </c>
-      <c r="F7" s="36">
-        <v>54257</v>
-      </c>
-      <c r="G7" s="37">
-        <v>9.5949412011421007</v>
-      </c>
-      <c r="H7" s="38">
-        <v>9.804994383812506</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>2024</v>
+      </c>
+      <c r="D8" s="35">
+        <v>28131</v>
+      </c>
+      <c r="E8" s="35">
+        <v>56327</v>
+      </c>
+      <c r="F8" s="35">
+        <v>84458</v>
+      </c>
+      <c r="G8" s="36">
+        <v>11.344791985933442</v>
+      </c>
+      <c r="H8" s="36">
+        <v>18.128538278582209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>296</v>
       </c>
-      <c r="B8" s="39">
-        <v>7</v>
-      </c>
-      <c r="C8" s="39">
-        <v>2024</v>
-      </c>
-      <c r="D8" s="36">
-        <v>28131</v>
-      </c>
-      <c r="E8" s="36">
-        <v>56327</v>
-      </c>
-      <c r="F8" s="36">
-        <v>84458</v>
-      </c>
-      <c r="G8" s="37">
-        <v>11.344791985933442</v>
-      </c>
-      <c r="H8" s="38">
-        <v>18.128538278582209</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="35" t="s">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>2024</v>
+      </c>
+      <c r="D9" s="35">
+        <v>33332</v>
+      </c>
+      <c r="E9" s="35">
+        <v>68733</v>
+      </c>
+      <c r="F9" s="35">
+        <v>102065</v>
+      </c>
+      <c r="G9" s="36">
+        <v>13.44227387846623</v>
+      </c>
+      <c r="H9" s="36">
+        <v>22.121341834320859</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>297</v>
       </c>
-      <c r="B9" s="39">
-        <v>8</v>
-      </c>
-      <c r="C9" s="39">
-        <v>2024</v>
-      </c>
-      <c r="D9" s="36">
-        <v>33332</v>
-      </c>
-      <c r="E9" s="36">
-        <v>68733</v>
-      </c>
-      <c r="F9" s="36">
-        <v>102065</v>
-      </c>
-      <c r="G9" s="37">
-        <v>13.44227387846623</v>
-      </c>
-      <c r="H9" s="38">
-        <v>22.121341834320859</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="35" t="s">
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>2024</v>
+      </c>
+      <c r="D10" s="35">
+        <v>26236</v>
+      </c>
+      <c r="E10" s="35">
+        <v>35212</v>
+      </c>
+      <c r="F10" s="35">
+        <v>61448</v>
+      </c>
+      <c r="G10" s="36">
+        <v>10.580568146989078</v>
+      </c>
+      <c r="H10" s="36">
+        <v>11.332790488849696</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>298</v>
       </c>
-      <c r="B10" s="39">
-        <v>9</v>
-      </c>
-      <c r="C10" s="39">
-        <v>2024</v>
-      </c>
-      <c r="D10" s="36">
-        <v>26236</v>
-      </c>
-      <c r="E10" s="36">
-        <v>35212</v>
-      </c>
-      <c r="F10" s="36">
-        <v>61448</v>
-      </c>
-      <c r="G10" s="37">
-        <v>10.580568146989078</v>
-      </c>
-      <c r="H10" s="38">
-        <v>11.332790488849696</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>2024</v>
+      </c>
+      <c r="D11" s="35">
+        <v>26518</v>
+      </c>
+      <c r="E11" s="35">
+        <v>13838</v>
+      </c>
+      <c r="F11" s="35">
+        <v>40356</v>
+      </c>
+      <c r="G11" s="36">
+        <v>10.694294333048346</v>
+      </c>
+      <c r="H11" s="36">
+        <v>4.4536849592383874</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>299</v>
       </c>
-      <c r="B11" s="39">
-        <v>10</v>
-      </c>
-      <c r="C11" s="39">
-        <v>2024</v>
-      </c>
-      <c r="D11" s="36">
-        <v>26518</v>
-      </c>
-      <c r="E11" s="36">
-        <v>13838</v>
-      </c>
-      <c r="F11" s="36">
-        <v>40356</v>
-      </c>
-      <c r="G11" s="37">
-        <v>10.694294333048346</v>
-      </c>
-      <c r="H11" s="38">
-        <v>4.4536849592383874</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="35" t="s">
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>2024</v>
+      </c>
+      <c r="D12" s="35">
+        <v>14261</v>
+      </c>
+      <c r="E12" s="35">
+        <v>9723</v>
+      </c>
+      <c r="F12" s="35">
+        <v>23984</v>
+      </c>
+      <c r="G12" s="36">
+        <v>5.7512380829475243</v>
+      </c>
+      <c r="H12" s="36">
+        <v>3.1292946132876742</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>300</v>
       </c>
-      <c r="B12" s="39">
-        <v>11</v>
-      </c>
-      <c r="C12" s="39">
-        <v>2024</v>
-      </c>
-      <c r="D12" s="36">
-        <v>14261</v>
-      </c>
-      <c r="E12" s="36">
-        <v>9723</v>
-      </c>
-      <c r="F12" s="36">
-        <v>23984</v>
-      </c>
-      <c r="G12" s="37">
-        <v>5.7512380829475243</v>
-      </c>
-      <c r="H12" s="38">
-        <v>3.1292946132876742</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="B13" s="39">
+      <c r="B13">
         <v>12</v>
       </c>
-      <c r="C13" s="39">
-        <v>2024</v>
-      </c>
-      <c r="D13" s="36">
+      <c r="C13">
+        <v>2024</v>
+      </c>
+      <c r="D13" s="35">
         <v>11948</v>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="35">
         <v>14062</v>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="35">
         <v>26010</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <v>4.8184413866529017</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13" s="36">
         <v>4.5257781396741006</v>
       </c>
     </row>
     <row r="19" spans="9:21" x14ac:dyDescent="0.3">
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
-      <c r="S19" s="37"/>
-      <c r="T19" s="37"/>
-      <c r="U19" s="37"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
+      <c r="S19" s="36"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="36"/>
     </row>
     <row r="21" spans="9:21" x14ac:dyDescent="0.3">
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="38"/>
-      <c r="T21" s="38"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
+      <c r="S21" s="36"/>
+      <c r="T21" s="36"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -5778,8 +5794,7 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="39" customWidth="1"/>
+    <col min="1" max="2" width="23.44140625" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.77734375" bestFit="1" customWidth="1"/>
@@ -5789,230 +5804,230 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="40" t="s">
-        <v>328</v>
-      </c>
-      <c r="B1" s="40" t="s">
+      <c r="A1" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="D1" s="37" t="s">
         <v>304</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="E1" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="F1" s="37" t="s">
         <v>306</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="G1" s="37" t="s">
+        <v>315</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A2" s="37" t="s">
         <v>307</v>
       </c>
-      <c r="G1" s="40" t="s">
-        <v>316</v>
-      </c>
-      <c r="H1" s="40" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A2" s="40" t="s">
-        <v>308</v>
-      </c>
-      <c r="B2" s="40">
-        <v>2024</v>
-      </c>
-      <c r="C2" s="40">
+      <c r="B2" s="37">
+        <v>2024</v>
+      </c>
+      <c r="C2" s="37">
         <v>14</v>
       </c>
-      <c r="D2" s="40">
+      <c r="D2" s="37">
         <v>3863</v>
       </c>
-      <c r="E2" s="40">
+      <c r="E2" s="37">
         <v>1921</v>
       </c>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41">
+      <c r="F2" s="37"/>
+      <c r="G2" s="38">
         <f>(C2)/C$9</f>
         <v>2.6410111299754765E-3</v>
       </c>
-      <c r="H2" s="41">
+      <c r="H2" s="38">
         <f>D2/D$9</f>
         <v>0.1188067045978779</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A3" s="40" t="s">
-        <v>315</v>
-      </c>
-      <c r="B3" s="40">
-        <v>2024</v>
-      </c>
-      <c r="C3" s="40">
+      <c r="A3" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="B3" s="37">
+        <v>2024</v>
+      </c>
+      <c r="C3" s="37">
         <v>5</v>
       </c>
-      <c r="D3" s="40">
+      <c r="D3" s="37">
         <v>100</v>
       </c>
-      <c r="E3" s="40">
+      <c r="E3" s="37">
         <v>50</v>
       </c>
-      <c r="F3" s="40"/>
-      <c r="G3" s="41">
+      <c r="F3" s="37"/>
+      <c r="G3" s="38">
         <f t="shared" ref="G3:G8" si="0">(C3)/C$9</f>
         <v>9.4321826070552727E-4</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="38">
         <f t="shared" ref="H3:H9" si="1">D3/D$9</f>
         <v>3.0755036137167461E-3</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A4" s="40" t="s">
-        <v>309</v>
-      </c>
-      <c r="B4" s="40">
-        <v>2024</v>
-      </c>
-      <c r="C4" s="40">
+      <c r="A4" s="37" t="s">
+        <v>308</v>
+      </c>
+      <c r="B4" s="37">
+        <v>2024</v>
+      </c>
+      <c r="C4" s="37">
         <v>5267</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="37">
         <v>26304</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="41">
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="38">
         <f t="shared" si="0"/>
         <v>0.99358611582720247</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="38">
         <f t="shared" si="1"/>
         <v>0.80898047055205291</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A5" s="40" t="s">
-        <v>310</v>
-      </c>
-      <c r="B5" s="40">
-        <v>2024</v>
-      </c>
-      <c r="C5" s="40">
+      <c r="A5" s="37" t="s">
+        <v>309</v>
+      </c>
+      <c r="B5" s="37">
+        <v>2024</v>
+      </c>
+      <c r="C5" s="37">
         <v>7</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="37">
         <v>2130</v>
       </c>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40">
+      <c r="E5" s="37"/>
+      <c r="F5" s="37">
         <v>691</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="38">
         <f t="shared" si="0"/>
         <v>1.3205055649877383E-3</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="38">
         <f t="shared" si="1"/>
         <v>6.5508226972166697E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A6" s="40" t="s">
-        <v>311</v>
-      </c>
-      <c r="B6" s="40">
-        <v>2024</v>
-      </c>
-      <c r="C6" s="40">
+      <c r="A6" s="37" t="s">
+        <v>310</v>
+      </c>
+      <c r="B6" s="37">
+        <v>2024</v>
+      </c>
+      <c r="C6" s="37">
         <v>0</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="37">
         <v>0</v>
       </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="41">
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A7" s="40" t="s">
-        <v>312</v>
-      </c>
-      <c r="B7" s="40">
-        <v>2024</v>
-      </c>
-      <c r="C7" s="40">
+      <c r="A7" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="B7" s="37">
+        <v>2024</v>
+      </c>
+      <c r="C7" s="37">
         <v>0</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="37">
         <v>0</v>
       </c>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41">
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A8" s="40" t="s">
-        <v>313</v>
-      </c>
-      <c r="B8" s="40">
-        <v>2024</v>
-      </c>
-      <c r="C8" s="40">
+      <c r="A8" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="B8" s="37">
+        <v>2024</v>
+      </c>
+      <c r="C8" s="37">
         <v>8</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="37">
         <v>118</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="37">
         <v>60</v>
       </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41">
+      <c r="F8" s="37"/>
+      <c r="G8" s="38">
         <f t="shared" si="0"/>
         <v>1.5091492171288435E-3</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="38">
         <f t="shared" si="1"/>
         <v>3.6290942641857603E-3</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A9" s="42" t="s">
-        <v>314</v>
-      </c>
-      <c r="B9" s="40">
-        <v>2024</v>
-      </c>
-      <c r="C9" s="42">
+      <c r="A9" s="39" t="s">
+        <v>313</v>
+      </c>
+      <c r="B9" s="37">
+        <v>2024</v>
+      </c>
+      <c r="C9" s="39">
         <v>5301</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="39">
         <v>32515</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="39">
         <v>2031</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="39">
         <v>691</v>
       </c>
-      <c r="G9" s="43">
+      <c r="G9" s="40">
         <v>1</v>
       </c>
-      <c r="H9" s="44">
+      <c r="H9" s="41">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>

--- a/data/DB_Dashboard.xlsx
+++ b/data/DB_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmari\Desktop\Observatorio Calp\observatorio_calp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E54697-B080-4C1B-B2B8-7CC63FE6A5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454D9A31-421E-4B80-B3A6-2193DD68ED30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A3E3E45F-D34A-4772-8FFC-37BF922E3DDC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
     <author>tc={86248D9D-A426-4266-983B-342EA897A500}</author>
   </authors>
   <commentList>
-    <comment ref="M30" authorId="0" shapeId="0" xr:uid="{86248D9D-A426-4266-983B-342EA897A500}">
+    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{86248D9D-A426-4266-983B-342EA897A500}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="347">
   <si>
     <t>Año</t>
   </si>
@@ -1463,6 +1463,27 @@
   </si>
   <si>
     <t>ETIS - Residuos reciclados por residentes respecto al total</t>
+  </si>
+  <si>
+    <t>Número de turistas o visitantes extranjeros que visitaron Calp durante el último año.</t>
+  </si>
+  <si>
+    <t>Número de turistas o visitantes nacionales que visitaron Calp durante el último año.</t>
+  </si>
+  <si>
+    <t>WTO - Estacionalidad turística</t>
+  </si>
+  <si>
+    <t>Recuendo de turistas extranjero que visitaron Calp por mes.</t>
+  </si>
+  <si>
+    <t>Recuendo de turistas nacionales que visitaron Calp por mes.</t>
+  </si>
+  <si>
+    <t>Nº de turistas nacionales que visitaron Calp en el último año. Datos mensuales</t>
+  </si>
+  <si>
+    <t>Nº de turistas extranjeros que visitaron Calp en el último año. Datos mensuales</t>
   </si>
 </sst>
 </file>
@@ -1558,7 +1579,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1686,13 +1707,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1802,6 +1834,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1809,6 +1842,12 @@
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="35">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1982,12 +2021,6 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
@@ -2556,14 +2589,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{72A2E2F1-7CAD-4C76-BEFF-2442C0A18302}" name="Dashboard" displayName="Dashboard" ref="A1:O52" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31" totalsRowBorderDxfId="30">
-  <autoFilter ref="A1:O52" xr:uid="{72A2E2F1-7CAD-4C76-BEFF-2442C0A18302}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Gestión de residuos"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{72A2E2F1-7CAD-4C76-BEFF-2442C0A18302}" name="Dashboard" displayName="Dashboard" ref="A1:O53" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31" totalsRowBorderDxfId="30">
+  <autoFilter ref="A1:O53" xr:uid="{72A2E2F1-7CAD-4C76-BEFF-2442C0A18302}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{1793D8B9-1834-4672-94E2-370894E55593}" name="Año" dataDxfId="29"/>
     <tableColumn id="12" xr3:uid="{2FF65C8B-F0E1-459C-B72F-3A1A5329FDAB}" name="ETIS" dataDxfId="28"/>
@@ -2595,25 +2622,29 @@
     <tableColumn id="2" xr3:uid="{B343196D-F313-4338-A33E-C35CA22E1037}" name="1. Turistas extranjeros que visitaron Calp" dataDxfId="14"/>
     <tableColumn id="3" xr3:uid="{7694471A-5A27-4BAB-9627-5B49B697400E}" name="1. Turistas nacionales que visitaron Calp" dataDxfId="13"/>
     <tableColumn id="4" xr3:uid="{1BAEF350-378C-40C2-820B-759FCF4ED388}" name="1. Total turistas" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{A35DAE71-EE4A-4EC9-8460-F2F26963F5A2}" name="2.% Turistas extranjeros que visitaron Calp" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{77257F63-E741-45A0-A7C8-573D91BC35FA}" name="2. % Turistas nacionales que visitaron Calp" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{A35DAE71-EE4A-4EC9-8460-F2F26963F5A2}" name="2.% Turistas extranjeros que visitaron Calp" dataDxfId="0">
+      <calculatedColumnFormula>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{77257F63-E741-45A0-A7C8-573D91BC35FA}" name="2. % Turistas nacionales que visitaron Calp" dataDxfId="1">
+      <calculatedColumnFormula>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{32B811EC-84D2-45FC-891C-7E090EB6CBCD}" name="Alojamientos" displayName="Alojamientos" ref="A1:H9" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{32B811EC-84D2-45FC-891C-7E090EB6CBCD}" name="Alojamientos" displayName="Alojamientos" ref="A1:H9" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:H9" xr:uid="{32B811EC-84D2-45FC-891C-7E090EB6CBCD}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{07BCC607-7EEB-4361-B136-CCDA8E5F70BE}" name="Tipo" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{0871BF09-A2EB-42F4-86E2-C14CDB481EC8}" name="Año" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{B1AB5E11-B4CF-48BB-A35C-C459F9489AB4}" name="Establecimientos" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{ACC63EB1-5B06-4BEE-9E7E-B340C9BD2498}" name="Plazas" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{03DB75FF-9B48-49D9-9D17-D4363A5A9025}" name="Habitaciones" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{B55E2CBA-9D33-447F-AFD9-B5ED8123A040}" name="Parcelas" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{18A9F2D6-F247-4306-843D-3BC9A08F8F16}" name="% alojamientos" dataDxfId="1" dataCellStyle="Porcentaje"/>
-    <tableColumn id="7" xr3:uid="{0CA9FABA-AC27-4D35-A37F-5ADFC3A1E28A}" name="% plazas" dataDxfId="0" dataCellStyle="Porcentaje">
+    <tableColumn id="1" xr3:uid="{07BCC607-7EEB-4361-B136-CCDA8E5F70BE}" name="Tipo" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{0871BF09-A2EB-42F4-86E2-C14CDB481EC8}" name="Año" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{B1AB5E11-B4CF-48BB-A35C-C459F9489AB4}" name="Establecimientos" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{ACC63EB1-5B06-4BEE-9E7E-B340C9BD2498}" name="Plazas" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{03DB75FF-9B48-49D9-9D17-D4363A5A9025}" name="Habitaciones" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{B55E2CBA-9D33-447F-AFD9-B5ED8123A040}" name="Parcelas" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{18A9F2D6-F247-4306-843D-3BC9A08F8F16}" name="% alojamientos" dataDxfId="3" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{0CA9FABA-AC27-4D35-A37F-5ADFC3A1E28A}" name="% plazas" dataDxfId="2" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>D2/D$9</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2938,7 +2969,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="M30" dT="2025-12-11T16:46:50.50" personId="{AB9528B7-6643-4F77-B76C-533514F2F00F}" id="{86248D9D-A426-4266-983B-342EA897A500}">
+  <threadedComment ref="M31" dT="2025-12-11T16:46:50.50" personId="{AB9528B7-6643-4F77-B76C-533514F2F00F}" id="{86248D9D-A426-4266-983B-342EA897A500}">
     <text>Preguntar a Paula si tenim este dato</text>
   </threadedComment>
 </ThreadedComments>
@@ -2946,7 +2977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27BA13B8-EC56-4433-A73B-150D55368D4D}">
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="11.5546875" style="37"/>
@@ -3012,7 +3043,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" s="24">
         <v>2024</v>
       </c>
@@ -3059,7 +3090,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <v>2024</v>
       </c>
@@ -3104,7 +3135,7 @@
       </c>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <v>2024</v>
       </c>
@@ -3149,7 +3180,7 @@
       </c>
       <c r="O4" s="8"/>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
         <v>2024</v>
       </c>
@@ -3194,7 +3225,7 @@
       </c>
       <c r="O5" s="6"/>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <v>2024</v>
       </c>
@@ -3239,7 +3270,7 @@
       </c>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" s="24">
         <v>2024</v>
       </c>
@@ -3286,7 +3317,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8" s="24">
         <v>2024</v>
       </c>
@@ -3333,7 +3364,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9" s="24">
         <v>2024</v>
       </c>
@@ -3378,7 +3409,7 @@
       </c>
       <c r="O9" s="29"/>
     </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10" s="24">
         <v>2024</v>
       </c>
@@ -3423,7 +3454,7 @@
       </c>
       <c r="O10" s="29"/>
     </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11" s="24">
         <v>2024</v>
       </c>
@@ -3470,7 +3501,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A12" s="24">
         <v>2024</v>
       </c>
@@ -3517,7 +3548,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A13" s="24">
         <v>2024</v>
       </c>
@@ -3564,7 +3595,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14" s="24">
         <v>2024</v>
       </c>
@@ -3611,7 +3642,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15" s="24">
         <v>2024</v>
       </c>
@@ -3656,7 +3687,7 @@
       </c>
       <c r="O15" s="42"/>
     </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A16" s="24">
         <v>2024</v>
       </c>
@@ -3701,7 +3732,7 @@
       </c>
       <c r="O16" s="42"/>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A17" s="24">
         <v>2024</v>
       </c>
@@ -3746,153 +3777,153 @@
       </c>
       <c r="O17" s="42"/>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="18">
-        <v>2024</v>
-      </c>
-      <c r="B18" s="19" t="s">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A18" s="24">
+        <v>2024</v>
+      </c>
+      <c r="B18" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="26">
         <v>4</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="26" t="s">
+        <v>340</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>342</v>
+      </c>
+      <c r="H18" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="I18" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="J18" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L18" s="26" t="s">
+        <v>343</v>
+      </c>
+      <c r="M18" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="N18" s="32">
+        <v>247964</v>
+      </c>
+      <c r="O18" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="G18" s="20" t="s">
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A19" s="47">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="C19" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="26">
+        <v>4</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>341</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>342</v>
+      </c>
+      <c r="H19" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="I19" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="J19" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="K19" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" s="26" t="s">
+        <v>344</v>
+      </c>
+      <c r="M19" s="26" t="s">
+        <v>345</v>
+      </c>
+      <c r="N19" s="32">
+        <v>310709</v>
+      </c>
+      <c r="O19" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="I18" s="20" t="s">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A20" s="5">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="7">
+        <v>5</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="N20" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="J18" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="K18" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="L18" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="M18" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N18" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="O18" s="23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="5">
-        <v>2024</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="7">
-        <v>5</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="O19" s="8" t="s">
+      <c r="O20" s="8" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B20" s="25" t="s">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A21" s="24">
+        <v>2024</v>
+      </c>
+      <c r="B21" s="25" t="s">
         <v>139</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="26">
-        <v>6</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="G20" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="H20" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="I20" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="J20" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="K20" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L20" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="M20" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="N20" s="28">
-        <v>68.89</v>
-      </c>
-      <c r="O20" s="29" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="18" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>148</v>
       </c>
       <c r="C21" s="26" t="s">
         <v>20</v>
@@ -3904,42 +3935,42 @@
         <v>25</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G21" s="26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="I21" s="26" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="J21" s="26" t="s">
-        <v>11</v>
+        <v>143</v>
       </c>
       <c r="K21" s="27" t="s">
-        <v>154</v>
+        <v>12</v>
       </c>
       <c r="L21" s="26" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="M21" s="26" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="N21" s="28">
-        <v>6.59</v>
+        <v>68.89</v>
       </c>
       <c r="O21" s="29" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="18" hidden="1" x14ac:dyDescent="0.4">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="18" x14ac:dyDescent="0.4">
       <c r="A22" s="24">
         <v>2024</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C22" s="26" t="s">
         <v>20</v>
@@ -3969,24 +4000,24 @@
         <v>154</v>
       </c>
       <c r="L22" s="26" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M22" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N22" s="28">
-        <v>12.02</v>
+        <v>6.59</v>
       </c>
       <c r="O22" s="29" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="18" hidden="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:15" ht="18" x14ac:dyDescent="0.4">
       <c r="A23" s="24">
         <v>2024</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C23" s="26" t="s">
         <v>20</v>
@@ -4016,63 +4047,63 @@
         <v>154</v>
       </c>
       <c r="L23" s="26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M23" s="26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N23" s="28">
-        <v>9.56</v>
+        <v>12.02</v>
       </c>
       <c r="O23" s="29" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:15" ht="18" x14ac:dyDescent="0.4">
       <c r="A24" s="24">
         <v>2024</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>48</v>
+        <v>146</v>
       </c>
       <c r="C24" s="26" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="J24" s="26" t="s">
         <v>11</v>
       </c>
       <c r="K24" s="27" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="L24" s="26" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="M24" s="26" t="s">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="N24" s="28">
-        <v>36.78</v>
+        <v>9.56</v>
       </c>
       <c r="O24" s="29" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.4">
@@ -4080,7 +4111,7 @@
         <v>2024</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" s="26" t="s">
         <v>20</v>
@@ -4095,7 +4126,7 @@
         <v>37</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H25" s="26" t="s">
         <v>38</v>
@@ -4110,13 +4141,13 @@
         <v>41</v>
       </c>
       <c r="L25" s="26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M25" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N25" s="28">
-        <v>34.18</v>
+        <v>36.78</v>
       </c>
       <c r="O25" s="29" t="s">
         <v>54</v>
@@ -4127,7 +4158,7 @@
         <v>2024</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="C26" s="26" t="s">
         <v>20</v>
@@ -4139,10 +4170,10 @@
         <v>18</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H26" s="26" t="s">
         <v>38</v>
@@ -4154,19 +4185,19 @@
         <v>11</v>
       </c>
       <c r="K26" s="27" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="L26" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M26" s="26" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="N26" s="28">
-        <v>50.85</v>
+        <v>34.18</v>
       </c>
       <c r="O26" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.4">
@@ -4174,7 +4205,7 @@
         <v>2024</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C27" s="26" t="s">
         <v>20</v>
@@ -4185,11 +4216,11 @@
       <c r="E27" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="46" t="s">
-        <v>336</v>
+      <c r="F27" s="26" t="s">
+        <v>42</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>339</v>
+        <v>199</v>
       </c>
       <c r="H27" s="26" t="s">
         <v>38</v>
@@ -4201,19 +4232,19 @@
         <v>11</v>
       </c>
       <c r="K27" s="27" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="L27" s="26" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M27" s="26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N27" s="28">
-        <v>2.1</v>
+        <v>50.85</v>
       </c>
       <c r="O27" s="29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.4">
@@ -4221,7 +4252,7 @@
         <v>2024</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C28" s="26" t="s">
         <v>20</v>
@@ -4232,11 +4263,11 @@
       <c r="E28" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="26" t="s">
-        <v>337</v>
+      <c r="F28" s="46" t="s">
+        <v>336</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H28" s="26" t="s">
         <v>38</v>
@@ -4251,66 +4282,66 @@
         <v>43</v>
       </c>
       <c r="L28" s="26" t="s">
-        <v>335</v>
+        <v>49</v>
       </c>
       <c r="M28" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N28" s="28">
-        <v>4.8899999999999997</v>
+        <v>2.1</v>
       </c>
       <c r="O28" s="29" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="18" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="5">
-        <v>2024</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" s="7" t="s">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A29" s="24">
+        <v>2024</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="7">
-        <v>8</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="J29" s="7" t="s">
+      <c r="D29" s="26">
+        <v>7</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>337</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>338</v>
+      </c>
+      <c r="H29" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="I29" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="J29" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K29" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="M29" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="O29" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+      <c r="K29" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="L29" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="M29" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="28">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="O29" s="29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="18" x14ac:dyDescent="0.4">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -4327,7 +4358,7 @@
         <v>26</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>261</v>
@@ -4342,22 +4373,22 @@
         <v>11</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>17</v>
+        <v>262</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="N30" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="O30" s="6" t="s">
+      <c r="O30" s="8" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A31" s="5">
         <v>2024</v>
       </c>
@@ -4374,7 +4405,7 @@
         <v>26</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>261</v>
@@ -4383,28 +4414,28 @@
         <v>64</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="J31" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="K31" s="8" t="s">
-        <v>272</v>
+      <c r="K31" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="N31" s="9" t="s">
         <v>123</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A32" s="5">
         <v>2024</v>
       </c>
@@ -4421,7 +4452,7 @@
         <v>26</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>261</v>
@@ -4430,101 +4461,101 @@
         <v>64</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>231</v>
+        <v>271</v>
       </c>
       <c r="J32" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="K32" s="10" t="s">
-        <v>123</v>
+      <c r="K32" s="8" t="s">
+        <v>272</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="N32" s="9" t="s">
         <v>123</v>
       </c>
       <c r="O32" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A33" s="5">
+        <v>2024</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="7">
+        <v>8</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="O33" s="6" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B33" s="25" t="s">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A34" s="24">
+        <v>2024</v>
+      </c>
+      <c r="B34" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C34" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D34" s="26">
         <v>9</v>
       </c>
-      <c r="E33" s="26" t="s">
+      <c r="E34" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="F33" s="26" t="s">
+      <c r="F34" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="G33" s="26" t="s">
+      <c r="G34" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="H33" s="26" t="s">
+      <c r="H34" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="I33" s="26" t="s">
+      <c r="I34" s="26" t="s">
         <v>182</v>
-      </c>
-      <c r="J33" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K33" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L33" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="M33" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="N33" s="30">
-        <v>45</v>
-      </c>
-      <c r="O33" s="29" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B34" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" s="26">
-        <v>10</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="G34" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="H34" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I34" s="26" t="s">
-        <v>166</v>
       </c>
       <c r="J34" s="26" t="s">
         <v>11</v>
@@ -4533,24 +4564,24 @@
         <v>12</v>
       </c>
       <c r="L34" s="26" t="s">
-        <v>167</v>
+        <v>253</v>
       </c>
       <c r="M34" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="N34" s="28">
-        <v>82.11</v>
+        <v>254</v>
+      </c>
+      <c r="N34" s="30">
+        <v>45</v>
       </c>
       <c r="O34" s="29" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A35" s="24">
         <v>2024</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C35" s="26" t="s">
         <v>28</v>
@@ -4562,7 +4593,7 @@
         <v>29</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G35" s="26" t="s">
         <v>198</v>
@@ -4580,66 +4611,66 @@
         <v>12</v>
       </c>
       <c r="L35" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="M35" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="N35" s="28">
+        <v>82.11</v>
+      </c>
+      <c r="O35" s="29" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A36" s="24">
+        <v>2024</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="26">
+        <v>10</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G36" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="H36" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="I36" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="J36" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="K36" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="L36" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="M35" s="26" t="s">
+      <c r="M36" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="N35" s="28">
+      <c r="N36" s="28">
         <v>17.89</v>
       </c>
-      <c r="O35" s="29" t="s">
+      <c r="O36" s="29" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="18">
-        <v>2024</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="20">
-        <v>11</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="G36" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H36" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="I36" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="J36" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="K36" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="L36" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="M36" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N36" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="O36" s="23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A37" s="18">
         <v>2024</v>
       </c>
@@ -4650,10 +4681,10 @@
         <v>28</v>
       </c>
       <c r="D37" s="20">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F37" s="20" t="s">
         <v>123</v>
@@ -4686,59 +4717,59 @@
         <v>123</v>
       </c>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B38" s="25" t="s">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A38" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="20">
+        <v>12</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="I38" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K38" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M38" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N38" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="O38" s="23" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A39" s="24">
+        <v>2024</v>
+      </c>
+      <c r="B39" s="25" t="s">
         <v>86</v>
-      </c>
-      <c r="C38" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="26">
-        <v>13</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="F38" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="G38" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="H38" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="I38" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="J38" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K38" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="L38" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="M38" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="N38" s="28">
-        <v>49.16</v>
-      </c>
-      <c r="O38" s="29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B39" s="25" t="s">
-        <v>100</v>
       </c>
       <c r="C39" s="26" t="s">
         <v>28</v>
@@ -4750,42 +4781,42 @@
         <v>30</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G39" s="26" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I39" s="26" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="J39" s="26" t="s">
         <v>11</v>
       </c>
       <c r="K39" s="27" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="L39" s="26" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M39" s="26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N39" s="28">
-        <v>37.65</v>
-      </c>
-      <c r="O39" s="43" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+        <v>49.16</v>
+      </c>
+      <c r="O39" s="29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A40" s="24">
         <v>2024</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C40" s="26" t="s">
         <v>28</v>
@@ -4797,7 +4828,7 @@
         <v>30</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G40" s="26" t="s">
         <v>197</v>
@@ -4815,24 +4846,24 @@
         <v>12</v>
       </c>
       <c r="L40" s="26" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="M40" s="26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N40" s="28">
-        <v>32.590000000000003</v>
+        <v>37.65</v>
       </c>
       <c r="O40" s="43" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A41" s="24">
         <v>2024</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C41" s="26" t="s">
         <v>28</v>
@@ -4844,16 +4875,16 @@
         <v>30</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G41" s="26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="I41" s="26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J41" s="26" t="s">
         <v>11</v>
@@ -4862,45 +4893,45 @@
         <v>12</v>
       </c>
       <c r="L41" s="26" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="M41" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="N41" s="30">
-        <v>70</v>
-      </c>
-      <c r="O41" s="31" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+        <v>109</v>
+      </c>
+      <c r="N41" s="28">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="O41" s="43" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A42" s="24">
         <v>2024</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>225</v>
+        <v>102</v>
       </c>
       <c r="C42" s="26" t="s">
         <v>28</v>
       </c>
       <c r="D42" s="26">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>193</v>
+        <v>103</v>
       </c>
       <c r="G42" s="26" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="H42" s="26" t="s">
-        <v>181</v>
+        <v>104</v>
       </c>
       <c r="I42" s="26" t="s">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="J42" s="26" t="s">
         <v>11</v>
@@ -4909,45 +4940,45 @@
         <v>12</v>
       </c>
       <c r="L42" s="26" t="s">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="M42" s="26" t="s">
-        <v>229</v>
+        <v>108</v>
       </c>
       <c r="N42" s="30">
-        <v>18</v>
-      </c>
-      <c r="O42" s="29" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+      <c r="O42" s="31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A43" s="24">
         <v>2024</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C43" s="26" t="s">
         <v>28</v>
       </c>
       <c r="D43" s="26">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="G43" s="26" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>64</v>
+        <v>181</v>
       </c>
       <c r="I43" s="26" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="J43" s="26" t="s">
         <v>11</v>
@@ -4956,24 +4987,24 @@
         <v>12</v>
       </c>
       <c r="L43" s="26" t="s">
-        <v>121</v>
+        <v>192</v>
       </c>
       <c r="M43" s="26" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="N43" s="30">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="O43" s="29" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A44" s="24">
         <v>2024</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C44" s="26" t="s">
         <v>28</v>
@@ -4985,7 +5016,7 @@
         <v>32</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>195</v>
@@ -5006,21 +5037,21 @@
         <v>121</v>
       </c>
       <c r="M44" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N44" s="30">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="O44" s="29" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A45" s="24">
         <v>2024</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>119</v>
+        <v>219</v>
       </c>
       <c r="C45" s="26" t="s">
         <v>28</v>
@@ -5032,7 +5063,7 @@
         <v>32</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>132</v>
+        <v>222</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>195</v>
@@ -5047,25 +5078,27 @@
         <v>11</v>
       </c>
       <c r="K45" s="27" t="s">
-        <v>122</v>
+        <v>12</v>
       </c>
       <c r="L45" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="M45" s="26"/>
-      <c r="N45" s="32">
-        <v>737000000</v>
+        <v>121</v>
+      </c>
+      <c r="M45" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="N45" s="30">
+        <v>6</v>
       </c>
       <c r="O45" s="29" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A46" s="24">
         <v>2024</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C46" s="26" t="s">
         <v>28</v>
@@ -5077,7 +5110,7 @@
         <v>32</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G46" s="26" t="s">
         <v>195</v>
@@ -5095,24 +5128,22 @@
         <v>122</v>
       </c>
       <c r="L46" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="M46" s="26" t="s">
-        <v>130</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="M46" s="26"/>
       <c r="N46" s="32">
-        <v>575000000</v>
+        <v>737000000</v>
       </c>
       <c r="O46" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A47" s="24">
         <v>2024</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C47" s="26" t="s">
         <v>28</v>
@@ -5124,7 +5155,7 @@
         <v>32</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G47" s="26" t="s">
         <v>195</v>
@@ -5142,66 +5173,66 @@
         <v>122</v>
       </c>
       <c r="L47" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M47" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N47" s="32">
-        <v>162000000</v>
+        <v>575000000</v>
       </c>
       <c r="O47" s="29" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="16.8" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="5">
-        <v>2024</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C48" s="7" t="s">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A48" s="24">
+        <v>2024</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D48" s="7">
-        <v>16</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="J48" s="7" t="s">
+      <c r="D48" s="26">
+        <v>15</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="G48" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="H48" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="I48" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="J48" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K48" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="L48" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="M48" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="N48" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="O48" s="8" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="16.8" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K48" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="L48" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="M48" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="N48" s="32">
+        <v>162000000</v>
+      </c>
+      <c r="O48" s="29" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="5">
         <v>2024</v>
       </c>
@@ -5218,7 +5249,7 @@
         <v>33</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>241</v>
@@ -5233,118 +5264,118 @@
         <v>11</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="L49" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M49" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="N49" s="9"/>
+      <c r="N49" s="9" t="s">
+        <v>123</v>
+      </c>
       <c r="O49" s="8" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B50" s="25" t="s">
+    <row r="50" spans="1:15" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="5">
+        <v>2024</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" s="7">
+        <v>16</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K50" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L50" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="M50" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="N50" s="9"/>
+      <c r="O50" s="8" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A51" s="24">
+        <v>2024</v>
+      </c>
+      <c r="B51" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="C50" s="26" t="s">
+      <c r="C51" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D50" s="26">
+      <c r="D51" s="26">
         <v>17</v>
       </c>
-      <c r="E50" s="26" t="s">
+      <c r="E51" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="F50" s="26" t="s">
+      <c r="F51" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="G50" s="26" t="s">
+      <c r="G51" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="H50" s="26" t="s">
+      <c r="H51" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="I50" s="26" t="s">
+      <c r="I51" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="J50" s="26" t="s">
+      <c r="J51" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K50" s="27" t="s">
+      <c r="K51" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="L50" s="26" t="s">
+      <c r="L51" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="M50" s="26" t="s">
+      <c r="M51" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="N50" s="30">
+      <c r="N51" s="30">
         <v>9</v>
       </c>
-      <c r="O50" s="29" t="s">
+      <c r="O51" s="29" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="5">
-        <v>2024</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D51" s="7">
-        <v>18</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K51" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L51" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="M51" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="N51" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="O51" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="13">
-        <v>2024</v>
-      </c>
-      <c r="B52" s="14" t="s">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A52" s="5">
+        <v>2024</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>123</v>
       </c>
       <c r="C52" s="7" t="s">
@@ -5356,8 +5387,8 @@
       <c r="E52" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F52" s="15" t="s">
-        <v>267</v>
+      <c r="F52" s="7" t="s">
+        <v>256</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>241</v>
@@ -5374,16 +5405,63 @@
       <c r="K52" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L52" s="15" t="s">
+      <c r="L52" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="M52" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="N52" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="O52" s="8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A53" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="7">
+        <v>18</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L53" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="M52" s="15" t="s">
+      <c r="M53" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="N52" s="16" t="s">
+      <c r="N53" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="O52" s="8" t="s">
+      <c r="O53" s="8" t="s">
         <v>259</v>
       </c>
     </row>
@@ -5391,7 +5469,7 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="O13" r:id="rId1" display="https://www.seg-social.es/wps/portal/wss/internet/EstadisticasPresupuestosEstudios/Estadisticas/EST8/EST10/EST305/c43ad8ea-fe79-4329-ac8e-e5758f3c4d7a/f83fe4aa-2dee-49c5-8317-98d105813796" xr:uid="{61128FB4-53B2-4EAF-8DD6-669E31DEF896}"/>
-    <hyperlink ref="O40" r:id="rId2" display="https://www.seg-social.es/wps/portal/wss/internet/EstadisticasPresupuestosEstudios/Estadisticas/EST8/EST10/EST305/c43ad8ea-fe79-4329-ac8e-e5758f3c4d7a/f83fe4aa-2dee-49c5-8317-98d105813796" xr:uid="{AAB67715-CF03-4157-B01F-134351755964}"/>
+    <hyperlink ref="O41" r:id="rId2" display="https://www.seg-social.es/wps/portal/wss/internet/EstadisticasPresupuestosEstudios/Estadisticas/EST8/EST10/EST305/c43ad8ea-fe79-4329-ac8e-e5758f3c4d7a/f83fe4aa-2dee-49c5-8317-98d105813796" xr:uid="{AAB67715-CF03-4157-B01F-134351755964}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -5460,10 +5538,12 @@
         <v>26001</v>
       </c>
       <c r="G2" s="36">
-        <v>5.4483715378038751</v>
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.5195954001769163</v>
       </c>
       <c r="H2" s="36">
-        <v>4.0201603429575581</v>
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.4804045998230837</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5486,10 +5566,12 @@
         <v>23273</v>
       </c>
       <c r="G3" s="36">
-        <v>5.1955122517784842</v>
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.55355991921969661</v>
       </c>
       <c r="H3" s="36">
-        <v>3.3439649318172311</v>
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.44644008078030334</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -5512,10 +5594,12 @@
         <v>33487</v>
       </c>
       <c r="G4" s="36">
-        <v>6.4831991740736559</v>
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.4800668916295876</v>
       </c>
       <c r="H4" s="36">
-        <v>5.6036355560991149</v>
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.5199331083704124</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -5538,10 +5622,12 @@
         <v>38995</v>
       </c>
       <c r="G5" s="36">
-        <v>7.8200867867916308</v>
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.49726888062572122</v>
       </c>
       <c r="H5" s="36">
-        <v>6.3094406663469673</v>
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.50273111937427872</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -5564,10 +5650,12 @@
         <v>44339</v>
       </c>
       <c r="G6" s="36">
-        <v>8.8262812343727308</v>
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.49360608042581022</v>
       </c>
       <c r="H6" s="36">
-        <v>7.2263758050136948</v>
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.50639391957418978</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -5590,10 +5678,12 @@
         <v>54257</v>
       </c>
       <c r="G7" s="36">
-        <v>9.5949412011421007</v>
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.43850563060987524</v>
       </c>
       <c r="H7" s="36">
-        <v>9.804994383812506</v>
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.56149436939012476</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -5616,10 +5706,12 @@
         <v>84458</v>
       </c>
       <c r="G8" s="36">
-        <v>11.344791985933442</v>
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.33307679556702741</v>
       </c>
       <c r="H8" s="36">
-        <v>18.128538278582209</v>
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.66692320443297259</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -5642,10 +5734,12 @@
         <v>102065</v>
       </c>
       <c r="G9" s="36">
-        <v>13.44227387846623</v>
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.32657620144025867</v>
       </c>
       <c r="H9" s="36">
-        <v>22.121341834320859</v>
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.67342379855974133</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -5668,10 +5762,12 @@
         <v>61448</v>
       </c>
       <c r="G10" s="36">
-        <v>10.580568146989078</v>
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.42696263507355814</v>
       </c>
       <c r="H10" s="36">
-        <v>11.332790488849696</v>
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.57303736492644186</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -5694,10 +5790,12 @@
         <v>40356</v>
       </c>
       <c r="G11" s="36">
-        <v>10.694294333048346</v>
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.65710179403310531</v>
       </c>
       <c r="H11" s="36">
-        <v>4.4536849592383874</v>
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.34289820596689463</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -5720,10 +5818,12 @@
         <v>23984</v>
       </c>
       <c r="G12" s="36">
-        <v>5.7512380829475243</v>
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.59460473649099399</v>
       </c>
       <c r="H12" s="36">
-        <v>3.1292946132876742</v>
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.40539526350900601</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -5746,10 +5846,12 @@
         <v>26010</v>
       </c>
       <c r="G13" s="36">
-        <v>4.8184413866529017</v>
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.45936178392925797</v>
       </c>
       <c r="H13" s="36">
-        <v>4.5257781396741006</v>
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
+        <v>0.54063821607074203</v>
       </c>
     </row>
     <row r="19" spans="9:21" x14ac:dyDescent="0.3">

--- a/data/DB_Dashboard.xlsx
+++ b/data/DB_Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmari\Desktop\Observatorio Calp\observatorio_calp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454D9A31-421E-4B80-B3A6-2193DD68ED30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3B65B2-054B-40C5-B3D6-725C58CAFD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A3E3E45F-D34A-4772-8FFC-37BF922E3DDC}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{A3E3E45F-D34A-4772-8FFC-37BF922E3DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,18 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={86248D9D-A426-4266-983B-342EA897A500}</author>
+    <author>tc={C1CEE11B-07A1-41EC-931F-B2E17012E67A}</author>
   </authors>
   <commentList>
-    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{86248D9D-A426-4266-983B-342EA897A500}">
+    <comment ref="M30" authorId="0" shapeId="0" xr:uid="{86248D9D-A426-4266-983B-342EA897A500}">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Preguntar a Paula si tenim este dato</t>
+      </text>
+    </comment>
+    <comment ref="M78" authorId="1" shapeId="0" xr:uid="{C1CEE11B-07A1-41EC-931F-B2E17012E67A}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -56,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="343">
   <si>
     <t>Año</t>
   </si>
@@ -141,9 +150,6 @@
     <t>Acción por el clima</t>
   </si>
   <si>
-    <t>Accesibilidad</t>
-  </si>
-  <si>
     <t>Adicionales</t>
   </si>
   <si>
@@ -157,9 +163,6 @@
   </si>
   <si>
     <t>Reducción del impacto generado por el transporte</t>
-  </si>
-  <si>
-    <t>Eventos sostenibles</t>
   </si>
   <si>
     <t>Protección del paisaje y biodiversidad</t>
@@ -253,9 +256,6 @@
     <t>A.1.1</t>
   </si>
   <si>
-    <t>Lista de empresas certificadas/etiquetadas, lista de todas las empresas de turismo registradas</t>
-  </si>
-  <si>
     <t>Empresas turísticas</t>
   </si>
   <si>
@@ -267,9 +267,6 @@
   <si>
     <t>Nº empresas certificadas
 Nº total de empresas destinadas al sector turístico</t>
-  </si>
-  <si>
-    <t>3 empresas certificadas en S, EMAS; 261 actividades de hostelería y transporte</t>
   </si>
   <si>
     <t>B.1.1</t>
@@ -1024,44 +1021,7 @@
     <t>Comisión interdepartamental y Consejo de Turismo</t>
   </si>
   <si>
-    <t>Identificar canales y vías destinadas a la promoción del turísmo sostenible (redes sociales, canales de Youtube, páginas web, newsletter, plataformas de reservas online, Blogs, etc.)</t>
-  </si>
-  <si>
-    <t>Tipo de vías/canales utilizados para promover el turismo sostenible.</t>
-  </si>
-  <si>
-    <t>Número de vías/canales utilizados para promover el turismo sostenible.</t>
-  </si>
-  <si>
-    <t>Canales y vías destinadas a la promoción del turísmo sostenible (redes sociales, canales de Youtube, páginas web, newsletter, plataformas de reservas online, Blogs, etc.)</t>
-  </si>
-  <si>
-    <t>Tipo de vías/canales de comunicación utilizados para promover el turismo sostenible en Calp.</t>
-  </si>
-  <si>
-    <t>Número de vías/canales de comunicación utilizados para promover el turismo sostenible en Calp.</t>
-  </si>
-  <si>
     <t>Diferenciar entre los tipos de canales</t>
-  </si>
-  <si>
-    <t>Porcentaje de habitaciones del alojamiento accesibles para personas con discapacidad o movilidad reducida</t>
-  </si>
-  <si>
-    <t>WTO - Accesibilidad</t>
-  </si>
-  <si>
-    <t>Consejo de Turismo</t>
-  </si>
-  <si>
-    <t>Número total de infraestructuras de los agentes turísticos accesibles para personas con discapacidad  ÷ Número total de respuestas en la encuesta de agentes turísticos = % de infraestructuras accesibles para personas con discapacidad</t>
-  </si>
-  <si>
-    <t>Nº de agentes turísticos que cuentan con habitaciones o instalaciones accesibles
-Nº total de respuestas al cuestionario</t>
-  </si>
-  <si>
-    <t>Encuesta a los agentes turísticos</t>
   </si>
   <si>
     <t>Porcentaje de turistas conscientes de la importancia del sitio de conservación</t>
@@ -1228,37 +1188,7 @@
     <t>Calcular a partir de los datos de Mabrian</t>
   </si>
   <si>
-    <t>Nivel de daños ocasionados por eventos climáticos extremos en el sector turístico (inundación costera, ola de calor que provoca cierres de actividades turísticas, vertidos por tormenta, etc.).</t>
-  </si>
-  <si>
-    <t>Frecuencia de eventos extremos climáticos.
-Valor (€) de los daños ocasionados por eventos extremos climáticos en el sector turístico (facturas o presupuestos de reparaciones).
-Promedio de eventos extremos en los últimos 5 años. Establecer umbrales tipo:
--Bajo: &lt; 3 eventos al año
--Medio: 3-4 eventos al año
--Alto: &gt; 5 eventos al año
-Promedio de daños ocasionados por eventos extremos en los últimos 5 años. Establecer umbrales tipo:
--Bajo impacto: &lt; X €
--Medio impacto: X-X €
--Alto impacto: &gt;X €</t>
-  </si>
-  <si>
-    <t>Frecuencia = Nº de eventos extremos al año o por temporada.
-Daño medio anual = Coste total de la reparaciones (€) ÷ Nº de eventos ocurridos al año
-Umbral de impacto = Comparación nº eventos extremos anual respecto al promedio de eventos en los últimos 5 años.
-Umbral daños ocasionados = Comparación daños anual respecto al promedio de daños en los últimos 5 años.</t>
-  </si>
-  <si>
-    <t>Se puede sacar varios subindicadores</t>
-  </si>
-  <si>
-    <t>Porcentaje de material/documentos que estén a disposición de la lengua materna de los Stakeholders (partes interesadas)</t>
-  </si>
-  <si>
     <t>WTO - Bienes culturales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de documentos en valenciano ÷ Número de documentos en castellano = % en lengua materna </t>
   </si>
   <si>
     <t>Nº total de veces que se ha cerrado el baño durante el año.
@@ -1266,25 +1196,6 @@
 Número de veces que se ha cerrado el baño en la temporada de baño (verano) 
 % de días cerrado = Número de días de cierre en temporada de baño ÷ Número de días totales que dura la temporada de baño x 100
 Se pueden sacar varios subindicadores</t>
-  </si>
-  <si>
-    <t>Nº de documentos o materiales disponibles en la lengua materna de las partes interesadas (valenciano).
-Nº de documentos o materiales disponibles en castellano para las partes interesadas.</t>
-  </si>
-  <si>
-    <t>% / Importe de fondos asignados anualmente a la restauración, prevención y mantenimiento de bienes culturales (diferenciando según las diferentes fuentes de financiación, com tarifas de entrada por visitante (tickets), tarifas de operadores turísticos, donaciones, fondos gubernamentales, fundaciones privadas, instituciones financieras y de desarrollo internacionales, OMG, etc.</t>
-  </si>
-  <si>
-    <t>% de fondos destinados a la preservación y mantenimiento de bienes culturales.</t>
-  </si>
-  <si>
-    <t>Identificar y separar los fondos según su origen:
--Tickets/entradas de visitantes.
--Tarifas de operadores turísticos (comisiones).
--Donaciones privadas.
--Fondos gubernamentales.
--Fundaciones privadas.
--ONG's</t>
   </si>
   <si>
     <t>id</t>
@@ -1485,16 +1396,96 @@
   <si>
     <t>Nº de turistas extranjeros que visitaron Calp en el último año. Datos mensuales</t>
   </si>
+  <si>
+    <t>Tourist Info; Empresa de recogida de residuos (en caso de incluir campañas de educación ambiental en el contrato); Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Número de campañas de educación ambiental realizadas al año (en colegios, residencias, actos públicos, etc.)</t>
+  </si>
+  <si>
+    <t>Número de campañas de edicación ambiental/charlas/formaciones realizadas en Calp.</t>
+  </si>
+  <si>
+    <t>Se considerarán campañas de educación ambiental aquellas acciones organizadas o coorganizadas por la entidad que tengan como objetivo sensibilizar o formar en materia ambiental (gestión de residuos, economía circular, eficiencia energética, reducción del desperdicio, etc.), incluyendo:
+- Charlas informativas
+- Talleres prácticos
+- Jornadas o seminarios
+- Campañas de comunicación (cartelería, RRSS, mailing)
+- Acciones con escolares o asociaciones
+- Formación interna al personal</t>
+  </si>
+  <si>
+    <t>Ayuntamiento/Tourist Info</t>
+  </si>
+  <si>
+    <t>Porcentaje de folletos/material informativo que estén a disposición de la lengua materna de los ciudadanos (valenciano)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Número de folletos/material informativo en valenciano ÷ Número de folletos/material informativo en castellano = % en lengua materna </t>
+  </si>
+  <si>
+    <t>Nº de folletos o material informativo disponibles en la lengua materna de la ciudadania (valenciano).
+Nº de folletos o material informativo disponibles en castellano para la ciudadanía.</t>
+  </si>
+  <si>
+    <t>WTO - Rendimiento empresarial turístico</t>
+  </si>
+  <si>
+    <t>Actas de reuniones comunitarias, y encuestas a los agentes turísticos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pernoctaciones totales anuales (Mabrian)
+Gasto medio diario (EGATUR o Red DTI)
+</t>
+  </si>
+  <si>
+    <t>Gasto turístico medio diario x Número tde pernoctaciones turistas anuales = Ingreso generado por el turismo en el destino</t>
+  </si>
+  <si>
+    <t>Ingreso estimado generado por el turismo en el destino. Mide la capacidad del destino para generar ingresos por cada visitante recibido, como indicador básico del rendimiento económico del sector turístico.</t>
+  </si>
+  <si>
+    <t>Porcentaje de empresas que declara comprar a proveedores locales</t>
+  </si>
+  <si>
+    <t>WTO - Cadena de suministros</t>
+  </si>
+  <si>
+    <t>Mabrian, Red DTI C. Valenciana</t>
+  </si>
+  <si>
+    <t>Nº de empresas que declaran comprar a proveedores locales / Nº total de empresas encuestadas x 100 = % de empresas que declara comprar a proveedores locales</t>
+  </si>
+  <si>
+    <t>Nº total de empresas turísticas encuestadas
+Nº de empresas que indiquen que:
+- Compran alimentos locales
+- Contratan servicios locales
+- Trabajan con proveedores del municipio/comarca</t>
+  </si>
+  <si>
+    <t>https://smarttourismcv.invattur.org/api/visualizaciones-genericas/comportamiento-del-turismo/turismo-internacional</t>
+  </si>
+  <si>
+    <t>3 empresas certificadas en S, EMAS y 1 en SICTED; 261 actividades de hostelería y transporte</t>
+  </si>
+  <si>
+    <t>Consumo de agua por cada pernoctación de un turista internacional en comparación con el consumo de agua por cada noche de un residente</t>
+  </si>
+  <si>
+    <t>Consumo de agua por cada pernoctación de un turista nacional en comparación con el consumo de agua por cada noche de un residente</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1552,8 +1543,14 @@
       <color theme="10"/>
       <name val="Montserrat"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1569,12 +1566,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1724,7 +1715,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1768,20 +1759,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1835,6 +1812,47 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1842,12 +1860,6 @@
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="35">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2019,6 +2031,12 @@
         <name val="Montserrat"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
@@ -2589,8 +2607,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{72A2E2F1-7CAD-4C76-BEFF-2442C0A18302}" name="Dashboard" displayName="Dashboard" ref="A1:O53" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31" totalsRowBorderDxfId="30">
-  <autoFilter ref="A1:O53" xr:uid="{72A2E2F1-7CAD-4C76-BEFF-2442C0A18302}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{72A2E2F1-7CAD-4C76-BEFF-2442C0A18302}" name="Dashboard" displayName="Dashboard" ref="A1:O97" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31" totalsRowBorderDxfId="30">
+  <autoFilter ref="A1:O97" xr:uid="{72A2E2F1-7CAD-4C76-BEFF-2442C0A18302}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{1793D8B9-1834-4672-94E2-370894E55593}" name="Año" dataDxfId="29"/>
     <tableColumn id="12" xr3:uid="{2FF65C8B-F0E1-459C-B72F-3A1A5329FDAB}" name="ETIS" dataDxfId="28"/>
@@ -2608,7 +2626,7 @@
     <tableColumn id="11" xr3:uid="{1CC99560-09A8-483F-9CD5-16A60F770D27}" name="Valor" dataDxfId="16"/>
     <tableColumn id="16" xr3:uid="{AB90ABD6-A80B-4C26-AC5E-FC8654EC0E4D}" name="Comentarios" dataDxfId="15"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2622,11 +2640,11 @@
     <tableColumn id="2" xr3:uid="{B343196D-F313-4338-A33E-C35CA22E1037}" name="1. Turistas extranjeros que visitaron Calp" dataDxfId="14"/>
     <tableColumn id="3" xr3:uid="{7694471A-5A27-4BAB-9627-5B49B697400E}" name="1. Turistas nacionales que visitaron Calp" dataDxfId="13"/>
     <tableColumn id="4" xr3:uid="{1BAEF350-378C-40C2-820B-759FCF4ED388}" name="1. Total turistas" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{A35DAE71-EE4A-4EC9-8460-F2F26963F5A2}" name="2.% Turistas extranjeros que visitaron Calp" dataDxfId="0">
-      <calculatedColumnFormula>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{A35DAE71-EE4A-4EC9-8460-F2F26963F5A2}" name="2.% Turistas extranjeros que visitaron Calp" dataDxfId="11">
+      <calculatedColumnFormula>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{77257F63-E741-45A0-A7C8-573D91BC35FA}" name="2. % Turistas nacionales que visitaron Calp" dataDxfId="1">
-      <calculatedColumnFormula>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{77257F63-E741-45A0-A7C8-573D91BC35FA}" name="2. % Turistas nacionales que visitaron Calp" dataDxfId="10">
+      <calculatedColumnFormula>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2634,17 +2652,17 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{32B811EC-84D2-45FC-891C-7E090EB6CBCD}" name="Alojamientos" displayName="Alojamientos" ref="A1:H9" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{32B811EC-84D2-45FC-891C-7E090EB6CBCD}" name="Alojamientos" displayName="Alojamientos" ref="A1:H9" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:H9" xr:uid="{32B811EC-84D2-45FC-891C-7E090EB6CBCD}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{07BCC607-7EEB-4361-B136-CCDA8E5F70BE}" name="Tipo" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{0871BF09-A2EB-42F4-86E2-C14CDB481EC8}" name="Año" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{B1AB5E11-B4CF-48BB-A35C-C459F9489AB4}" name="Establecimientos" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{ACC63EB1-5B06-4BEE-9E7E-B340C9BD2498}" name="Plazas" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{03DB75FF-9B48-49D9-9D17-D4363A5A9025}" name="Habitaciones" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{B55E2CBA-9D33-447F-AFD9-B5ED8123A040}" name="Parcelas" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{18A9F2D6-F247-4306-843D-3BC9A08F8F16}" name="% alojamientos" dataDxfId="3" dataCellStyle="Porcentaje"/>
-    <tableColumn id="7" xr3:uid="{0CA9FABA-AC27-4D35-A37F-5ADFC3A1E28A}" name="% plazas" dataDxfId="2" dataCellStyle="Porcentaje">
+    <tableColumn id="1" xr3:uid="{07BCC607-7EEB-4361-B136-CCDA8E5F70BE}" name="Tipo" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{0871BF09-A2EB-42F4-86E2-C14CDB481EC8}" name="Año" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{B1AB5E11-B4CF-48BB-A35C-C459F9489AB4}" name="Establecimientos" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{ACC63EB1-5B06-4BEE-9E7E-B340C9BD2498}" name="Plazas" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{03DB75FF-9B48-49D9-9D17-D4363A5A9025}" name="Habitaciones" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{B55E2CBA-9D33-447F-AFD9-B5ED8123A040}" name="Parcelas" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{18A9F2D6-F247-4306-843D-3BC9A08F8F16}" name="% alojamientos" dataDxfId="1" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{0CA9FABA-AC27-4D35-A37F-5ADFC3A1E28A}" name="% plazas" dataDxfId="0" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>D2/D$9</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2969,7 +2987,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="M31" dT="2025-12-11T16:46:50.50" personId="{AB9528B7-6643-4F77-B76C-533514F2F00F}" id="{86248D9D-A426-4266-983B-342EA897A500}">
+  <threadedComment ref="M30" dT="2025-12-11T16:46:50.50" personId="{AB9528B7-6643-4F77-B76C-533514F2F00F}" id="{86248D9D-A426-4266-983B-342EA897A500}">
+    <text>Preguntar a Paula si tenim este dato</text>
+  </threadedComment>
+  <threadedComment ref="M78" dT="2025-12-11T16:46:50.50" personId="{AB9528B7-6643-4F77-B76C-533514F2F00F}" id="{C1CEE11B-07A1-41EC-931F-B2E17012E67A}">
     <text>Preguntar a Paula si tenim este dato</text>
   </threadedComment>
 </ThreadedComments>
@@ -2977,23 +2998,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27BA13B8-EC56-4433-A73B-150D55368D4D}">
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="11.5546875" style="37"/>
-    <col min="3" max="4" width="16.6640625" style="37" customWidth="1"/>
-    <col min="5" max="5" width="52.5546875" style="37" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="113" style="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.6640625" style="37" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.6640625" style="37" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.6640625" style="37" customWidth="1"/>
-    <col min="10" max="10" width="14.21875" style="37" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" style="37"/>
-    <col min="12" max="12" width="22" style="37" customWidth="1"/>
-    <col min="13" max="13" width="21.5546875" style="37" customWidth="1"/>
-    <col min="14" max="14" width="15.21875" style="44" customWidth="1"/>
-    <col min="15" max="15" width="255.77734375" style="45" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="11.5546875" style="37"/>
+    <col min="1" max="2" width="11.5546875" style="31"/>
+    <col min="3" max="4" width="16.6640625" style="31" customWidth="1"/>
+    <col min="5" max="5" width="52.5546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="113" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.6640625" style="31" customWidth="1"/>
+    <col min="10" max="10" width="14.21875" style="31" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" style="31"/>
+    <col min="12" max="12" width="68.44140625" style="31" customWidth="1"/>
+    <col min="13" max="13" width="21.5546875" style="31" customWidth="1"/>
+    <col min="14" max="14" width="15.21875" style="38" customWidth="1"/>
+    <col min="15" max="15" width="255.77734375" style="39" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="11.5546875" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
@@ -3001,13 +3022,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -3019,7 +3040,7 @@
         <v>2</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>3</v>
@@ -3034,60 +3055,60 @@
         <v>6</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A2" s="24">
+      <c r="A2" s="18">
         <v>2024</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="20">
+        <v>1</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="26">
-        <v>1</v>
-      </c>
-      <c r="E2" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="H2" s="27" t="s">
+      <c r="G2" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="I2" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="J2" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="N2" s="28">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="O2" s="29" t="s">
-        <v>61</v>
+      <c r="N2" s="22">
+        <v>1.53</v>
+      </c>
+      <c r="O2" s="23" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
@@ -3095,7 +3116,7 @@
         <v>2024</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>20</v>
@@ -3110,13 +3131,13 @@
         <v>9</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>11</v>
@@ -3128,10 +3149,10 @@
         <v>14</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="O3" s="11"/>
     </row>
@@ -3140,7 +3161,7 @@
         <v>2024</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>20</v>
@@ -3155,13 +3176,13 @@
         <v>15</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>11</v>
@@ -3173,10 +3194,10 @@
         <v>16</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="O4" s="8"/>
     </row>
@@ -3185,7 +3206,7 @@
         <v>2024</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>20</v>
@@ -3197,16 +3218,16 @@
         <v>8</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>280</v>
+        <v>326</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>231</v>
+        <v>325</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>11</v>
@@ -3215,1138 +3236,1140 @@
         <v>12</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A6" s="5">
+      <c r="A6" s="18">
         <v>2024</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="7">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="D6" s="20">
+        <v>2</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="N6" s="22">
+        <v>52.27</v>
+      </c>
+      <c r="O6" s="23" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A7" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="20">
+        <v>2</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="M7" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="N7" s="22">
+        <v>47.73</v>
+      </c>
+      <c r="O7" s="23" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A8" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="20">
+        <v>3</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="N8" s="26">
+        <v>401126</v>
+      </c>
+      <c r="O8" s="23"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A9" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="20">
+        <v>3</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="N9" s="26">
+        <v>4813511</v>
+      </c>
+      <c r="O9" s="23"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A10" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="20">
+        <v>3</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="N10" s="28">
+        <v>120.8</v>
+      </c>
+      <c r="O10" s="23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A11" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="20">
+        <v>3</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="N11" s="28">
+        <v>9.75</v>
+      </c>
+      <c r="O11" s="23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A12" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="20">
+        <v>3</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="N12" s="28">
+        <v>34.97</v>
+      </c>
+      <c r="O12" s="37" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A13" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="20">
+        <v>3</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="N13" s="28">
+        <v>11.7</v>
+      </c>
+      <c r="O13" s="25" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A14" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="20">
+        <v>3</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="M14" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="N14" s="28">
+        <v>859</v>
+      </c>
+      <c r="O14" s="36"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A15" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="20">
+        <v>3</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="M15" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="N15" s="28">
+        <v>7</v>
+      </c>
+      <c r="O15" s="36"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A16" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="20">
+        <v>3</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="M16" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="N16" s="28">
+        <v>4</v>
+      </c>
+      <c r="O16" s="36"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A17" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="20">
+        <v>4</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="M17" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="N17" s="26">
+        <v>247964</v>
+      </c>
+      <c r="O17" s="23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A18" s="41">
+        <v>2024</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="20">
+        <v>4</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="M18" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="N18" s="26">
+        <v>310709</v>
+      </c>
+      <c r="O18" s="19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A19" s="5">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="7">
+        <v>5</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A20" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="20">
+        <v>6</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="M20" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="N20" s="22">
+        <v>68.89</v>
+      </c>
+      <c r="O20" s="23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+      <c r="A21" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="20">
+        <v>6</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="N21" s="22">
+        <v>6.59</v>
+      </c>
+      <c r="O21" s="23" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+      <c r="A22" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="20">
+        <v>6</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K22" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="M22" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="N22" s="22">
+        <v>12.02</v>
+      </c>
+      <c r="O22" s="23" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+      <c r="A23" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="20">
+        <v>6</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K23" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="N23" s="22">
+        <v>9.56</v>
+      </c>
+      <c r="O23" s="23" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A24" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="20">
+        <v>7</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K24" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="N24" s="22">
+        <v>36.78</v>
+      </c>
+      <c r="O24" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A25" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="20">
+        <v>7</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K25" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="N25" s="22">
+        <v>34.18</v>
+      </c>
+      <c r="O25" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A26" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="20">
+        <v>7</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K26" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="N26" s="22">
+        <v>50.85</v>
+      </c>
+      <c r="O26" s="23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A27" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="20">
+        <v>7</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="40" t="s">
+        <v>310</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K27" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="N27" s="22">
+        <v>2.1</v>
+      </c>
+      <c r="O27" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A28" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="20">
+        <v>7</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I28" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="N28" s="22">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="O28" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+      <c r="A29" s="5">
+        <v>2024</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="7">
         <v>8</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="O6" s="6"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A7" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="26">
-        <v>2</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="H7" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="J7" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L7" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="M7" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="N7" s="28">
-        <v>52.27</v>
-      </c>
-      <c r="O7" s="29" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A8" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="26">
-        <v>2</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="J8" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K8" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="M8" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="N8" s="28">
-        <v>47.73</v>
-      </c>
-      <c r="O8" s="29" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A9" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="26">
-        <v>3</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K9" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="L9" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="M9" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="N9" s="32">
-        <v>401126</v>
-      </c>
-      <c r="O9" s="29"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A10" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="26">
-        <v>3</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="H10" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I10" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="K10" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="L10" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="M10" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="N10" s="32">
-        <v>4813511</v>
-      </c>
-      <c r="O10" s="29"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A11" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="26">
-        <v>3</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="H11" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="J11" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K11" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="L11" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="M11" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="N11" s="34">
-        <v>120.8</v>
-      </c>
-      <c r="O11" s="29" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A12" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="26">
-        <v>3</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="H12" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="J12" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="L12" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="M12" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N12" s="34">
-        <v>9.75</v>
-      </c>
-      <c r="O12" s="29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A13" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="26">
-        <v>3</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="H13" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="I13" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="J13" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K13" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="M13" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="N13" s="34">
-        <v>34.97</v>
-      </c>
-      <c r="O13" s="43" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A14" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="26">
-        <v>3</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="H14" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="I14" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="J14" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K14" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L14" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="M14" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="N14" s="34">
-        <v>11.7</v>
-      </c>
-      <c r="O14" s="31" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A15" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="26">
-        <v>3</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="H15" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="J15" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K15" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L15" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="M15" s="26" t="s">
-        <v>324</v>
-      </c>
-      <c r="N15" s="34">
-        <v>859</v>
-      </c>
-      <c r="O15" s="42"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A16" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="26">
-        <v>3</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>318</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="H16" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="J16" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K16" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="M16" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="N16" s="34">
-        <v>7</v>
-      </c>
-      <c r="O16" s="42"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A17" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="26">
-        <v>3</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="H17" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="J17" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K17" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L17" s="26" t="s">
-        <v>323</v>
-      </c>
-      <c r="M17" s="26" t="s">
-        <v>326</v>
-      </c>
-      <c r="N17" s="34">
-        <v>4</v>
-      </c>
-      <c r="O17" s="42"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A18" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="26">
-        <v>4</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="H18" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I18" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="J18" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K18" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L18" s="26" t="s">
-        <v>343</v>
-      </c>
-      <c r="M18" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="N18" s="32">
-        <v>247964</v>
-      </c>
-      <c r="O18" s="29" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A19" s="47">
-        <v>2024</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="26">
-        <v>4</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>341</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="H19" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I19" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="J19" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K19" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L19" s="26" t="s">
-        <v>344</v>
-      </c>
-      <c r="M19" s="26" t="s">
-        <v>345</v>
-      </c>
-      <c r="N19" s="32">
-        <v>310709</v>
-      </c>
-      <c r="O19" s="25" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A20" s="5">
-        <v>2024</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="7">
-        <v>5</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A21" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="26">
-        <v>6</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="G21" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="H21" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="I21" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="J21" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="K21" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L21" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="M21" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="N21" s="28">
-        <v>68.89</v>
-      </c>
-      <c r="O21" s="29" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="18" x14ac:dyDescent="0.4">
-      <c r="A22" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="26">
-        <v>6</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="H22" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="I22" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="J22" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K22" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="L22" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="M22" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="N22" s="28">
-        <v>6.59</v>
-      </c>
-      <c r="O22" s="29" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="18" x14ac:dyDescent="0.4">
-      <c r="A23" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="26">
-        <v>6</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="H23" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="I23" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="J23" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K23" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="L23" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="M23" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="N23" s="28">
-        <v>12.02</v>
-      </c>
-      <c r="O23" s="29" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="18" x14ac:dyDescent="0.4">
-      <c r="A24" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="26">
-        <v>6</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="G24" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="H24" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="I24" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="J24" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K24" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="L24" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="M24" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="N24" s="28">
-        <v>9.56</v>
-      </c>
-      <c r="O24" s="29" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A25" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="26">
-        <v>7</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="H25" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="I25" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="J25" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K25" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="L25" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="M25" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="N25" s="28">
-        <v>36.78</v>
-      </c>
-      <c r="O25" s="29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A26" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="26">
-        <v>7</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="H26" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="I26" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="J26" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K26" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="L26" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="M26" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="N26" s="28">
-        <v>34.18</v>
-      </c>
-      <c r="O26" s="29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A27" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B27" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="26">
-        <v>7</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="G27" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="H27" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="I27" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="J27" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K27" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L27" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M27" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="N27" s="28">
-        <v>50.85</v>
-      </c>
-      <c r="O27" s="29" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A28" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="C28" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="26">
-        <v>7</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" s="46" t="s">
-        <v>336</v>
-      </c>
-      <c r="G28" s="26" t="s">
-        <v>339</v>
-      </c>
-      <c r="H28" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="I28" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="J28" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K28" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="L28" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="M28" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="N28" s="28">
-        <v>2.1</v>
-      </c>
-      <c r="O28" s="29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A29" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B29" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="C29" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="26">
-        <v>7</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>337</v>
-      </c>
-      <c r="G29" s="26" t="s">
-        <v>338</v>
-      </c>
-      <c r="H29" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="I29" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="J29" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K29" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="L29" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="M29" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="N29" s="28">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="O29" s="29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+      <c r="E29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="O29" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>20</v>
@@ -4358,34 +4381,34 @@
         <v>26</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="G30" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L30" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="H30" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>263</v>
-      </c>
       <c r="M30" s="7" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="O30" s="8" t="s">
-        <v>123</v>
+        <v>119</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.4">
@@ -4393,7 +4416,7 @@
         <v>2024</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>20</v>
@@ -4405,269 +4428,267 @@
         <v>26</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="J31" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="K31" s="10" t="s">
-        <v>17</v>
+      <c r="K31" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>123</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A32" s="5">
+      <c r="A32" s="18">
         <v>2024</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="7">
-        <v>8</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="L32" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="M32" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="O32" s="6" t="s">
-        <v>275</v>
+      <c r="B32" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="20">
+        <v>10</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K32" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="N32" s="22">
+        <v>82.11</v>
+      </c>
+      <c r="O32" s="23" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A33" s="5">
+      <c r="A33" s="18">
         <v>2024</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="7">
-        <v>8</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="L33" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="M33" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="O33" s="6" t="s">
-        <v>279</v>
+      <c r="B33" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="20">
+        <v>10</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="M33" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="N33" s="22">
+        <v>17.89</v>
+      </c>
+      <c r="O33" s="23" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A34" s="24">
+      <c r="A34" s="5">
         <v>2024</v>
       </c>
-      <c r="B34" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D34" s="26">
-        <v>9</v>
-      </c>
-      <c r="E34" s="26" t="s">
+      <c r="B34" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F34" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="G34" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="H34" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="I34" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="J34" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K34" s="27" t="s">
+      <c r="D34" s="7">
+        <v>11</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="N34" s="42">
+        <v>581472128.79999995</v>
+      </c>
+      <c r="O34" s="8"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A35" s="5">
+        <v>2024</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="7">
         <v>12</v>
       </c>
-      <c r="L34" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="M34" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="N34" s="30">
-        <v>45</v>
-      </c>
-      <c r="O34" s="29" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A35" s="24">
+      <c r="E35" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="O35" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A36" s="18">
         <v>2024</v>
       </c>
-      <c r="B35" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" s="26">
-        <v>10</v>
-      </c>
-      <c r="E35" s="26" t="s">
+      <c r="B36" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="20">
+        <v>13</v>
+      </c>
+      <c r="E36" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F35" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="G35" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="H35" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I35" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="J35" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K35" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L35" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="M35" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="N35" s="28">
-        <v>82.11</v>
-      </c>
-      <c r="O35" s="29" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A36" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>334</v>
-      </c>
-      <c r="C36" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="26">
-        <v>10</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="G36" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="H36" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I36" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="J36" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K36" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L36" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="M36" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="N36" s="28">
-        <v>17.89</v>
-      </c>
-      <c r="O36" s="29" t="s">
-        <v>172</v>
+      <c r="F36" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="I36" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K36" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="M36" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="N36" s="22">
+        <v>49.16</v>
+      </c>
+      <c r="O36" s="23" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.4">
@@ -4675,46 +4696,46 @@
         <v>2024</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D37" s="20">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>215</v>
+        <v>29</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>123</v>
+        <v>193</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="I37" s="20" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="K37" s="21" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="L37" s="20" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="M37" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N37" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="O37" s="23" t="s">
-        <v>123</v>
+        <v>106</v>
+      </c>
+      <c r="N37" s="22">
+        <v>37.65</v>
+      </c>
+      <c r="O37" s="37" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.4">
@@ -4722,759 +4743,2734 @@
         <v>2024</v>
       </c>
       <c r="B38" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="20">
+        <v>13</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="I38" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K38" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M38" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="N38" s="22">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="O38" s="37" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A39" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="20">
+        <v>13</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K39" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L39" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="M39" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="N39" s="24">
+        <v>70</v>
+      </c>
+      <c r="O39" s="25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A40" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" s="20">
+        <v>14</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K40" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L40" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="M40" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="N40" s="24">
+        <v>18</v>
+      </c>
+      <c r="O40" s="23" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A41" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" s="20">
+        <v>15</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="H41" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I41" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K41" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L41" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="M41" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="N41" s="24">
+        <v>94</v>
+      </c>
+      <c r="O41" s="23" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A42" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="20">
+        <v>15</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I42" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K42" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L42" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="M42" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="N42" s="24">
+        <v>6</v>
+      </c>
+      <c r="O42" s="23" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A43" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" s="20">
+        <v>15</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K43" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="L43" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="M43" s="20"/>
+      <c r="N43" s="26">
+        <v>737000000</v>
+      </c>
+      <c r="O43" s="23" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A44" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" s="20">
+        <v>15</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="H44" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I44" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K44" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="L44" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="N44" s="26">
+        <v>575000000</v>
+      </c>
+      <c r="O44" s="23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A45" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="20">
+        <v>15</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F45" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="C38" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="20">
+      <c r="G45" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="H45" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I45" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K45" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="L45" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="M45" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="N45" s="26">
+        <v>162000000</v>
+      </c>
+      <c r="O45" s="23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A46" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D46" s="20">
+        <v>16</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="G46" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="H46" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="I46" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="J46" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K46" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="E38" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="G38" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H38" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="I38" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="J38" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="K38" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="L38" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="M38" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N38" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="O38" s="23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A39" s="24">
+      <c r="L46" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="M46" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="N46" s="24">
+        <v>9</v>
+      </c>
+      <c r="O46" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="5">
         <v>2024</v>
       </c>
-      <c r="B39" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" s="26">
-        <v>13</v>
-      </c>
-      <c r="E39" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="F39" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="G39" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="H39" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="I39" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="J39" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K39" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="L39" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="M39" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="N39" s="28">
-        <v>49.16</v>
-      </c>
-      <c r="O39" s="29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A40" s="24">
+      <c r="B47" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" s="7">
+        <v>17</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="M47" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="N47" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="O47" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A48" s="5">
         <v>2024</v>
       </c>
-      <c r="B40" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="C40" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="26">
-        <v>13</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="F40" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G40" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="H40" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="I40" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="J40" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K40" s="27" t="s">
+      <c r="B48" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="7">
+        <v>17</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K48" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L40" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="M40" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="N40" s="28">
-        <v>37.65</v>
-      </c>
-      <c r="O40" s="43" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A41" s="24">
+      <c r="L48" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="M48" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="N48" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="O48" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A49" s="13">
         <v>2024</v>
       </c>
-      <c r="B41" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="C41" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D41" s="26">
-        <v>13</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="F41" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="G41" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="H41" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="I41" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="J41" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K41" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L41" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="M41" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="N41" s="28">
-        <v>32.590000000000003</v>
-      </c>
-      <c r="O41" s="43" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A42" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B42" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="C42" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" s="26">
-        <v>13</v>
-      </c>
-      <c r="E42" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="F42" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="G42" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="H42" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="I42" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="J42" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K42" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L42" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="M42" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="N42" s="30">
-        <v>70</v>
-      </c>
-      <c r="O42" s="31" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A43" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B43" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="C43" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" s="26">
-        <v>14</v>
-      </c>
-      <c r="E43" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="G43" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="H43" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="I43" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="J43" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K43" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L43" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="M43" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="N43" s="30">
-        <v>18</v>
-      </c>
-      <c r="O43" s="29" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A44" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B44" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="C44" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D44" s="26">
-        <v>15</v>
-      </c>
-      <c r="E44" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F44" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="G44" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="H44" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I44" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="J44" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K44" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L44" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="M44" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="N44" s="30">
-        <v>94</v>
-      </c>
-      <c r="O44" s="29" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A45" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B45" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="C45" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" s="26">
-        <v>15</v>
-      </c>
-      <c r="E45" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F45" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="G45" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="H45" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I45" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="J45" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K45" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L45" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="M45" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="N45" s="30">
-        <v>6</v>
-      </c>
-      <c r="O45" s="29" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A46" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B46" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C46" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D46" s="26">
-        <v>15</v>
-      </c>
-      <c r="E46" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F46" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="G46" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="H46" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I46" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="J46" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K46" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="L46" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="M46" s="26"/>
-      <c r="N46" s="32">
-        <v>737000000</v>
-      </c>
-      <c r="O46" s="29" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A47" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B47" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C47" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D47" s="26">
-        <v>15</v>
-      </c>
-      <c r="E47" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F47" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="G47" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="H47" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I47" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="J47" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K47" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="L47" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="M47" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="N47" s="32">
-        <v>575000000</v>
-      </c>
-      <c r="O47" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A48" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B48" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="C48" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D48" s="26">
-        <v>15</v>
-      </c>
-      <c r="E48" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F48" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="G48" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="H48" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I48" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="J48" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K48" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="L48" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="M48" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="N48" s="32">
-        <v>162000000</v>
-      </c>
-      <c r="O48" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="5">
-        <v>2024</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>123</v>
+      <c r="B49" s="14" t="s">
+        <v>119</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D49" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L49" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="M49" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="N49" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="O49" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A50" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B50" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="52">
+        <v>1</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="G50" s="53" t="s">
+        <v>205</v>
+      </c>
+      <c r="H50" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="I50" s="54" t="s">
+        <v>330</v>
+      </c>
+      <c r="J50" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="K50" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L50" s="54" t="s">
+        <v>56</v>
+      </c>
+      <c r="M50" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="N50" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="O50" s="46"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A51" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B51" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="52">
+        <v>1</v>
+      </c>
+      <c r="E51" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="G51" s="52" t="s">
+        <v>209</v>
+      </c>
+      <c r="H51" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="I51" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="J51" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K51" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L51" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="M51" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="N51" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O51" s="44"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A52" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B52" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" s="52">
+        <v>1</v>
+      </c>
+      <c r="E52" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="52" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="H52" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="I52" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="J52" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K52" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="L52" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="M52" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="N52" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O52" s="44"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A53" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B53" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="52">
+        <v>1</v>
+      </c>
+      <c r="E53" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="52" t="s">
+        <v>326</v>
+      </c>
+      <c r="G53" s="52" t="s">
+        <v>260</v>
+      </c>
+      <c r="H53" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="I53" s="52" t="s">
+        <v>325</v>
+      </c>
+      <c r="J53" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K53" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L53" s="55" t="s">
+        <v>327</v>
+      </c>
+      <c r="M53" s="52" t="s">
+        <v>328</v>
+      </c>
+      <c r="N53" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O53" s="44"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A54" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B54" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="C54" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" s="52">
+        <v>2</v>
+      </c>
+      <c r="E54" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="F54" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="G54" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="H54" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="I54" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="J54" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K54" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L54" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="M54" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="N54" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O54" s="44"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A55" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B55" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="C55" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="52">
+        <v>2</v>
+      </c>
+      <c r="E55" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="F55" s="52" t="s">
+        <v>185</v>
+      </c>
+      <c r="G55" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="H55" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="I55" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="J55" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K55" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L55" s="52" t="s">
+        <v>156</v>
+      </c>
+      <c r="M55" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="N55" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O55" s="44"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A56" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B56" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C56" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" s="52">
+        <v>3</v>
+      </c>
+      <c r="E56" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F56" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G56" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="H56" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I56" s="52" t="s">
+        <v>63</v>
+      </c>
+      <c r="J56" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K56" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="L56" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="M56" s="52" t="s">
+        <v>111</v>
+      </c>
+      <c r="N56" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O56" s="44"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A57" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B57" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="52">
+        <v>3</v>
+      </c>
+      <c r="E57" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F57" s="52" t="s">
+        <v>64</v>
+      </c>
+      <c r="G57" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="H57" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I57" s="52" t="s">
+        <v>63</v>
+      </c>
+      <c r="J57" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="K57" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="L57" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="M57" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="N57" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O57" s="44"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A58" s="48">
+        <v>2025</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="50">
+        <v>3</v>
+      </c>
+      <c r="E58" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F58" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="G58" s="50" t="s">
+        <v>203</v>
+      </c>
+      <c r="H58" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I58" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="J58" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K58" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="L58" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="M58" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="N58" s="22">
+        <v>126.5</v>
+      </c>
+      <c r="O58" s="49" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A59" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B59" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="52">
+        <v>3</v>
+      </c>
+      <c r="E59" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F59" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="G59" s="52" t="s">
+        <v>202</v>
+      </c>
+      <c r="H59" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I59" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="J59" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K59" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="L59" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="M59" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="N59" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O59" s="44"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A60" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B60" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="C60" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" s="52">
+        <v>3</v>
+      </c>
+      <c r="E60" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F60" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="G60" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="H60" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="I60" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="J60" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K60" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L60" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="M60" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="N60" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O60" s="44"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A61" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B61" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" s="52">
+        <v>3</v>
+      </c>
+      <c r="E61" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F61" s="52" t="s">
+        <v>176</v>
+      </c>
+      <c r="G61" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="H61" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="I61" s="52" t="s">
+        <v>178</v>
+      </c>
+      <c r="J61" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K61" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L61" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="M61" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="N61" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O61" s="44"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A62" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B62" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62" s="52">
+        <v>3</v>
+      </c>
+      <c r="E62" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F62" s="52" t="s">
+        <v>291</v>
+      </c>
+      <c r="G62" s="52" t="s">
+        <v>294</v>
+      </c>
+      <c r="H62" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I62" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="J62" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K62" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="L62" s="52" t="s">
+        <v>295</v>
+      </c>
+      <c r="M62" s="52" t="s">
+        <v>298</v>
+      </c>
+      <c r="N62" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O62" s="44"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A63" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B63" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D63" s="52">
+        <v>3</v>
+      </c>
+      <c r="E63" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F63" s="52" t="s">
+        <v>292</v>
+      </c>
+      <c r="G63" s="52" t="s">
+        <v>294</v>
+      </c>
+      <c r="H63" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I63" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="J63" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K63" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="L63" s="52" t="s">
+        <v>296</v>
+      </c>
+      <c r="M63" s="52" t="s">
+        <v>299</v>
+      </c>
+      <c r="N63" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O63" s="44"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A64" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B64" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D64" s="52">
+        <v>3</v>
+      </c>
+      <c r="E64" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F64" s="52" t="s">
+        <v>293</v>
+      </c>
+      <c r="G64" s="52" t="s">
+        <v>294</v>
+      </c>
+      <c r="H64" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I64" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="J64" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K64" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="L64" s="52" t="s">
+        <v>297</v>
+      </c>
+      <c r="M64" s="52" t="s">
+        <v>300</v>
+      </c>
+      <c r="N64" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O64" s="44"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A65" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B65" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C65" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="52">
+        <v>4</v>
+      </c>
+      <c r="E65" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="F65" s="52" t="s">
+        <v>314</v>
+      </c>
+      <c r="G65" s="52" t="s">
+        <v>316</v>
+      </c>
+      <c r="H65" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I65" s="52" t="s">
+        <v>255</v>
+      </c>
+      <c r="J65" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K65" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="L65" s="52" t="s">
+        <v>317</v>
+      </c>
+      <c r="M65" s="52" t="s">
+        <v>320</v>
+      </c>
+      <c r="N65" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O65" s="44"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A66" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B66" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C66" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66" s="52">
+        <v>4</v>
+      </c>
+      <c r="E66" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" s="52" t="s">
+        <v>315</v>
+      </c>
+      <c r="G66" s="52" t="s">
+        <v>316</v>
+      </c>
+      <c r="H66" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I66" s="52" t="s">
+        <v>255</v>
+      </c>
+      <c r="J66" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K66" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="L66" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="M66" s="52" t="s">
+        <v>319</v>
+      </c>
+      <c r="N66" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O66" s="44"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A67" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B67" s="51" t="s">
+        <v>232</v>
+      </c>
+      <c r="C67" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67" s="52">
+        <v>5</v>
+      </c>
+      <c r="E67" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" s="52" t="s">
+        <v>233</v>
+      </c>
+      <c r="G67" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="H67" s="52" t="s">
+        <v>228</v>
+      </c>
+      <c r="I67" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="J67" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K67" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="L67" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="M67" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="N67" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O67" s="44"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A68" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B68" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="C68" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" s="52">
+        <v>6</v>
+      </c>
+      <c r="E68" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="G68" s="52" t="s">
+        <v>199</v>
+      </c>
+      <c r="H68" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="I68" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="J68" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="K68" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L68" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="M68" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="N68" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O68" s="44"/>
+    </row>
+    <row r="69" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+      <c r="A69" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B69" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="C69" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D69" s="52">
+        <v>6</v>
+      </c>
+      <c r="E69" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="G69" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="H69" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="I69" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="J69" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K69" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="L69" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="M69" s="52" t="s">
+        <v>152</v>
+      </c>
+      <c r="N69" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O69" s="44"/>
+    </row>
+    <row r="70" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+      <c r="A70" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B70" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="C70" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70" s="52">
+        <v>6</v>
+      </c>
+      <c r="E70" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F70" s="52" t="s">
+        <v>341</v>
+      </c>
+      <c r="G70" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="H70" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="I70" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="J70" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K70" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="L70" s="52" t="s">
+        <v>147</v>
+      </c>
+      <c r="M70" s="52" t="s">
+        <v>153</v>
+      </c>
+      <c r="N70" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O70" s="44"/>
+    </row>
+    <row r="71" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+      <c r="A71" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B71" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="C71" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="52">
+        <v>6</v>
+      </c>
+      <c r="E71" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F71" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="G71" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="H71" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="I71" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="J71" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K71" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="L71" s="52" t="s">
+        <v>148</v>
+      </c>
+      <c r="M71" s="52" t="s">
+        <v>154</v>
+      </c>
+      <c r="N71" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O71" s="44"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A72" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B72" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="C72" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" s="52">
+        <v>7</v>
+      </c>
+      <c r="E72" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F72" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G72" s="52" t="s">
+        <v>197</v>
+      </c>
+      <c r="H72" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="I72" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="J72" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K72" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="L72" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="M72" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="N72" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O72" s="44"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A73" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B73" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C73" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" s="52">
+        <v>7</v>
+      </c>
+      <c r="E73" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G73" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="H73" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="I73" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="J73" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K73" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="L73" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="M73" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="N73" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O73" s="44"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A74" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B74" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C74" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D74" s="52">
+        <v>7</v>
+      </c>
+      <c r="E74" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F74" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="G74" s="52" t="s">
+        <v>195</v>
+      </c>
+      <c r="H74" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="I74" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="J74" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K74" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L74" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="M74" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="N74" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O74" s="44"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A75" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B75" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C75" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D75" s="52">
+        <v>7</v>
+      </c>
+      <c r="E75" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F75" s="52" t="s">
+        <v>310</v>
+      </c>
+      <c r="G75" s="52" t="s">
+        <v>313</v>
+      </c>
+      <c r="H75" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="I75" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="J75" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K75" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="L75" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="M75" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="N75" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O75" s="44"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A76" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B76" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="C76" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D76" s="52">
+        <v>7</v>
+      </c>
+      <c r="E76" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F76" s="52" t="s">
+        <v>311</v>
+      </c>
+      <c r="G76" s="52" t="s">
+        <v>312</v>
+      </c>
+      <c r="H76" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="I76" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="J76" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K76" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="L76" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="M76" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="N76" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O76" s="44"/>
+    </row>
+    <row r="77" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+      <c r="A77" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B77" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C77" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D77" s="52">
+        <v>8</v>
+      </c>
+      <c r="E77" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F77" s="52" t="s">
         <v>244</v>
       </c>
-      <c r="G49" s="7" t="s">
+      <c r="G77" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="H77" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I77" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="J77" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K77" s="54" t="s">
+        <v>246</v>
+      </c>
+      <c r="L77" s="52" t="s">
+        <v>247</v>
+      </c>
+      <c r="M77" s="52" t="s">
+        <v>248</v>
+      </c>
+      <c r="N77" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O77" s="44"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A78" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B78" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C78" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" s="52">
+        <v>8</v>
+      </c>
+      <c r="E78" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F78" s="52" t="s">
+        <v>249</v>
+      </c>
+      <c r="G78" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="H78" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I78" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="J78" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K78" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="L78" s="52" t="s">
+        <v>261</v>
+      </c>
+      <c r="M78" s="52" t="s">
+        <v>250</v>
+      </c>
+      <c r="N78" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O78" s="44"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A79" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B79" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C79" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D79" s="52">
+        <v>8</v>
+      </c>
+      <c r="E79" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F79" s="52" t="s">
+        <v>254</v>
+      </c>
+      <c r="G79" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="H79" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I79" s="52" t="s">
+        <v>255</v>
+      </c>
+      <c r="J79" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K79" s="53" t="s">
+        <v>256</v>
+      </c>
+      <c r="L79" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="M79" s="52" t="s">
+        <v>258</v>
+      </c>
+      <c r="N79" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O79" s="44"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A80" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B80" s="51" t="s">
+        <v>307</v>
+      </c>
+      <c r="C80" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D80" s="52">
+        <v>10</v>
+      </c>
+      <c r="E80" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="F80" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="G80" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="H80" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I80" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="J80" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K80" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L80" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="M80" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="N80" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O80" s="44"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A81" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B81" s="51" t="s">
+        <v>308</v>
+      </c>
+      <c r="C81" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D81" s="52">
+        <v>10</v>
+      </c>
+      <c r="E81" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="F81" s="52" t="s">
+        <v>161</v>
+      </c>
+      <c r="G81" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="H81" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I81" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="J81" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K81" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L81" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="M81" s="52" t="s">
+        <v>166</v>
+      </c>
+      <c r="N81" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O81" s="44"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A82" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B82" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C82" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D82" s="52">
+        <v>11</v>
+      </c>
+      <c r="E82" s="52" t="s">
+        <v>211</v>
+      </c>
+      <c r="F82" s="52" t="s">
+        <v>333</v>
+      </c>
+      <c r="G82" s="52" t="s">
+        <v>329</v>
+      </c>
+      <c r="H82" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="I82" s="52" t="s">
+        <v>336</v>
+      </c>
+      <c r="J82" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K82" s="54" t="s">
+        <v>171</v>
+      </c>
+      <c r="L82" s="52" t="s">
+        <v>332</v>
+      </c>
+      <c r="M82" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="N82" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O82" s="44"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A83" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B83" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C83" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" s="52">
+        <v>12</v>
+      </c>
+      <c r="E83" s="52" t="s">
+        <v>212</v>
+      </c>
+      <c r="F83" s="52" t="s">
+        <v>334</v>
+      </c>
+      <c r="G83" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="H83" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="I83" s="52" t="s">
+        <v>178</v>
+      </c>
+      <c r="J83" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K83" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L83" s="52" t="s">
+        <v>337</v>
+      </c>
+      <c r="M83" s="52" t="s">
+        <v>338</v>
+      </c>
+      <c r="N83" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O83" s="44"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A84" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B84" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="C84" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D84" s="52">
+        <v>13</v>
+      </c>
+      <c r="E84" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F84" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="G84" s="52" t="s">
+        <v>213</v>
+      </c>
+      <c r="H84" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="I84" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="J84" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K84" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="L84" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="M84" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="N84" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O84" s="44"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A85" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B85" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="C85" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" s="52">
+        <v>13</v>
+      </c>
+      <c r="E85" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F85" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="G85" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="H85" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="I85" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="J85" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K85" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L85" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="M85" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="N85" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O85" s="44"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A86" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B86" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="C86" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D86" s="52">
+        <v>13</v>
+      </c>
+      <c r="E86" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F86" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="G86" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="H86" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="I86" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="J86" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K86" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L86" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="M86" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="N86" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O86" s="44"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A87" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B87" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="C87" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D87" s="52">
+        <v>13</v>
+      </c>
+      <c r="E87" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F87" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="G87" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="H87" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="I87" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="J87" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K87" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L87" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="M87" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="N87" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O87" s="44"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A88" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B88" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="C88" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D88" s="52">
+        <v>14</v>
+      </c>
+      <c r="E88" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="F88" s="52" t="s">
+        <v>189</v>
+      </c>
+      <c r="G88" s="52" t="s">
+        <v>223</v>
+      </c>
+      <c r="H88" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="I88" s="52" t="s">
+        <v>178</v>
+      </c>
+      <c r="J88" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K88" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L88" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="M88" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="N88" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O88" s="44"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A89" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B89" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="C89" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D89" s="52">
+        <v>15</v>
+      </c>
+      <c r="E89" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F89" s="52" t="s">
+        <v>219</v>
+      </c>
+      <c r="G89" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="H89" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I89" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="J89" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K89" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L89" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="M89" s="52" t="s">
+        <v>216</v>
+      </c>
+      <c r="N89" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O89" s="44"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A90" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B90" s="51" t="s">
+        <v>215</v>
+      </c>
+      <c r="C90" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D90" s="52">
+        <v>15</v>
+      </c>
+      <c r="E90" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F90" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="G90" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="H90" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I90" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="J90" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K90" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L90" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="M90" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="N90" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O90" s="44"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A91" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B91" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C91" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D91" s="52">
+        <v>15</v>
+      </c>
+      <c r="E91" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F91" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="G91" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="H91" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I91" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="J91" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K91" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="L91" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="M91" s="52"/>
+      <c r="N91" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O91" s="44"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A92" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B92" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="C92" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D92" s="52">
+        <v>15</v>
+      </c>
+      <c r="E92" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F92" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="G92" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="H92" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I92" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="J92" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K92" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="L92" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="M92" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="N92" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O92" s="44"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A93" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B93" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="C93" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D93" s="52">
+        <v>15</v>
+      </c>
+      <c r="E93" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F93" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="G93" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="H93" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I93" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="J93" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K93" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="L93" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="M93" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="N93" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O93" s="44"/>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A94" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B94" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="C94" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D94" s="52">
+        <v>16</v>
+      </c>
+      <c r="E94" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="F94" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="G94" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="H94" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="I94" s="52" t="s">
+        <v>178</v>
+      </c>
+      <c r="J94" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K94" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L94" s="52" t="s">
+        <v>224</v>
+      </c>
+      <c r="M94" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="N94" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O94" s="44"/>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A95" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B95" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C95" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D95" s="52">
+        <v>17</v>
+      </c>
+      <c r="E95" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="F95" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="G95" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="H95" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="I95" s="52" t="s">
+        <v>321</v>
+      </c>
+      <c r="J95" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K95" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="L95" s="52" t="s">
+        <v>323</v>
+      </c>
+      <c r="M95" s="52" t="s">
+        <v>324</v>
+      </c>
+      <c r="N95" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O95" s="44"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A96" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B96" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C96" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D96" s="52">
+        <v>17</v>
+      </c>
+      <c r="E96" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="F96" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="G96" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="H96" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I96" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="J96" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K96" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L96" s="52" t="s">
         <v>241</v>
       </c>
-      <c r="H49" s="7" t="s">
+      <c r="M96" s="52" t="s">
         <v>242</v>
       </c>
-      <c r="I49" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K49" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="L49" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="M49" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="N49" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="O49" s="8" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="5">
-        <v>2024</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50" s="7">
-        <v>16</v>
-      </c>
-      <c r="E50" s="7" t="s">
+      <c r="N96" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O96" s="44"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A97" s="43">
+        <v>2025</v>
+      </c>
+      <c r="B97" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="C97" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D97" s="52">
+        <v>17</v>
+      </c>
+      <c r="E97" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="F50" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="I50" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K50" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L50" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="M50" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="N50" s="9"/>
-      <c r="O50" s="8" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A51" s="24">
-        <v>2024</v>
-      </c>
-      <c r="B51" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="C51" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D51" s="26">
-        <v>17</v>
-      </c>
-      <c r="E51" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="F51" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="G51" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="H51" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="I51" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="J51" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="K51" s="27" t="s">
+      <c r="F97" s="58" t="s">
+        <v>251</v>
+      </c>
+      <c r="G97" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="H97" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I97" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="J97" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K97" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L51" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="M51" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="N51" s="30">
-        <v>9</v>
-      </c>
-      <c r="O51" s="29" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A52" s="5">
-        <v>2024</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D52" s="7">
-        <v>18</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K52" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L52" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="M52" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="N52" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="O52" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A53" s="13">
-        <v>2024</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D53" s="7">
-        <v>18</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K53" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L53" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="M53" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="N53" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="O53" s="8" t="s">
-        <v>259</v>
-      </c>
+      <c r="L97" s="58" t="s">
+        <v>252</v>
+      </c>
+      <c r="M97" s="58" t="s">
+        <v>253</v>
+      </c>
+      <c r="N97" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="O97" s="44"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="O13" r:id="rId1" display="https://www.seg-social.es/wps/portal/wss/internet/EstadisticasPresupuestosEstudios/Estadisticas/EST8/EST10/EST305/c43ad8ea-fe79-4329-ac8e-e5758f3c4d7a/f83fe4aa-2dee-49c5-8317-98d105813796" xr:uid="{61128FB4-53B2-4EAF-8DD6-669E31DEF896}"/>
-    <hyperlink ref="O41" r:id="rId2" display="https://www.seg-social.es/wps/portal/wss/internet/EstadisticasPresupuestosEstudios/Estadisticas/EST8/EST10/EST305/c43ad8ea-fe79-4329-ac8e-e5758f3c4d7a/f83fe4aa-2dee-49c5-8317-98d105813796" xr:uid="{AAB67715-CF03-4157-B01F-134351755964}"/>
+    <hyperlink ref="O12" r:id="rId1" display="https://www.seg-social.es/wps/portal/wss/internet/EstadisticasPresupuestosEstudios/Estadisticas/EST8/EST10/EST305/c43ad8ea-fe79-4329-ac8e-e5758f3c4d7a/f83fe4aa-2dee-49c5-8317-98d105813796" xr:uid="{61128FB4-53B2-4EAF-8DD6-669E31DEF896}"/>
+    <hyperlink ref="O38" r:id="rId2" display="https://www.seg-social.es/wps/portal/wss/internet/EstadisticasPresupuestosEstudios/Estadisticas/EST8/EST10/EST305/c43ad8ea-fe79-4329-ac8e-e5758f3c4d7a/f83fe4aa-2dee-49c5-8317-98d105813796" xr:uid="{AAB67715-CF03-4157-B01F-134351755964}"/>
+    <hyperlink ref="O58" r:id="rId3" xr:uid="{80EEF78C-8D1A-4A33-97CA-F767C517100E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5494,33 +7490,33 @@
   <sheetData>
     <row r="1" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="B1" t="s">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>332</v>
+        <v>306</v>
       </c>
       <c r="E1" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="F1" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="G1" t="s">
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="H1" t="s">
-        <v>329</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -5528,27 +7524,27 @@
       <c r="C2">
         <v>2024</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="29">
         <v>13510</v>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="29">
         <v>12491</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="29">
         <v>26001</v>
       </c>
-      <c r="G2" s="36">
-        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.5195954001769163</v>
-      </c>
-      <c r="H2" s="36">
-        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.4804045998230837</v>
+      <c r="G2" s="30">
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>51.95954001769163</v>
+      </c>
+      <c r="H2" s="30">
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>48.04045998230837</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -5556,27 +7552,27 @@
       <c r="C3">
         <v>2024</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="29">
         <v>12883</v>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="29">
         <v>10390</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="29">
         <v>23273</v>
       </c>
-      <c r="G3" s="36">
-        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.55355991921969661</v>
-      </c>
-      <c r="H3" s="36">
-        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.44644008078030334</v>
+      <c r="G3" s="30">
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>55.355991921969661</v>
+      </c>
+      <c r="H3" s="30">
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>44.644008078030332</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -5584,27 +7580,27 @@
       <c r="C4">
         <v>2024</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="29">
         <v>16076</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="29">
         <v>17411</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="29">
         <v>33487</v>
       </c>
-      <c r="G4" s="36">
-        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.4800668916295876</v>
-      </c>
-      <c r="H4" s="36">
-        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.5199331083704124</v>
+      <c r="G4" s="30">
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>48.006689162958757</v>
+      </c>
+      <c r="H4" s="30">
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>51.993310837041243</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -5612,27 +7608,27 @@
       <c r="C5">
         <v>2024</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="29">
         <v>19391</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="29">
         <v>19604</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="29">
         <v>38995</v>
       </c>
-      <c r="G5" s="36">
-        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.49726888062572122</v>
-      </c>
-      <c r="H5" s="36">
-        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.50273111937427872</v>
+      <c r="G5" s="30">
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>49.726888062572122</v>
+      </c>
+      <c r="H5" s="30">
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>50.273111937427871</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -5640,27 +7636,27 @@
       <c r="C6">
         <v>2024</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="29">
         <v>21886</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="29">
         <v>22453</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="29">
         <v>44339</v>
       </c>
-      <c r="G6" s="36">
-        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.49360608042581022</v>
-      </c>
-      <c r="H6" s="36">
-        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.50639391957418978</v>
+      <c r="G6" s="30">
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>49.360608042581021</v>
+      </c>
+      <c r="H6" s="30">
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>50.639391957418979</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -5668,27 +7664,27 @@
       <c r="C7">
         <v>2024</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="29">
         <v>23792</v>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="29">
         <v>30465</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="29">
         <v>54257</v>
       </c>
-      <c r="G7" s="36">
-        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.43850563060987524</v>
-      </c>
-      <c r="H7" s="36">
-        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.56149436939012476</v>
+      <c r="G7" s="30">
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>43.850563060987525</v>
+      </c>
+      <c r="H7" s="30">
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>56.149436939012475</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -5696,27 +7692,27 @@
       <c r="C8">
         <v>2024</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="29">
         <v>28131</v>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="29">
         <v>56327</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="29">
         <v>84458</v>
       </c>
-      <c r="G8" s="36">
-        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.33307679556702741</v>
-      </c>
-      <c r="H8" s="36">
-        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.66692320443297259</v>
+      <c r="G8" s="30">
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>33.307679556702738</v>
+      </c>
+      <c r="H8" s="30">
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>66.692320443297262</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -5724,27 +7720,27 @@
       <c r="C9">
         <v>2024</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="29">
         <v>33332</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="29">
         <v>68733</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="29">
         <v>102065</v>
       </c>
-      <c r="G9" s="36">
-        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.32657620144025867</v>
-      </c>
-      <c r="H9" s="36">
-        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.67342379855974133</v>
+      <c r="G9" s="30">
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>32.65762014402587</v>
+      </c>
+      <c r="H9" s="30">
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>67.34237985597413</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -5752,27 +7748,27 @@
       <c r="C10">
         <v>2024</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="29">
         <v>26236</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="29">
         <v>35212</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="29">
         <v>61448</v>
       </c>
-      <c r="G10" s="36">
-        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.42696263507355814</v>
-      </c>
-      <c r="H10" s="36">
-        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.57303736492644186</v>
+      <c r="G10" s="30">
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>42.696263507355816</v>
+      </c>
+      <c r="H10" s="30">
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>57.303736492644184</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -5780,27 +7776,27 @@
       <c r="C11">
         <v>2024</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="29">
         <v>26518</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="29">
         <v>13838</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="29">
         <v>40356</v>
       </c>
-      <c r="G11" s="36">
-        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.65710179403310531</v>
-      </c>
-      <c r="H11" s="36">
-        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.34289820596689463</v>
+      <c r="G11" s="30">
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>65.710179403310534</v>
+      </c>
+      <c r="H11" s="30">
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>34.289820596689466</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -5808,27 +7804,27 @@
       <c r="C12">
         <v>2024</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="29">
         <v>14261</v>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="29">
         <v>9723</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="29">
         <v>23984</v>
       </c>
-      <c r="G12" s="36">
-        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.59460473649099399</v>
-      </c>
-      <c r="H12" s="36">
-        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.40539526350900601</v>
+      <c r="G12" s="30">
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>59.460473649099399</v>
+      </c>
+      <c r="H12" s="30">
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>40.539526350900601</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -5836,51 +7832,51 @@
       <c r="C13">
         <v>2024</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="29">
         <v>11948</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="29">
         <v>14062</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="29">
         <v>26010</v>
       </c>
-      <c r="G13" s="36">
-        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.45936178392925797</v>
-      </c>
-      <c r="H13" s="36">
-        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]</f>
-        <v>0.54063821607074203</v>
+      <c r="G13" s="30">
+        <f>Turistas[[#This Row],[1. Turistas extranjeros que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>45.936178392925797</v>
+      </c>
+      <c r="H13" s="30">
+        <f>Turistas[[#This Row],[1. Turistas nacionales que visitaron Calp]]/Turistas[[#This Row],[1. Total turistas]]*100</f>
+        <v>54.063821607074203</v>
       </c>
     </row>
     <row r="19" spans="9:21" x14ac:dyDescent="0.3">
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
-      <c r="S19" s="36"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="36"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="30"/>
+      <c r="U19" s="30"/>
     </row>
     <row r="21" spans="9:21" x14ac:dyDescent="0.3">
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
-      <c r="S21" s="36"/>
-      <c r="T21" s="36"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="30"/>
+      <c r="R21" s="30"/>
+      <c r="S21" s="30"/>
+      <c r="T21" s="30"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -5906,230 +7902,230 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="B1" s="37" t="s">
+      <c r="A1" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="D1" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="E1" s="37" t="s">
-        <v>305</v>
-      </c>
-      <c r="F1" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="G1" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="H1" s="37" t="s">
-        <v>316</v>
+      <c r="C1" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>279</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A2" s="37" t="s">
-        <v>307</v>
-      </c>
-      <c r="B2" s="37">
+      <c r="A2" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="31">
         <v>2024</v>
       </c>
-      <c r="C2" s="37">
+      <c r="C2" s="31">
         <v>14</v>
       </c>
-      <c r="D2" s="37">
+      <c r="D2" s="31">
         <v>3863</v>
       </c>
-      <c r="E2" s="37">
+      <c r="E2" s="31">
         <v>1921</v>
       </c>
-      <c r="F2" s="37"/>
-      <c r="G2" s="38">
+      <c r="F2" s="31"/>
+      <c r="G2" s="32">
         <f>(C2)/C$9</f>
         <v>2.6410111299754765E-3</v>
       </c>
-      <c r="H2" s="38">
+      <c r="H2" s="32">
         <f>D2/D$9</f>
         <v>0.1188067045978779</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A3" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="B3" s="37">
+      <c r="A3" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="B3" s="31">
         <v>2024</v>
       </c>
-      <c r="C3" s="37">
+      <c r="C3" s="31">
         <v>5</v>
       </c>
-      <c r="D3" s="37">
+      <c r="D3" s="31">
         <v>100</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="31">
         <v>50</v>
       </c>
-      <c r="F3" s="37"/>
-      <c r="G3" s="38">
+      <c r="F3" s="31"/>
+      <c r="G3" s="32">
         <f t="shared" ref="G3:G8" si="0">(C3)/C$9</f>
         <v>9.4321826070552727E-4</v>
       </c>
-      <c r="H3" s="38">
+      <c r="H3" s="32">
         <f t="shared" ref="H3:H9" si="1">D3/D$9</f>
         <v>3.0755036137167461E-3</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A4" s="37" t="s">
-        <v>308</v>
-      </c>
-      <c r="B4" s="37">
+      <c r="A4" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" s="31">
         <v>2024</v>
       </c>
-      <c r="C4" s="37">
+      <c r="C4" s="31">
         <v>5267</v>
       </c>
-      <c r="D4" s="37">
+      <c r="D4" s="31">
         <v>26304</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="38">
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="32">
         <f t="shared" si="0"/>
         <v>0.99358611582720247</v>
       </c>
-      <c r="H4" s="38">
+      <c r="H4" s="32">
         <f t="shared" si="1"/>
         <v>0.80898047055205291</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A5" s="37" t="s">
-        <v>309</v>
-      </c>
-      <c r="B5" s="37">
+      <c r="A5" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="B5" s="31">
         <v>2024</v>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="31">
         <v>7</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="31">
         <v>2130</v>
       </c>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37">
+      <c r="E5" s="31"/>
+      <c r="F5" s="31">
         <v>691</v>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="32">
         <f t="shared" si="0"/>
         <v>1.3205055649877383E-3</v>
       </c>
-      <c r="H5" s="38">
+      <c r="H5" s="32">
         <f t="shared" si="1"/>
         <v>6.5508226972166697E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A6" s="37" t="s">
-        <v>310</v>
-      </c>
-      <c r="B6" s="37">
+      <c r="A6" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" s="31">
         <v>2024</v>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="31">
         <v>0</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="31">
         <v>0</v>
       </c>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="38">
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H6" s="38">
+      <c r="H6" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A7" s="37" t="s">
-        <v>311</v>
-      </c>
-      <c r="B7" s="37">
+      <c r="A7" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" s="31">
         <v>2024</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="31">
         <v>0</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="31">
         <v>0</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="38">
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A8" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="B8" s="37">
+      <c r="A8" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="B8" s="31">
         <v>2024</v>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="31">
         <v>8</v>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="31">
         <v>118</v>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="31">
         <v>60</v>
       </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="38">
+      <c r="F8" s="31"/>
+      <c r="G8" s="32">
         <f t="shared" si="0"/>
         <v>1.5091492171288435E-3</v>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="32">
         <f t="shared" si="1"/>
         <v>3.6290942641857603E-3</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A9" s="39" t="s">
-        <v>313</v>
-      </c>
-      <c r="B9" s="37">
+      <c r="A9" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="B9" s="31">
         <v>2024</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="33">
         <v>5301</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="33">
         <v>32515</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="33">
         <v>2031</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="33">
         <v>691</v>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="34">
         <v>1</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="35">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>

--- a/data/DB_Dashboard.xlsx
+++ b/data/DB_Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmari\Desktop\Observatorio Calp\observatorio_calp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3B65B2-054B-40C5-B3D6-725C58CAFD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5ACBA3A-5CD0-45EF-96C2-7259DC644B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{A3E3E45F-D34A-4772-8FFC-37BF922E3DDC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A3E3E45F-D34A-4772-8FFC-37BF922E3DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="344">
   <si>
     <t>Año</t>
   </si>
@@ -276,9 +276,6 @@
   </si>
   <si>
     <t>Departamento de turismo</t>
-  </si>
-  <si>
-    <t>Tasa de ocupación</t>
   </si>
   <si>
     <t>Número total de pernoctaciones de turistas por año ÷ 12 = Número promedio de pernoctaciones de turistas por mes</t>
@@ -1475,6 +1472,12 @@
   <si>
     <t>Consumo de agua por cada pernoctación de un turista nacional en comparación con el consumo de agua por cada noche de un residente</t>
   </si>
+  <si>
+    <t>Gestión de aguas residuales</t>
+  </si>
+  <si>
+    <t>Pernoctaciones</t>
+  </si>
 </sst>
 </file>
 
@@ -1485,7 +1488,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1542,12 +1545,6 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Montserrat"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1715,7 +1712,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1832,27 +1829,20 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -3028,7 +3018,7 @@
         <v>19</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -3055,13 +3045,13 @@
         <v>6</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.4">
@@ -3084,13 +3074,13 @@
         <v>55</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H2" s="21" t="s">
         <v>54</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J2" s="23" t="s">
         <v>11</v>
@@ -3108,7 +3098,7 @@
         <v>1.53</v>
       </c>
       <c r="O2" s="23" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
@@ -3116,7 +3106,7 @@
         <v>2024</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>20</v>
@@ -3131,13 +3121,13 @@
         <v>9</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>11</v>
@@ -3149,10 +3139,10 @@
         <v>14</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O3" s="11"/>
     </row>
@@ -3161,7 +3151,7 @@
         <v>2024</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>20</v>
@@ -3176,13 +3166,13 @@
         <v>15</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>11</v>
@@ -3194,10 +3184,10 @@
         <v>16</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O4" s="8"/>
     </row>
@@ -3206,7 +3196,7 @@
         <v>2024</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>20</v>
@@ -3218,16 +3208,16 @@
         <v>8</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>11</v>
@@ -3236,13 +3226,13 @@
         <v>12</v>
       </c>
       <c r="L5" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="M5" s="7" t="s">
-        <v>328</v>
-      </c>
       <c r="N5" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O5" s="6"/>
     </row>
@@ -3251,7 +3241,7 @@
         <v>2024</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>20</v>
@@ -3263,16 +3253,16 @@
         <v>21</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H6" s="20" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J6" s="20" t="s">
         <v>11</v>
@@ -3281,16 +3271,16 @@
         <v>12</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M6" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N6" s="22">
         <v>52.27</v>
       </c>
       <c r="O6" s="23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
@@ -3298,7 +3288,7 @@
         <v>2024</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>20</v>
@@ -3310,16 +3300,16 @@
         <v>21</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H7" s="20" t="s">
         <v>10</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J7" s="20" t="s">
         <v>11</v>
@@ -3328,16 +3318,16 @@
         <v>12</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M7" s="20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N7" s="22">
         <v>47.73</v>
       </c>
       <c r="O7" s="23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
@@ -3360,25 +3350,25 @@
         <v>59</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H8" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J8" s="20" t="s">
         <v>11</v>
       </c>
       <c r="K8" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="L8" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="L8" s="20" t="s">
-        <v>62</v>
-      </c>
       <c r="M8" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N8" s="26">
         <v>401126</v>
@@ -3390,7 +3380,7 @@
         <v>2024</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>20</v>
@@ -3402,28 +3392,28 @@
         <v>22</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H9" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J9" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="L9" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="K9" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" s="20" t="s">
-        <v>67</v>
-      </c>
       <c r="M9" s="20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N9" s="26">
         <v>4813511</v>
@@ -3435,7 +3425,7 @@
         <v>2024</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>20</v>
@@ -3447,34 +3437,34 @@
         <v>22</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H10" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I10" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="J10" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="K10" s="21" t="s">
+      <c r="L10" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="L10" s="20" t="s">
-        <v>172</v>
-      </c>
       <c r="M10" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N10" s="28">
         <v>120.8</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
@@ -3482,7 +3472,7 @@
         <v>2024</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>20</v>
@@ -3494,34 +3484,34 @@
         <v>22</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H11" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I11" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M11" s="20" t="s">
         <v>74</v>
-      </c>
-      <c r="J11" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="K11" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="L11" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="M11" s="20" t="s">
-        <v>75</v>
       </c>
       <c r="N11" s="28">
         <v>9.75</v>
       </c>
       <c r="O11" s="23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -3529,7 +3519,7 @@
         <v>2024</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>20</v>
@@ -3541,16 +3531,16 @@
         <v>22</v>
       </c>
       <c r="F12" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="H12" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="G12" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="H12" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="I12" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J12" s="20" t="s">
         <v>11</v>
@@ -3559,16 +3549,16 @@
         <v>12</v>
       </c>
       <c r="L12" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M12" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N12" s="28">
         <v>34.97</v>
       </c>
       <c r="O12" s="37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
@@ -3576,7 +3566,7 @@
         <v>2024</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>20</v>
@@ -3588,16 +3578,16 @@
         <v>22</v>
       </c>
       <c r="F13" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="H13" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="G13" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="H13" s="20" t="s">
+      <c r="I13" s="20" t="s">
         <v>177</v>
-      </c>
-      <c r="I13" s="20" t="s">
-        <v>178</v>
       </c>
       <c r="J13" s="20" t="s">
         <v>11</v>
@@ -3606,16 +3596,16 @@
         <v>12</v>
       </c>
       <c r="L13" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="M13" s="20" t="s">
         <v>179</v>
-      </c>
-      <c r="M13" s="20" t="s">
-        <v>180</v>
       </c>
       <c r="N13" s="28">
         <v>11.7</v>
       </c>
       <c r="O13" s="25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
@@ -3623,7 +3613,7 @@
         <v>2024</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>27</v>
@@ -3635,16 +3625,16 @@
         <v>22</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H14" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I14" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J14" s="20" t="s">
         <v>11</v>
@@ -3653,10 +3643,10 @@
         <v>17</v>
       </c>
       <c r="L14" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M14" s="20" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N14" s="28">
         <v>859</v>
@@ -3668,7 +3658,7 @@
         <v>2024</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>27</v>
@@ -3680,16 +3670,16 @@
         <v>22</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H15" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I15" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J15" s="20" t="s">
         <v>11</v>
@@ -3698,10 +3688,10 @@
         <v>17</v>
       </c>
       <c r="L15" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M15" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N15" s="28">
         <v>7</v>
@@ -3713,7 +3703,7 @@
         <v>2024</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>27</v>
@@ -3725,16 +3715,16 @@
         <v>22</v>
       </c>
       <c r="F16" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="G16" s="20" t="s">
         <v>293</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>294</v>
       </c>
       <c r="H16" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J16" s="20" t="s">
         <v>11</v>
@@ -3743,10 +3733,10 @@
         <v>17</v>
       </c>
       <c r="L16" s="20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M16" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N16" s="28">
         <v>4</v>
@@ -3758,7 +3748,7 @@
         <v>2024</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>20</v>
@@ -3770,16 +3760,16 @@
         <v>23</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H17" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J17" s="20" t="s">
         <v>11</v>
@@ -3788,16 +3778,16 @@
         <v>17</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M17" s="20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N17" s="26">
         <v>247964</v>
       </c>
       <c r="O17" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
@@ -3805,7 +3795,7 @@
         <v>2024</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>20</v>
@@ -3817,16 +3807,16 @@
         <v>23</v>
       </c>
       <c r="F18" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="G18" s="20" t="s">
         <v>315</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>316</v>
       </c>
       <c r="H18" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I18" s="20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J18" s="20" t="s">
         <v>11</v>
@@ -3835,16 +3825,16 @@
         <v>17</v>
       </c>
       <c r="L18" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="M18" s="20" t="s">
         <v>318</v>
-      </c>
-      <c r="M18" s="20" t="s">
-        <v>319</v>
       </c>
       <c r="N18" s="26">
         <v>310709</v>
       </c>
       <c r="O18" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.4">
@@ -3852,7 +3842,7 @@
         <v>2024</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>20</v>
@@ -3864,34 +3854,34 @@
         <v>24</v>
       </c>
       <c r="F19" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="H19" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="O19" s="8" t="s">
         <v>234</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
@@ -3899,7 +3889,7 @@
         <v>2024</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>20</v>
@@ -3908,37 +3898,37 @@
         <v>6</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>25</v>
+        <v>342</v>
       </c>
       <c r="F20" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="H20" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="G20" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="H20" s="20" t="s">
-        <v>137</v>
-      </c>
       <c r="I20" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J20" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K20" s="21" t="s">
         <v>12</v>
       </c>
       <c r="L20" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M20" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N20" s="22">
         <v>68.89</v>
       </c>
       <c r="O20" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="18" x14ac:dyDescent="0.4">
@@ -3946,46 +3936,46 @@
         <v>2024</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" s="20" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H21" s="20" t="s">
         <v>54</v>
       </c>
       <c r="I21" s="20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J21" s="20" t="s">
         <v>11</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L21" s="20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M21" s="20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N21" s="22">
         <v>6.59</v>
       </c>
       <c r="O21" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="18" x14ac:dyDescent="0.4">
@@ -3993,46 +3983,46 @@
         <v>2024</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H22" s="20" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K22" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="L22" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="J22" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="K22" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="L22" s="20" t="s">
-        <v>147</v>
-      </c>
       <c r="M22" s="20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N22" s="22">
         <v>12.02</v>
       </c>
       <c r="O22" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="18" x14ac:dyDescent="0.4">
@@ -4040,46 +4030,46 @@
         <v>2024</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" s="20" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H23" s="20" t="s">
         <v>54</v>
       </c>
       <c r="I23" s="20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J23" s="20" t="s">
         <v>11</v>
       </c>
       <c r="K23" s="21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L23" s="20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M23" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N23" s="22">
         <v>9.56</v>
       </c>
       <c r="O23" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.4">
@@ -4093,7 +4083,7 @@
         <v>20</v>
       </c>
       <c r="D24" s="20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>18</v>
@@ -4102,7 +4092,7 @@
         <v>35</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H24" s="20" t="s">
         <v>36</v>
@@ -4120,7 +4110,7 @@
         <v>43</v>
       </c>
       <c r="M24" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N24" s="22">
         <v>36.78</v>
@@ -4140,7 +4130,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" s="20" t="s">
         <v>18</v>
@@ -4149,7 +4139,7 @@
         <v>35</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H25" s="20" t="s">
         <v>36</v>
@@ -4167,7 +4157,7 @@
         <v>42</v>
       </c>
       <c r="M25" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N25" s="22">
         <v>34.18</v>
@@ -4181,13 +4171,13 @@
         <v>2024</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="20" t="s">
         <v>18</v>
@@ -4196,7 +4186,7 @@
         <v>40</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H26" s="20" t="s">
         <v>36</v>
@@ -4228,22 +4218,22 @@
         <v>2024</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D27" s="20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" s="20" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="40" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H27" s="20" t="s">
         <v>36</v>
@@ -4275,22 +4265,22 @@
         <v>2024</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D28" s="20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" s="20" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="G28" s="20" t="s">
         <v>311</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>312</v>
       </c>
       <c r="H28" s="20" t="s">
         <v>36</v>
@@ -4305,7 +4295,7 @@
         <v>41</v>
       </c>
       <c r="L28" s="20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M28" s="20" t="s">
         <v>49</v>
@@ -4322,46 +4312,46 @@
         <v>2024</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D29" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>26</v>
       </c>
       <c r="F29" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>244</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>245</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>60</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K29" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="L29" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="L29" s="7" t="s">
+      <c r="M29" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="M29" s="7" t="s">
-        <v>248</v>
-      </c>
       <c r="N29" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O29" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.4">
@@ -4369,28 +4359,28 @@
         <v>2024</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D30" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>60</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J30" s="7" t="s">
         <v>11</v>
@@ -4399,16 +4389,16 @@
         <v>17</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.4">
@@ -4416,46 +4406,46 @@
         <v>2024</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D31" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>26</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>60</v>
       </c>
       <c r="I31" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K31" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="J31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K31" s="8" t="s">
+      <c r="L31" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="L31" s="7" t="s">
+      <c r="M31" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="M31" s="7" t="s">
+      <c r="N31" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="O31" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="O31" s="6" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.4">
@@ -4463,7 +4453,7 @@
         <v>2024</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C32" s="20" t="s">
         <v>27</v>
@@ -4475,16 +4465,16 @@
         <v>28</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H32" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I32" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J32" s="20" t="s">
         <v>11</v>
@@ -4493,16 +4483,16 @@
         <v>12</v>
       </c>
       <c r="L32" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M32" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N32" s="22">
         <v>82.11</v>
       </c>
       <c r="O32" s="23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.4">
@@ -4510,7 +4500,7 @@
         <v>2024</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C33" s="20" t="s">
         <v>27</v>
@@ -4522,16 +4512,16 @@
         <v>28</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H33" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I33" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J33" s="20" t="s">
         <v>11</v>
@@ -4540,16 +4530,16 @@
         <v>12</v>
       </c>
       <c r="L33" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M33" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N33" s="22">
         <v>17.89</v>
       </c>
       <c r="O33" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.4">
@@ -4557,7 +4547,7 @@
         <v>2024</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>27</v>
@@ -4566,31 +4556,31 @@
         <v>11</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J34" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N34" s="42">
         <v>581472128.79999995</v>
@@ -4602,7 +4592,7 @@
         <v>2024</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>27</v>
@@ -4611,19 +4601,19 @@
         <v>12</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F35" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="G35" s="7" t="s">
         <v>334</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>335</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J35" s="7" t="s">
         <v>11</v>
@@ -4632,16 +4622,16 @@
         <v>12</v>
       </c>
       <c r="L35" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="M35" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="M35" s="7" t="s">
-        <v>338</v>
-      </c>
       <c r="N35" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.4">
@@ -4649,7 +4639,7 @@
         <v>2024</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C36" s="20" t="s">
         <v>27</v>
@@ -4661,34 +4651,34 @@
         <v>29</v>
       </c>
       <c r="F36" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="I36" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K36" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="G36" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="H36" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="I36" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="J36" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="K36" s="21" t="s">
+      <c r="L36" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="L36" s="20" t="s">
-        <v>85</v>
-      </c>
       <c r="M36" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N36" s="22">
         <v>49.16</v>
       </c>
       <c r="O36" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.4">
@@ -4696,7 +4686,7 @@
         <v>2024</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C37" s="20" t="s">
         <v>27</v>
@@ -4708,16 +4698,16 @@
         <v>29</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I37" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J37" s="20" t="s">
         <v>11</v>
@@ -4726,16 +4716,16 @@
         <v>12</v>
       </c>
       <c r="L37" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M37" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N37" s="22">
         <v>37.65</v>
       </c>
       <c r="O37" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.4">
@@ -4743,7 +4733,7 @@
         <v>2024</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C38" s="20" t="s">
         <v>27</v>
@@ -4755,16 +4745,16 @@
         <v>29</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I38" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J38" s="20" t="s">
         <v>11</v>
@@ -4773,16 +4763,16 @@
         <v>12</v>
       </c>
       <c r="L38" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M38" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N38" s="22">
         <v>32.590000000000003</v>
       </c>
       <c r="O38" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.4">
@@ -4790,7 +4780,7 @@
         <v>2024</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C39" s="20" t="s">
         <v>27</v>
@@ -4802,16 +4792,16 @@
         <v>29</v>
       </c>
       <c r="F39" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="H39" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="G39" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="H39" s="20" t="s">
+      <c r="I39" s="20" t="s">
         <v>100</v>
-      </c>
-      <c r="I39" s="20" t="s">
-        <v>101</v>
       </c>
       <c r="J39" s="20" t="s">
         <v>11</v>
@@ -4820,16 +4810,16 @@
         <v>12</v>
       </c>
       <c r="L39" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="M39" s="20" t="s">
         <v>103</v>
-      </c>
-      <c r="M39" s="20" t="s">
-        <v>104</v>
       </c>
       <c r="N39" s="24">
         <v>70</v>
       </c>
       <c r="O39" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.4">
@@ -4837,7 +4827,7 @@
         <v>2024</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C40" s="20" t="s">
         <v>27</v>
@@ -4849,16 +4839,16 @@
         <v>30</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H40" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="I40" s="20" t="s">
         <v>177</v>
-      </c>
-      <c r="I40" s="20" t="s">
-        <v>178</v>
       </c>
       <c r="J40" s="20" t="s">
         <v>11</v>
@@ -4867,16 +4857,16 @@
         <v>12</v>
       </c>
       <c r="L40" s="20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M40" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N40" s="24">
         <v>18</v>
       </c>
       <c r="O40" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.4">
@@ -4884,7 +4874,7 @@
         <v>2024</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C41" s="20" t="s">
         <v>27</v>
@@ -4896,16 +4886,16 @@
         <v>31</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H41" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I41" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J41" s="20" t="s">
         <v>11</v>
@@ -4914,16 +4904,16 @@
         <v>12</v>
       </c>
       <c r="L41" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N41" s="24">
         <v>94</v>
       </c>
       <c r="O41" s="23" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.4">
@@ -4931,7 +4921,7 @@
         <v>2024</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C42" s="20" t="s">
         <v>27</v>
@@ -4943,16 +4933,16 @@
         <v>31</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G42" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H42" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I42" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J42" s="20" t="s">
         <v>11</v>
@@ -4961,16 +4951,16 @@
         <v>12</v>
       </c>
       <c r="L42" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N42" s="24">
         <v>6</v>
       </c>
       <c r="O42" s="23" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.4">
@@ -4978,7 +4968,7 @@
         <v>2024</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C43" s="20" t="s">
         <v>27</v>
@@ -4990,32 +4980,32 @@
         <v>31</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H43" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I43" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J43" s="20" t="s">
         <v>11</v>
       </c>
       <c r="K43" s="21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L43" s="20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M43" s="20"/>
       <c r="N43" s="26">
         <v>737000000</v>
       </c>
       <c r="O43" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.4">
@@ -5023,7 +5013,7 @@
         <v>2024</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C44" s="20" t="s">
         <v>27</v>
@@ -5035,34 +5025,34 @@
         <v>31</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H44" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I44" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J44" s="20" t="s">
         <v>11</v>
       </c>
       <c r="K44" s="21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L44" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M44" s="20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N44" s="26">
         <v>575000000</v>
       </c>
       <c r="O44" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.4">
@@ -5070,7 +5060,7 @@
         <v>2024</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>27</v>
@@ -5082,34 +5072,34 @@
         <v>31</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H45" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I45" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J45" s="20" t="s">
         <v>11</v>
       </c>
       <c r="K45" s="21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L45" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M45" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N45" s="26">
         <v>162000000</v>
       </c>
       <c r="O45" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.4">
@@ -5117,7 +5107,7 @@
         <v>2024</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C46" s="20" t="s">
         <v>27</v>
@@ -5129,16 +5119,16 @@
         <v>32</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H46" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="I46" s="20" t="s">
         <v>177</v>
-      </c>
-      <c r="I46" s="20" t="s">
-        <v>178</v>
       </c>
       <c r="J46" s="20" t="s">
         <v>11</v>
@@ -5147,10 +5137,10 @@
         <v>12</v>
       </c>
       <c r="L46" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="M46" s="20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N46" s="24">
         <v>9</v>
@@ -5164,7 +5154,7 @@
         <v>2024</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>27</v>
@@ -5176,16 +5166,16 @@
         <v>33</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G47" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="H47" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="H47" s="7" t="s">
-        <v>238</v>
-      </c>
       <c r="I47" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>11</v>
@@ -5194,16 +5184,16 @@
         <v>17</v>
       </c>
       <c r="L47" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="M47" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="M47" s="12" t="s">
-        <v>324</v>
-      </c>
       <c r="N47" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O47" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.4">
@@ -5211,7 +5201,7 @@
         <v>2024</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>27</v>
@@ -5223,16 +5213,16 @@
         <v>33</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H48" s="7" t="s">
         <v>60</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J48" s="7" t="s">
         <v>11</v>
@@ -5241,16 +5231,16 @@
         <v>12</v>
       </c>
       <c r="L48" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="M48" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="M48" s="7" t="s">
+      <c r="N48" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="O48" s="8" t="s">
         <v>242</v>
-      </c>
-      <c r="N48" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="O48" s="8" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.4">
@@ -5258,7 +5248,7 @@
         <v>2024</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>27</v>
@@ -5270,16 +5260,16 @@
         <v>33</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>60</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J49" s="7" t="s">
         <v>11</v>
@@ -5288,60 +5278,60 @@
         <v>12</v>
       </c>
       <c r="L49" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="M49" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="M49" s="15" t="s">
-        <v>253</v>
-      </c>
       <c r="N49" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O49" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A50" s="43">
         <v>2025</v>
       </c>
-      <c r="B50" s="51" t="s">
+      <c r="B50" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="C50" s="52" t="s">
+      <c r="C50" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D50" s="52">
+      <c r="D50" s="50">
         <v>1</v>
       </c>
-      <c r="E50" s="53" t="s">
+      <c r="E50" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="53" t="s">
+      <c r="F50" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="G50" s="53" t="s">
-        <v>205</v>
-      </c>
-      <c r="H50" s="54" t="s">
+      <c r="G50" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="H50" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="I50" s="54" t="s">
-        <v>330</v>
-      </c>
-      <c r="J50" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="K50" s="54" t="s">
+      <c r="I50" s="52" t="s">
+        <v>329</v>
+      </c>
+      <c r="J50" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="K50" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="L50" s="54" t="s">
+      <c r="L50" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="M50" s="54" t="s">
+      <c r="M50" s="52" t="s">
         <v>57</v>
       </c>
       <c r="N50" s="45" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O50" s="46"/>
     </row>
@@ -5349,44 +5339,44 @@
       <c r="A51" s="43">
         <v>2025</v>
       </c>
-      <c r="B51" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C51" s="52" t="s">
+      <c r="B51" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D51" s="52">
+      <c r="D51" s="50">
         <v>1</v>
       </c>
-      <c r="E51" s="52" t="s">
+      <c r="E51" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="52" t="s">
+      <c r="F51" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G51" s="52" t="s">
-        <v>209</v>
-      </c>
-      <c r="H51" s="52" t="s">
+      <c r="G51" s="50" t="s">
+        <v>208</v>
+      </c>
+      <c r="H51" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="I51" s="52" t="s">
-        <v>227</v>
-      </c>
-      <c r="J51" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K51" s="54" t="s">
+      <c r="I51" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="J51" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K51" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="L51" s="52" t="s">
+      <c r="L51" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="M51" s="52" t="s">
-        <v>113</v>
+      <c r="M51" s="50" t="s">
+        <v>112</v>
       </c>
       <c r="N51" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O51" s="44"/>
     </row>
@@ -5394,44 +5384,44 @@
       <c r="A52" s="43">
         <v>2025</v>
       </c>
-      <c r="B52" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C52" s="52" t="s">
+      <c r="B52" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C52" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D52" s="52">
+      <c r="D52" s="50">
         <v>1</v>
       </c>
-      <c r="E52" s="52" t="s">
+      <c r="E52" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="52" t="s">
+      <c r="F52" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="G52" s="52" t="s">
-        <v>210</v>
-      </c>
-      <c r="H52" s="52" t="s">
+      <c r="G52" s="50" t="s">
+        <v>209</v>
+      </c>
+      <c r="H52" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="I52" s="52" t="s">
-        <v>227</v>
-      </c>
-      <c r="J52" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K52" s="54" t="s">
+      <c r="I52" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="J52" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K52" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="L52" s="52" t="s">
+      <c r="L52" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="M52" s="52" t="s">
-        <v>112</v>
+      <c r="M52" s="50" t="s">
+        <v>111</v>
       </c>
       <c r="N52" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O52" s="44"/>
     </row>
@@ -5439,44 +5429,44 @@
       <c r="A53" s="43">
         <v>2025</v>
       </c>
-      <c r="B53" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C53" s="52" t="s">
+      <c r="B53" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D53" s="52">
+      <c r="D53" s="50">
         <v>1</v>
       </c>
-      <c r="E53" s="52" t="s">
+      <c r="E53" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="52" t="s">
+      <c r="F53" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="G53" s="50" t="s">
+        <v>259</v>
+      </c>
+      <c r="H53" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="I53" s="50" t="s">
+        <v>324</v>
+      </c>
+      <c r="J53" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K53" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="L53" s="53" t="s">
         <v>326</v>
       </c>
-      <c r="G53" s="52" t="s">
-        <v>260</v>
-      </c>
-      <c r="H53" s="52" t="s">
-        <v>10</v>
-      </c>
-      <c r="I53" s="52" t="s">
-        <v>325</v>
-      </c>
-      <c r="J53" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K53" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="L53" s="55" t="s">
+      <c r="M53" s="50" t="s">
         <v>327</v>
       </c>
-      <c r="M53" s="52" t="s">
-        <v>328</v>
-      </c>
       <c r="N53" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O53" s="44"/>
     </row>
@@ -5484,44 +5474,44 @@
       <c r="A54" s="43">
         <v>2025</v>
       </c>
-      <c r="B54" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="C54" s="52" t="s">
+      <c r="B54" s="44" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D54" s="52">
+      <c r="D54" s="50">
         <v>2</v>
       </c>
-      <c r="E54" s="52" t="s">
+      <c r="E54" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="F54" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="G54" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="H54" s="52" t="s">
+      <c r="F54" s="50" t="s">
+        <v>185</v>
+      </c>
+      <c r="G54" s="50" t="s">
+        <v>203</v>
+      </c>
+      <c r="H54" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="I54" s="52" t="s">
-        <v>182</v>
-      </c>
-      <c r="J54" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K54" s="54" t="s">
+      <c r="I54" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="J54" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K54" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="L54" s="52" t="s">
-        <v>155</v>
-      </c>
-      <c r="M54" s="52" t="s">
-        <v>157</v>
+      <c r="L54" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="M54" s="50" t="s">
+        <v>156</v>
       </c>
       <c r="N54" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O54" s="44"/>
     </row>
@@ -5529,44 +5519,44 @@
       <c r="A55" s="43">
         <v>2025</v>
       </c>
-      <c r="B55" s="51" t="s">
-        <v>183</v>
-      </c>
-      <c r="C55" s="52" t="s">
+      <c r="B55" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="C55" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D55" s="52">
+      <c r="D55" s="50">
         <v>2</v>
       </c>
-      <c r="E55" s="52" t="s">
+      <c r="E55" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="F55" s="52" t="s">
-        <v>185</v>
-      </c>
-      <c r="G55" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="H55" s="52" t="s">
+      <c r="F55" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="G55" s="50" t="s">
+        <v>203</v>
+      </c>
+      <c r="H55" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="I55" s="52" t="s">
-        <v>182</v>
-      </c>
-      <c r="J55" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K55" s="54" t="s">
+      <c r="I55" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="J55" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K55" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="L55" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="M55" s="52" t="s">
-        <v>158</v>
+      <c r="L55" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="M55" s="50" t="s">
+        <v>157</v>
       </c>
       <c r="N55" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O55" s="44"/>
     </row>
@@ -5574,44 +5564,44 @@
       <c r="A56" s="43">
         <v>2025</v>
       </c>
-      <c r="B56" s="51" t="s">
+      <c r="B56" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="C56" s="52" t="s">
+      <c r="C56" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D56" s="52">
+      <c r="D56" s="50">
         <v>3</v>
       </c>
-      <c r="E56" s="52" t="s">
+      <c r="E56" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F56" s="52" t="s">
+      <c r="F56" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="G56" s="52" t="s">
-        <v>203</v>
-      </c>
-      <c r="H56" s="52" t="s">
+      <c r="G56" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="H56" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I56" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="J56" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K56" s="56" t="s">
+      <c r="I56" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="J56" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K56" s="55" t="s">
+        <v>343</v>
+      </c>
+      <c r="L56" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="L56" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="M56" s="52" t="s">
-        <v>111</v>
+      <c r="M56" s="50" t="s">
+        <v>110</v>
       </c>
       <c r="N56" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O56" s="44"/>
     </row>
@@ -5619,44 +5609,44 @@
       <c r="A57" s="43">
         <v>2025</v>
       </c>
-      <c r="B57" s="51" t="s">
+      <c r="B57" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="50">
+        <v>3</v>
+      </c>
+      <c r="E57" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F57" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="G57" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="H57" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I57" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="J57" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="C57" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="D57" s="52">
-        <v>3</v>
-      </c>
-      <c r="E57" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="F57" s="52" t="s">
-        <v>64</v>
-      </c>
-      <c r="G57" s="52" t="s">
-        <v>203</v>
-      </c>
-      <c r="H57" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="I57" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="J57" s="52" t="s">
+      <c r="K57" s="55" t="s">
+        <v>343</v>
+      </c>
+      <c r="L57" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="K57" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="L57" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="M57" s="52" t="s">
-        <v>110</v>
+      <c r="M57" s="50" t="s">
+        <v>109</v>
       </c>
       <c r="N57" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O57" s="44"/>
     </row>
@@ -5665,90 +5655,90 @@
         <v>2025</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C58" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D58" s="50">
+      <c r="D58" s="20">
         <v>3</v>
       </c>
-      <c r="E58" s="50" t="s">
+      <c r="E58" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="F58" s="50" t="s">
+      <c r="F58" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="G58" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H58" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I58" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G58" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="H58" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="I58" s="50" t="s">
+      <c r="J58" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K58" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="J58" s="50" t="s">
-        <v>11</v>
-      </c>
-      <c r="K58" s="21" t="s">
+      <c r="L58" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="L58" s="50" t="s">
-        <v>172</v>
-      </c>
-      <c r="M58" s="50" t="s">
-        <v>174</v>
+      <c r="M58" s="20" t="s">
+        <v>173</v>
       </c>
       <c r="N58" s="22">
         <v>126.5</v>
       </c>
       <c r="O58" s="49" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A59" s="43">
         <v>2025</v>
       </c>
-      <c r="B59" s="51" t="s">
+      <c r="B59" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="50">
+        <v>3</v>
+      </c>
+      <c r="E59" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F59" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="G59" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="H59" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I59" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="J59" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K59" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="C59" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="D59" s="52">
-        <v>3</v>
-      </c>
-      <c r="E59" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="F59" s="52" t="s">
-        <v>72</v>
-      </c>
-      <c r="G59" s="52" t="s">
-        <v>202</v>
-      </c>
-      <c r="H59" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="I59" s="52" t="s">
+      <c r="L59" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="M59" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="J59" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K59" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="L59" s="52" t="s">
-        <v>71</v>
-      </c>
-      <c r="M59" s="52" t="s">
-        <v>75</v>
-      </c>
       <c r="N59" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O59" s="44"/>
     </row>
@@ -5756,44 +5746,44 @@
       <c r="A60" s="43">
         <v>2025</v>
       </c>
-      <c r="B60" s="51" t="s">
+      <c r="B60" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" s="50">
+        <v>3</v>
+      </c>
+      <c r="E60" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F60" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="C60" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="D60" s="52">
-        <v>3</v>
-      </c>
-      <c r="E60" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="F60" s="52" t="s">
+      <c r="G60" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="H60" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="G60" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="H60" s="52" t="s">
+      <c r="I60" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="J60" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K60" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="L60" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="M60" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="I60" s="52" t="s">
-        <v>78</v>
-      </c>
-      <c r="J60" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K60" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="L60" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="M60" s="52" t="s">
-        <v>79</v>
-      </c>
       <c r="N60" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O60" s="44"/>
     </row>
@@ -5801,44 +5791,44 @@
       <c r="A61" s="43">
         <v>2025</v>
       </c>
-      <c r="B61" s="51" t="s">
+      <c r="B61" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="C61" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" s="50">
+        <v>3</v>
+      </c>
+      <c r="E61" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F61" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="C61" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="D61" s="52">
-        <v>3</v>
-      </c>
-      <c r="E61" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="F61" s="52" t="s">
+      <c r="G61" s="50" t="s">
+        <v>199</v>
+      </c>
+      <c r="H61" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="G61" s="52" t="s">
-        <v>200</v>
-      </c>
-      <c r="H61" s="52" t="s">
+      <c r="I61" s="50" t="s">
         <v>177</v>
       </c>
-      <c r="I61" s="52" t="s">
+      <c r="J61" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K61" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="L61" s="50" t="s">
         <v>178</v>
       </c>
-      <c r="J61" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K61" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="L61" s="52" t="s">
+      <c r="M61" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="M61" s="52" t="s">
-        <v>180</v>
-      </c>
       <c r="N61" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O61" s="44"/>
     </row>
@@ -5846,44 +5836,44 @@
       <c r="A62" s="43">
         <v>2025</v>
       </c>
-      <c r="B62" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C62" s="52" t="s">
+      <c r="B62" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D62" s="52">
+      <c r="D62" s="50">
         <v>3</v>
       </c>
-      <c r="E62" s="52" t="s">
+      <c r="E62" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F62" s="52" t="s">
-        <v>291</v>
-      </c>
-      <c r="G62" s="52" t="s">
+      <c r="F62" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="G62" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="H62" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I62" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="J62" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K62" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="L62" s="50" t="s">
         <v>294</v>
       </c>
-      <c r="H62" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="I62" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="J62" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K62" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="L62" s="52" t="s">
-        <v>295</v>
-      </c>
-      <c r="M62" s="52" t="s">
-        <v>298</v>
+      <c r="M62" s="50" t="s">
+        <v>297</v>
       </c>
       <c r="N62" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O62" s="44"/>
     </row>
@@ -5891,44 +5881,44 @@
       <c r="A63" s="43">
         <v>2025</v>
       </c>
-      <c r="B63" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C63" s="52" t="s">
+      <c r="B63" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C63" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D63" s="52">
+      <c r="D63" s="50">
         <v>3</v>
       </c>
-      <c r="E63" s="52" t="s">
+      <c r="E63" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F63" s="52" t="s">
-        <v>292</v>
-      </c>
-      <c r="G63" s="52" t="s">
-        <v>294</v>
-      </c>
-      <c r="H63" s="52" t="s">
+      <c r="F63" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="G63" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="H63" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I63" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="J63" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K63" s="54" t="s">
+      <c r="I63" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="J63" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K63" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="L63" s="52" t="s">
-        <v>296</v>
-      </c>
-      <c r="M63" s="52" t="s">
-        <v>299</v>
+      <c r="L63" s="50" t="s">
+        <v>295</v>
+      </c>
+      <c r="M63" s="50" t="s">
+        <v>298</v>
       </c>
       <c r="N63" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O63" s="44"/>
     </row>
@@ -5936,44 +5926,44 @@
       <c r="A64" s="43">
         <v>2025</v>
       </c>
-      <c r="B64" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C64" s="52" t="s">
+      <c r="B64" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C64" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="52">
+      <c r="D64" s="50">
         <v>3</v>
       </c>
-      <c r="E64" s="52" t="s">
+      <c r="E64" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F64" s="52" t="s">
+      <c r="F64" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="G64" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="G64" s="52" t="s">
-        <v>294</v>
-      </c>
-      <c r="H64" s="52" t="s">
+      <c r="H64" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I64" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="J64" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K64" s="54" t="s">
+      <c r="I64" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="J64" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K64" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="L64" s="52" t="s">
-        <v>297</v>
-      </c>
-      <c r="M64" s="52" t="s">
-        <v>300</v>
+      <c r="L64" s="50" t="s">
+        <v>296</v>
+      </c>
+      <c r="M64" s="50" t="s">
+        <v>299</v>
       </c>
       <c r="N64" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O64" s="44"/>
     </row>
@@ -5981,44 +5971,44 @@
       <c r="A65" s="43">
         <v>2025</v>
       </c>
-      <c r="B65" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C65" s="52" t="s">
+      <c r="B65" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C65" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="52">
+      <c r="D65" s="50">
         <v>4</v>
       </c>
-      <c r="E65" s="52" t="s">
+      <c r="E65" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="F65" s="52" t="s">
-        <v>314</v>
-      </c>
-      <c r="G65" s="52" t="s">
+      <c r="F65" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="G65" s="50" t="s">
+        <v>315</v>
+      </c>
+      <c r="H65" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I65" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="J65" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K65" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="L65" s="50" t="s">
         <v>316</v>
       </c>
-      <c r="H65" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="I65" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="J65" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K65" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="L65" s="52" t="s">
-        <v>317</v>
-      </c>
-      <c r="M65" s="52" t="s">
-        <v>320</v>
+      <c r="M65" s="50" t="s">
+        <v>319</v>
       </c>
       <c r="N65" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O65" s="44"/>
     </row>
@@ -6026,44 +6016,44 @@
       <c r="A66" s="43">
         <v>2025</v>
       </c>
-      <c r="B66" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C66" s="52" t="s">
+      <c r="B66" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C66" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D66" s="52">
+      <c r="D66" s="50">
         <v>4</v>
       </c>
-      <c r="E66" s="52" t="s">
+      <c r="E66" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="F66" s="52" t="s">
+      <c r="F66" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="G66" s="50" t="s">
         <v>315</v>
       </c>
-      <c r="G66" s="52" t="s">
-        <v>316</v>
-      </c>
-      <c r="H66" s="52" t="s">
+      <c r="H66" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I66" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="J66" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K66" s="54" t="s">
+      <c r="I66" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="J66" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K66" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="L66" s="52" t="s">
+      <c r="L66" s="50" t="s">
+        <v>317</v>
+      </c>
+      <c r="M66" s="50" t="s">
         <v>318</v>
       </c>
-      <c r="M66" s="52" t="s">
-        <v>319</v>
-      </c>
       <c r="N66" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O66" s="44"/>
     </row>
@@ -6071,44 +6061,44 @@
       <c r="A67" s="43">
         <v>2025</v>
       </c>
-      <c r="B67" s="51" t="s">
+      <c r="B67" s="44" t="s">
+        <v>231</v>
+      </c>
+      <c r="C67" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67" s="50">
+        <v>5</v>
+      </c>
+      <c r="E67" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" s="50" t="s">
         <v>232</v>
       </c>
-      <c r="C67" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="D67" s="52">
-        <v>5</v>
-      </c>
-      <c r="E67" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="F67" s="52" t="s">
+      <c r="G67" s="50" t="s">
         <v>233</v>
       </c>
-      <c r="G67" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="H67" s="52" t="s">
+      <c r="H67" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="I67" s="50" t="s">
         <v>228</v>
       </c>
-      <c r="I67" s="52" t="s">
+      <c r="J67" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K67" s="51" t="s">
+        <v>230</v>
+      </c>
+      <c r="L67" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="J67" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K67" s="53" t="s">
-        <v>231</v>
-      </c>
-      <c r="L67" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="M67" s="52" t="s">
-        <v>236</v>
+      <c r="M67" s="50" t="s">
+        <v>235</v>
       </c>
       <c r="N67" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O67" s="44"/>
     </row>
@@ -6116,44 +6106,44 @@
       <c r="A68" s="43">
         <v>2025</v>
       </c>
-      <c r="B68" s="51" t="s">
+      <c r="B68" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" s="50">
+        <v>6</v>
+      </c>
+      <c r="E68" s="50" t="s">
+        <v>342</v>
+      </c>
+      <c r="F68" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="C68" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="D68" s="52">
-        <v>6</v>
-      </c>
-      <c r="E68" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="F68" s="52" t="s">
+      <c r="G68" s="50" t="s">
+        <v>198</v>
+      </c>
+      <c r="H68" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="G68" s="52" t="s">
-        <v>199</v>
-      </c>
-      <c r="H68" s="52" t="s">
+      <c r="I68" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="J68" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="K68" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="L68" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="M68" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="I68" s="52" t="s">
-        <v>137</v>
-      </c>
-      <c r="J68" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="K68" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="L68" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="M68" s="52" t="s">
-        <v>138</v>
-      </c>
       <c r="N68" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O68" s="44"/>
     </row>
@@ -6161,44 +6151,44 @@
       <c r="A69" s="43">
         <v>2025</v>
       </c>
-      <c r="B69" s="51" t="s">
+      <c r="B69" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="C69" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D69" s="50">
+        <v>7</v>
+      </c>
+      <c r="E69" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="C69" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="D69" s="52">
-        <v>6</v>
-      </c>
-      <c r="E69" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="F69" s="52" t="s">
+      <c r="G69" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="H69" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="I69" s="50" t="s">
         <v>145</v>
       </c>
-      <c r="G69" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="H69" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="I69" s="52" t="s">
-        <v>146</v>
-      </c>
-      <c r="J69" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K69" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="L69" s="52" t="s">
+      <c r="J69" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K69" s="52" t="s">
         <v>149</v>
       </c>
-      <c r="M69" s="52" t="s">
-        <v>152</v>
+      <c r="L69" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="M69" s="50" t="s">
+        <v>151</v>
       </c>
       <c r="N69" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O69" s="44"/>
     </row>
@@ -6206,44 +6196,44 @@
       <c r="A70" s="43">
         <v>2025</v>
       </c>
-      <c r="B70" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="C70" s="52" t="s">
+      <c r="B70" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="C70" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D70" s="52">
-        <v>6</v>
-      </c>
-      <c r="E70" s="52" t="s">
+      <c r="D70" s="50">
+        <v>7</v>
+      </c>
+      <c r="E70" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="F70" s="52" t="s">
-        <v>341</v>
-      </c>
-      <c r="G70" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="H70" s="52" t="s">
+      <c r="F70" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="G70" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="H70" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="I70" s="52" t="s">
+      <c r="I70" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="J70" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K70" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="L70" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="J70" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K70" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="L70" s="52" t="s">
-        <v>147</v>
-      </c>
-      <c r="M70" s="52" t="s">
-        <v>153</v>
+      <c r="M70" s="50" t="s">
+        <v>152</v>
       </c>
       <c r="N70" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O70" s="44"/>
     </row>
@@ -6251,44 +6241,44 @@
       <c r="A71" s="43">
         <v>2025</v>
       </c>
-      <c r="B71" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="C71" s="52" t="s">
+      <c r="B71" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="C71" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D71" s="52">
-        <v>6</v>
-      </c>
-      <c r="E71" s="52" t="s">
+      <c r="D71" s="50">
+        <v>7</v>
+      </c>
+      <c r="E71" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="F71" s="52" t="s">
-        <v>342</v>
-      </c>
-      <c r="G71" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="H71" s="52" t="s">
+      <c r="F71" s="50" t="s">
+        <v>341</v>
+      </c>
+      <c r="G71" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="H71" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="I71" s="52" t="s">
-        <v>146</v>
-      </c>
-      <c r="J71" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K71" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="L71" s="52" t="s">
-        <v>148</v>
-      </c>
-      <c r="M71" s="52" t="s">
-        <v>154</v>
+      <c r="I71" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="J71" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K71" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="L71" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="M71" s="50" t="s">
+        <v>153</v>
       </c>
       <c r="N71" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O71" s="44"/>
     </row>
@@ -6296,44 +6286,44 @@
       <c r="A72" s="43">
         <v>2025</v>
       </c>
-      <c r="B72" s="51" t="s">
+      <c r="B72" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="C72" s="52" t="s">
+      <c r="C72" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D72" s="52">
-        <v>7</v>
-      </c>
-      <c r="E72" s="52" t="s">
+      <c r="D72" s="50">
+        <v>8</v>
+      </c>
+      <c r="E72" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F72" s="52" t="s">
+      <c r="F72" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="G72" s="52" t="s">
-        <v>197</v>
-      </c>
-      <c r="H72" s="52" t="s">
+      <c r="G72" s="50" t="s">
+        <v>196</v>
+      </c>
+      <c r="H72" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="I72" s="52" t="s">
+      <c r="I72" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="J72" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K72" s="54" t="s">
+      <c r="J72" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K72" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="L72" s="52" t="s">
+      <c r="L72" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="M72" s="52" t="s">
-        <v>109</v>
+      <c r="M72" s="50" t="s">
+        <v>108</v>
       </c>
       <c r="N72" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O72" s="44"/>
     </row>
@@ -6341,44 +6331,44 @@
       <c r="A73" s="43">
         <v>2025</v>
       </c>
-      <c r="B73" s="51" t="s">
+      <c r="B73" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C73" s="52" t="s">
+      <c r="C73" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D73" s="52">
-        <v>7</v>
-      </c>
-      <c r="E73" s="52" t="s">
+      <c r="D73" s="50">
+        <v>8</v>
+      </c>
+      <c r="E73" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F73" s="52" t="s">
+      <c r="F73" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="G73" s="52" t="s">
-        <v>196</v>
-      </c>
-      <c r="H73" s="52" t="s">
+      <c r="G73" s="50" t="s">
+        <v>195</v>
+      </c>
+      <c r="H73" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="I73" s="52" t="s">
+      <c r="I73" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="J73" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K73" s="54" t="s">
+      <c r="J73" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K73" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="L73" s="52" t="s">
+      <c r="L73" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="M73" s="52" t="s">
-        <v>108</v>
+      <c r="M73" s="50" t="s">
+        <v>107</v>
       </c>
       <c r="N73" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O73" s="44"/>
     </row>
@@ -6386,44 +6376,44 @@
       <c r="A74" s="43">
         <v>2025</v>
       </c>
-      <c r="B74" s="51" t="s">
-        <v>132</v>
-      </c>
-      <c r="C74" s="52" t="s">
+      <c r="B74" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="C74" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D74" s="52">
-        <v>7</v>
-      </c>
-      <c r="E74" s="52" t="s">
+      <c r="D74" s="50">
+        <v>8</v>
+      </c>
+      <c r="E74" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F74" s="52" t="s">
+      <c r="F74" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="G74" s="52" t="s">
-        <v>195</v>
-      </c>
-      <c r="H74" s="52" t="s">
+      <c r="G74" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="H74" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="I74" s="52" t="s">
+      <c r="I74" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="J74" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K74" s="54" t="s">
+      <c r="J74" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K74" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="L74" s="52" t="s">
+      <c r="L74" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="M74" s="52" t="s">
+      <c r="M74" s="50" t="s">
         <v>50</v>
       </c>
       <c r="N74" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O74" s="44"/>
     </row>
@@ -6431,44 +6421,44 @@
       <c r="A75" s="43">
         <v>2025</v>
       </c>
-      <c r="B75" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="C75" s="52" t="s">
+      <c r="B75" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="C75" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D75" s="52">
-        <v>7</v>
-      </c>
-      <c r="E75" s="52" t="s">
+      <c r="D75" s="50">
+        <v>8</v>
+      </c>
+      <c r="E75" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F75" s="52" t="s">
-        <v>310</v>
-      </c>
-      <c r="G75" s="52" t="s">
-        <v>313</v>
-      </c>
-      <c r="H75" s="52" t="s">
+      <c r="F75" s="50" t="s">
+        <v>309</v>
+      </c>
+      <c r="G75" s="50" t="s">
+        <v>312</v>
+      </c>
+      <c r="H75" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="I75" s="52" t="s">
+      <c r="I75" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="J75" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K75" s="54" t="s">
+      <c r="J75" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K75" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="L75" s="52" t="s">
+      <c r="L75" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="M75" s="52" t="s">
+      <c r="M75" s="50" t="s">
         <v>48</v>
       </c>
       <c r="N75" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O75" s="44"/>
     </row>
@@ -6476,44 +6466,44 @@
       <c r="A76" s="43">
         <v>2025</v>
       </c>
-      <c r="B76" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="C76" s="52" t="s">
+      <c r="B76" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="C76" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D76" s="52">
-        <v>7</v>
-      </c>
-      <c r="E76" s="52" t="s">
+      <c r="D76" s="50">
+        <v>8</v>
+      </c>
+      <c r="E76" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F76" s="52" t="s">
+      <c r="F76" s="50" t="s">
+        <v>310</v>
+      </c>
+      <c r="G76" s="50" t="s">
         <v>311</v>
       </c>
-      <c r="G76" s="52" t="s">
-        <v>312</v>
-      </c>
-      <c r="H76" s="52" t="s">
+      <c r="H76" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="I76" s="52" t="s">
+      <c r="I76" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="J76" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K76" s="54" t="s">
+      <c r="J76" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K76" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="L76" s="52" t="s">
-        <v>309</v>
-      </c>
-      <c r="M76" s="52" t="s">
+      <c r="L76" s="50" t="s">
+        <v>308</v>
+      </c>
+      <c r="M76" s="50" t="s">
         <v>49</v>
       </c>
       <c r="N76" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O76" s="44"/>
     </row>
@@ -6521,44 +6511,44 @@
       <c r="A77" s="43">
         <v>2025</v>
       </c>
-      <c r="B77" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C77" s="52" t="s">
+      <c r="B77" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C77" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D77" s="52">
-        <v>8</v>
-      </c>
-      <c r="E77" s="52" t="s">
+      <c r="D77" s="50">
+        <v>9</v>
+      </c>
+      <c r="E77" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="F77" s="52" t="s">
+      <c r="F77" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="G77" s="50" t="s">
         <v>244</v>
       </c>
-      <c r="G77" s="52" t="s">
+      <c r="H77" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I77" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="J77" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K77" s="52" t="s">
         <v>245</v>
       </c>
-      <c r="H77" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="I77" s="52" t="s">
-        <v>227</v>
-      </c>
-      <c r="J77" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K77" s="54" t="s">
+      <c r="L77" s="50" t="s">
         <v>246</v>
       </c>
-      <c r="L77" s="52" t="s">
+      <c r="M77" s="50" t="s">
         <v>247</v>
       </c>
-      <c r="M77" s="52" t="s">
-        <v>248</v>
-      </c>
       <c r="N77" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O77" s="44"/>
     </row>
@@ -6566,44 +6556,44 @@
       <c r="A78" s="43">
         <v>2025</v>
       </c>
-      <c r="B78" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C78" s="52" t="s">
+      <c r="B78" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C78" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D78" s="52">
-        <v>8</v>
-      </c>
-      <c r="E78" s="52" t="s">
+      <c r="D78" s="50">
+        <v>9</v>
+      </c>
+      <c r="E78" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="F78" s="52" t="s">
+      <c r="F78" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="G78" s="50" t="s">
+        <v>244</v>
+      </c>
+      <c r="H78" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I78" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="J78" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K78" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="L78" s="50" t="s">
+        <v>260</v>
+      </c>
+      <c r="M78" s="50" t="s">
         <v>249</v>
       </c>
-      <c r="G78" s="52" t="s">
-        <v>245</v>
-      </c>
-      <c r="H78" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="I78" s="52" t="s">
-        <v>227</v>
-      </c>
-      <c r="J78" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K78" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="L78" s="52" t="s">
-        <v>261</v>
-      </c>
-      <c r="M78" s="52" t="s">
-        <v>250</v>
-      </c>
       <c r="N78" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O78" s="44"/>
     </row>
@@ -6611,44 +6601,44 @@
       <c r="A79" s="43">
         <v>2025</v>
       </c>
-      <c r="B79" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C79" s="52" t="s">
+      <c r="B79" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C79" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D79" s="52">
-        <v>8</v>
-      </c>
-      <c r="E79" s="52" t="s">
+      <c r="D79" s="50">
+        <v>9</v>
+      </c>
+      <c r="E79" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="F79" s="52" t="s">
+      <c r="F79" s="50" t="s">
+        <v>253</v>
+      </c>
+      <c r="G79" s="50" t="s">
+        <v>244</v>
+      </c>
+      <c r="H79" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I79" s="50" t="s">
         <v>254</v>
       </c>
-      <c r="G79" s="52" t="s">
-        <v>245</v>
-      </c>
-      <c r="H79" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="I79" s="52" t="s">
+      <c r="J79" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K79" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="J79" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K79" s="53" t="s">
+      <c r="L79" s="50" t="s">
         <v>256</v>
       </c>
-      <c r="L79" s="52" t="s">
+      <c r="M79" s="50" t="s">
         <v>257</v>
       </c>
-      <c r="M79" s="52" t="s">
-        <v>258</v>
-      </c>
       <c r="N79" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O79" s="44"/>
     </row>
@@ -6656,44 +6646,44 @@
       <c r="A80" s="43">
         <v>2025</v>
       </c>
-      <c r="B80" s="51" t="s">
-        <v>307</v>
-      </c>
-      <c r="C80" s="52" t="s">
+      <c r="B80" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="C80" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D80" s="52">
+      <c r="D80" s="50">
         <v>10</v>
       </c>
-      <c r="E80" s="52" t="s">
+      <c r="E80" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="F80" s="52" t="s">
-        <v>160</v>
-      </c>
-      <c r="G80" s="52" t="s">
-        <v>194</v>
-      </c>
-      <c r="H80" s="52" t="s">
+      <c r="F80" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="G80" s="50" t="s">
+        <v>193</v>
+      </c>
+      <c r="H80" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I80" s="52" t="s">
+      <c r="I80" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="J80" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K80" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="L80" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="J80" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K80" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="L80" s="52" t="s">
-        <v>163</v>
-      </c>
-      <c r="M80" s="52" t="s">
-        <v>165</v>
+      <c r="M80" s="50" t="s">
+        <v>164</v>
       </c>
       <c r="N80" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O80" s="44"/>
     </row>
@@ -6701,44 +6691,44 @@
       <c r="A81" s="43">
         <v>2025</v>
       </c>
-      <c r="B81" s="51" t="s">
-        <v>308</v>
-      </c>
-      <c r="C81" s="52" t="s">
+      <c r="B81" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="C81" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D81" s="52">
+      <c r="D81" s="50">
         <v>10</v>
       </c>
-      <c r="E81" s="52" t="s">
+      <c r="E81" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="F81" s="52" t="s">
+      <c r="F81" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="G81" s="50" t="s">
+        <v>193</v>
+      </c>
+      <c r="H81" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I81" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="G81" s="52" t="s">
-        <v>194</v>
-      </c>
-      <c r="H81" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="I81" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="J81" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K81" s="54" t="s">
+      <c r="J81" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K81" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="L81" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="M81" s="52" t="s">
-        <v>166</v>
+      <c r="L81" s="50" t="s">
+        <v>163</v>
+      </c>
+      <c r="M81" s="50" t="s">
+        <v>165</v>
       </c>
       <c r="N81" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O81" s="44"/>
     </row>
@@ -6746,44 +6736,44 @@
       <c r="A82" s="43">
         <v>2025</v>
       </c>
-      <c r="B82" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C82" s="52" t="s">
+      <c r="B82" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C82" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D82" s="52">
-        <v>11</v>
-      </c>
-      <c r="E82" s="52" t="s">
-        <v>211</v>
-      </c>
-      <c r="F82" s="52" t="s">
-        <v>333</v>
-      </c>
-      <c r="G82" s="52" t="s">
-        <v>329</v>
-      </c>
-      <c r="H82" s="52" t="s">
+      <c r="D82" s="50">
+        <v>11</v>
+      </c>
+      <c r="E82" s="50" t="s">
+        <v>210</v>
+      </c>
+      <c r="F82" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="G82" s="50" t="s">
+        <v>328</v>
+      </c>
+      <c r="H82" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="I82" s="52" t="s">
-        <v>336</v>
-      </c>
-      <c r="J82" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K82" s="54" t="s">
-        <v>171</v>
-      </c>
-      <c r="L82" s="52" t="s">
-        <v>332</v>
-      </c>
-      <c r="M82" s="52" t="s">
+      <c r="I82" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J82" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K82" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="L82" s="50" t="s">
         <v>331</v>
       </c>
+      <c r="M82" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="N82" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O82" s="44"/>
     </row>
@@ -6791,44 +6781,44 @@
       <c r="A83" s="43">
         <v>2025</v>
       </c>
-      <c r="B83" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C83" s="52" t="s">
+      <c r="B83" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C83" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D83" s="52">
+      <c r="D83" s="50">
         <v>12</v>
       </c>
-      <c r="E83" s="52" t="s">
-        <v>212</v>
-      </c>
-      <c r="F83" s="52" t="s">
+      <c r="E83" s="50" t="s">
+        <v>211</v>
+      </c>
+      <c r="F83" s="50" t="s">
+        <v>333</v>
+      </c>
+      <c r="G83" s="50" t="s">
         <v>334</v>
       </c>
-      <c r="G83" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="H83" s="52" t="s">
+      <c r="H83" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="I83" s="52" t="s">
-        <v>178</v>
-      </c>
-      <c r="J83" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K83" s="54" t="s">
+      <c r="I83" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="J83" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K83" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="L83" s="52" t="s">
+      <c r="L83" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="M83" s="50" t="s">
         <v>337</v>
       </c>
-      <c r="M83" s="52" t="s">
-        <v>338</v>
-      </c>
       <c r="N83" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O83" s="44"/>
     </row>
@@ -6836,44 +6826,44 @@
       <c r="A84" s="43">
         <v>2025</v>
       </c>
-      <c r="B84" s="51" t="s">
+      <c r="B84" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="C84" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D84" s="50">
+        <v>13</v>
+      </c>
+      <c r="E84" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="F84" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="C84" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="D84" s="52">
-        <v>13</v>
-      </c>
-      <c r="E84" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="F84" s="52" t="s">
+      <c r="G84" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="H84" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="I84" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="J84" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K84" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="G84" s="52" t="s">
-        <v>213</v>
-      </c>
-      <c r="H84" s="52" t="s">
-        <v>78</v>
-      </c>
-      <c r="I84" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="J84" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K84" s="54" t="s">
+      <c r="L84" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="L84" s="52" t="s">
-        <v>85</v>
-      </c>
-      <c r="M84" s="52" t="s">
-        <v>107</v>
+      <c r="M84" s="50" t="s">
+        <v>106</v>
       </c>
       <c r="N84" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O84" s="44"/>
     </row>
@@ -6881,44 +6871,44 @@
       <c r="A85" s="43">
         <v>2025</v>
       </c>
-      <c r="B85" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="C85" s="52" t="s">
+      <c r="B85" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="C85" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D85" s="52">
+      <c r="D85" s="50">
         <v>13</v>
       </c>
-      <c r="E85" s="52" t="s">
+      <c r="E85" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="F85" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="G85" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="H85" s="52" t="s">
-        <v>88</v>
-      </c>
-      <c r="I85" s="52" t="s">
-        <v>102</v>
-      </c>
-      <c r="J85" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K85" s="54" t="s">
+      <c r="F85" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G85" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="H85" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="I85" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="J85" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K85" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="L85" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="M85" s="52" t="s">
-        <v>106</v>
+      <c r="L85" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="M85" s="50" t="s">
+        <v>105</v>
       </c>
       <c r="N85" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O85" s="44"/>
     </row>
@@ -6926,44 +6916,44 @@
       <c r="A86" s="43">
         <v>2025</v>
       </c>
-      <c r="B86" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="C86" s="52" t="s">
+      <c r="B86" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="C86" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D86" s="52">
+      <c r="D86" s="50">
         <v>13</v>
       </c>
-      <c r="E86" s="52" t="s">
+      <c r="E86" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="F86" s="52" t="s">
+      <c r="F86" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="G86" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="H86" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="I86" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="J86" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K86" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="L86" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="G86" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="H86" s="52" t="s">
-        <v>88</v>
-      </c>
-      <c r="I86" s="52" t="s">
-        <v>102</v>
-      </c>
-      <c r="J86" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K86" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="L86" s="52" t="s">
-        <v>93</v>
-      </c>
-      <c r="M86" s="52" t="s">
-        <v>105</v>
+      <c r="M86" s="50" t="s">
+        <v>104</v>
       </c>
       <c r="N86" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O86" s="44"/>
     </row>
@@ -6971,44 +6961,44 @@
       <c r="A87" s="43">
         <v>2025</v>
       </c>
-      <c r="B87" s="51" t="s">
+      <c r="B87" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C87" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D87" s="50">
+        <v>13</v>
+      </c>
+      <c r="E87" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="F87" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="C87" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="D87" s="52">
-        <v>13</v>
-      </c>
-      <c r="E87" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="F87" s="52" t="s">
+      <c r="G87" s="50" t="s">
+        <v>191</v>
+      </c>
+      <c r="H87" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="G87" s="52" t="s">
-        <v>192</v>
-      </c>
-      <c r="H87" s="52" t="s">
+      <c r="I87" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="I87" s="52" t="s">
-        <v>101</v>
-      </c>
-      <c r="J87" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K87" s="54" t="s">
+      <c r="J87" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K87" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="L87" s="52" t="s">
+      <c r="L87" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="M87" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="M87" s="52" t="s">
-        <v>104</v>
-      </c>
       <c r="N87" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O87" s="44"/>
     </row>
@@ -7016,44 +7006,44 @@
       <c r="A88" s="43">
         <v>2025</v>
       </c>
-      <c r="B88" s="51" t="s">
-        <v>221</v>
-      </c>
-      <c r="C88" s="52" t="s">
+      <c r="B88" s="44" t="s">
+        <v>220</v>
+      </c>
+      <c r="C88" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D88" s="52">
+      <c r="D88" s="50">
         <v>14</v>
       </c>
-      <c r="E88" s="52" t="s">
+      <c r="E88" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="F88" s="52" t="s">
-        <v>189</v>
-      </c>
-      <c r="G88" s="52" t="s">
-        <v>223</v>
-      </c>
-      <c r="H88" s="52" t="s">
+      <c r="F88" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="G88" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="H88" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="I88" s="50" t="s">
         <v>177</v>
       </c>
-      <c r="I88" s="52" t="s">
-        <v>178</v>
-      </c>
-      <c r="J88" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K88" s="54" t="s">
+      <c r="J88" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K88" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="L88" s="52" t="s">
-        <v>188</v>
-      </c>
-      <c r="M88" s="52" t="s">
-        <v>225</v>
+      <c r="L88" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="M88" s="50" t="s">
+        <v>224</v>
       </c>
       <c r="N88" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O88" s="44"/>
     </row>
@@ -7061,44 +7051,44 @@
       <c r="A89" s="43">
         <v>2025</v>
       </c>
-      <c r="B89" s="51" t="s">
-        <v>214</v>
-      </c>
-      <c r="C89" s="52" t="s">
+      <c r="B89" s="44" t="s">
+        <v>213</v>
+      </c>
+      <c r="C89" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D89" s="52">
+      <c r="D89" s="50">
         <v>15</v>
       </c>
-      <c r="E89" s="52" t="s">
+      <c r="E89" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="F89" s="52" t="s">
-        <v>219</v>
-      </c>
-      <c r="G89" s="52" t="s">
-        <v>191</v>
-      </c>
-      <c r="H89" s="52" t="s">
+      <c r="F89" s="50" t="s">
+        <v>218</v>
+      </c>
+      <c r="G89" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="H89" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I89" s="52" t="s">
+      <c r="I89" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="J89" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K89" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="L89" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="J89" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K89" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="L89" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="M89" s="52" t="s">
-        <v>216</v>
+      <c r="M89" s="50" t="s">
+        <v>215</v>
       </c>
       <c r="N89" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O89" s="44"/>
     </row>
@@ -7106,44 +7096,44 @@
       <c r="A90" s="43">
         <v>2025</v>
       </c>
-      <c r="B90" s="51" t="s">
-        <v>215</v>
-      </c>
-      <c r="C90" s="52" t="s">
+      <c r="B90" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="C90" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D90" s="52">
+      <c r="D90" s="50">
         <v>15</v>
       </c>
-      <c r="E90" s="52" t="s">
+      <c r="E90" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="F90" s="52" t="s">
-        <v>218</v>
-      </c>
-      <c r="G90" s="52" t="s">
-        <v>191</v>
-      </c>
-      <c r="H90" s="52" t="s">
+      <c r="F90" s="50" t="s">
+        <v>217</v>
+      </c>
+      <c r="G90" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="H90" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I90" s="52" t="s">
+      <c r="I90" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="J90" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K90" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="L90" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="J90" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K90" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="L90" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="M90" s="52" t="s">
-        <v>217</v>
+      <c r="M90" s="50" t="s">
+        <v>216</v>
       </c>
       <c r="N90" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O90" s="44"/>
     </row>
@@ -7151,42 +7141,42 @@
       <c r="A91" s="43">
         <v>2025</v>
       </c>
-      <c r="B91" s="51" t="s">
+      <c r="B91" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C91" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D91" s="50">
+        <v>15</v>
+      </c>
+      <c r="E91" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F91" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="G91" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="H91" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I91" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="C91" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="D91" s="52">
-        <v>15</v>
-      </c>
-      <c r="E91" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="F91" s="52" t="s">
+      <c r="J91" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K91" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="L91" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="G91" s="52" t="s">
-        <v>191</v>
-      </c>
-      <c r="H91" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="I91" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="J91" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K91" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="L91" s="52" t="s">
-        <v>129</v>
-      </c>
-      <c r="M91" s="52"/>
+      <c r="M91" s="50"/>
       <c r="N91" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O91" s="44"/>
     </row>
@@ -7194,44 +7184,44 @@
       <c r="A92" s="43">
         <v>2025</v>
       </c>
-      <c r="B92" s="51" t="s">
+      <c r="B92" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="C92" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D92" s="50">
+        <v>15</v>
+      </c>
+      <c r="E92" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F92" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="C92" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="D92" s="52">
-        <v>15</v>
-      </c>
-      <c r="E92" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="F92" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="G92" s="52" t="s">
-        <v>191</v>
-      </c>
-      <c r="H92" s="52" t="s">
+      <c r="G92" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="H92" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I92" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="J92" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K92" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="L92" s="52" t="s">
-        <v>124</v>
-      </c>
-      <c r="M92" s="52" t="s">
-        <v>126</v>
+      <c r="I92" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="J92" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K92" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="L92" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="M92" s="50" t="s">
+        <v>125</v>
       </c>
       <c r="N92" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O92" s="44"/>
     </row>
@@ -7239,44 +7229,44 @@
       <c r="A93" s="43">
         <v>2025</v>
       </c>
-      <c r="B93" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="C93" s="52" t="s">
+      <c r="B93" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="C93" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D93" s="52">
+      <c r="D93" s="50">
         <v>15</v>
       </c>
-      <c r="E93" s="52" t="s">
+      <c r="E93" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="F93" s="52" t="s">
-        <v>123</v>
-      </c>
-      <c r="G93" s="52" t="s">
-        <v>191</v>
-      </c>
-      <c r="H93" s="52" t="s">
+      <c r="F93" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="G93" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="H93" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I93" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="J93" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K93" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="L93" s="52" t="s">
-        <v>125</v>
-      </c>
-      <c r="M93" s="52" t="s">
-        <v>127</v>
+      <c r="I93" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="J93" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K93" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="L93" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="M93" s="50" t="s">
+        <v>126</v>
       </c>
       <c r="N93" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O93" s="44"/>
     </row>
@@ -7284,44 +7274,44 @@
       <c r="A94" s="43">
         <v>2025</v>
       </c>
-      <c r="B94" s="51" t="s">
-        <v>187</v>
-      </c>
-      <c r="C94" s="52" t="s">
+      <c r="B94" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="C94" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D94" s="52">
+      <c r="D94" s="50">
         <v>16</v>
       </c>
-      <c r="E94" s="52" t="s">
+      <c r="E94" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="F94" s="52" t="s">
-        <v>222</v>
-      </c>
-      <c r="G94" s="52" t="s">
-        <v>190</v>
-      </c>
-      <c r="H94" s="52" t="s">
+      <c r="F94" s="50" t="s">
+        <v>221</v>
+      </c>
+      <c r="G94" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="H94" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="I94" s="50" t="s">
         <v>177</v>
       </c>
-      <c r="I94" s="52" t="s">
-        <v>178</v>
-      </c>
-      <c r="J94" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K94" s="54" t="s">
+      <c r="J94" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K94" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="L94" s="52" t="s">
-        <v>224</v>
-      </c>
-      <c r="M94" s="52" t="s">
-        <v>206</v>
+      <c r="L94" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="M94" s="50" t="s">
+        <v>205</v>
       </c>
       <c r="N94" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O94" s="44"/>
     </row>
@@ -7329,44 +7319,44 @@
       <c r="A95" s="43">
         <v>2025</v>
       </c>
-      <c r="B95" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C95" s="52" t="s">
+      <c r="B95" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C95" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D95" s="52">
+      <c r="D95" s="50">
         <v>17</v>
       </c>
-      <c r="E95" s="52" t="s">
+      <c r="E95" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="F95" s="52" t="s">
+      <c r="F95" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="G95" s="50" t="s">
+        <v>236</v>
+      </c>
+      <c r="H95" s="50" t="s">
+        <v>237</v>
+      </c>
+      <c r="I95" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="J95" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K95" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="L95" s="50" t="s">
         <v>322</v>
       </c>
-      <c r="G95" s="52" t="s">
-        <v>237</v>
-      </c>
-      <c r="H95" s="52" t="s">
-        <v>238</v>
-      </c>
-      <c r="I95" s="52" t="s">
-        <v>321</v>
-      </c>
-      <c r="J95" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K95" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="L95" s="52" t="s">
+      <c r="M95" s="50" t="s">
         <v>323</v>
       </c>
-      <c r="M95" s="52" t="s">
-        <v>324</v>
-      </c>
       <c r="N95" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O95" s="44"/>
     </row>
@@ -7374,44 +7364,44 @@
       <c r="A96" s="43">
         <v>2025</v>
       </c>
-      <c r="B96" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C96" s="52" t="s">
+      <c r="B96" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C96" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D96" s="52">
+      <c r="D96" s="50">
         <v>17</v>
       </c>
-      <c r="E96" s="52" t="s">
+      <c r="E96" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="F96" s="52" t="s">
+      <c r="F96" s="50" t="s">
+        <v>239</v>
+      </c>
+      <c r="G96" s="50" t="s">
+        <v>236</v>
+      </c>
+      <c r="H96" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I96" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="J96" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K96" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="L96" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="G96" s="52" t="s">
-        <v>237</v>
-      </c>
-      <c r="H96" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="I96" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="J96" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K96" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="L96" s="52" t="s">
+      <c r="M96" s="50" t="s">
         <v>241</v>
       </c>
-      <c r="M96" s="52" t="s">
-        <v>242</v>
-      </c>
       <c r="N96" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O96" s="44"/>
     </row>
@@ -7419,44 +7409,44 @@
       <c r="A97" s="43">
         <v>2025</v>
       </c>
-      <c r="B97" s="57" t="s">
-        <v>119</v>
-      </c>
-      <c r="C97" s="52" t="s">
+      <c r="B97" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="C97" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D97" s="52">
+      <c r="D97" s="50">
         <v>17</v>
       </c>
-      <c r="E97" s="52" t="s">
+      <c r="E97" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="F97" s="58" t="s">
+      <c r="F97" s="54" t="s">
+        <v>250</v>
+      </c>
+      <c r="G97" s="50" t="s">
+        <v>236</v>
+      </c>
+      <c r="H97" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I97" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="J97" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K97" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="L97" s="54" t="s">
         <v>251</v>
       </c>
-      <c r="G97" s="52" t="s">
-        <v>237</v>
-      </c>
-      <c r="H97" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="I97" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="J97" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="K97" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="L97" s="58" t="s">
+      <c r="M97" s="54" t="s">
         <v>252</v>
       </c>
-      <c r="M97" s="58" t="s">
-        <v>253</v>
-      </c>
       <c r="N97" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O97" s="44"/>
     </row>
@@ -7490,33 +7480,33 @@
   <sheetData>
     <row r="1" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -7544,7 +7534,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -7572,7 +7562,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -7600,7 +7590,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -7628,7 +7618,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -7656,7 +7646,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -7684,7 +7674,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -7712,7 +7702,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -7740,7 +7730,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -7768,7 +7758,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -7796,7 +7786,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -7824,7 +7814,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -7903,33 +7893,33 @@
   <sheetData>
     <row r="1" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A1" s="31" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="D1" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="E1" s="31" t="s">
         <v>278</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="F1" s="31" t="s">
         <v>279</v>
       </c>
-      <c r="F1" s="31" t="s">
-        <v>280</v>
-      </c>
       <c r="G1" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1" s="31" t="s">
         <v>289</v>
-      </c>
-      <c r="H1" s="31" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A2" s="31" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B2" s="31">
         <v>2024</v>
@@ -7955,7 +7945,7 @@
     </row>
     <row r="3" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A3" s="31" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B3" s="31">
         <v>2024</v>
@@ -7981,7 +7971,7 @@
     </row>
     <row r="4" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A4" s="31" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B4" s="31">
         <v>2024</v>
@@ -8005,7 +7995,7 @@
     </row>
     <row r="5" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A5" s="31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B5" s="31">
         <v>2024</v>
@@ -8031,7 +8021,7 @@
     </row>
     <row r="6" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A6" s="31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B6" s="31">
         <v>2024</v>
@@ -8055,7 +8045,7 @@
     </row>
     <row r="7" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A7" s="31" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B7" s="31">
         <v>2024</v>
@@ -8079,7 +8069,7 @@
     </row>
     <row r="8" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A8" s="31" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B8" s="31">
         <v>2024</v>
@@ -8105,7 +8095,7 @@
     </row>
     <row r="9" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A9" s="33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B9" s="31">
         <v>2024</v>
